--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfw\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC282DF3-576D-4027-BB26-43B9829CDE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2209,6 +2206,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2216,7 +2214,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4654,6 +4651,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4661,7 +4659,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5158,6 +5155,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5165,7 +5163,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7603,6 +7600,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7610,7 +7608,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8104,6 +8101,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8111,7 +8109,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11385,9 +11382,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
   <dimension ref="A1:N160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11419,7 +11416,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -11461,7 +11458,7 @@
         <v>2.4909699122220328E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -11503,7 +11500,7 @@
         <v>3.9061146219856075E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -11514,7 +11511,7 @@
         <v>0.13701539714226199</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -11525,7 +11522,7 @@
         <v>0.13611960900852699</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -11536,7 +11533,7 @@
         <v>0.13627945937632699</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -11547,7 +11544,7 @@
         <v>0.30390235043574698</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -11558,7 +11555,7 @@
         <v>0.30438419283964002</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -11569,7 +11566,7 @@
         <v>0.297161130585052</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -11580,7 +11577,7 @@
         <v>0.30092447877826201</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -11591,7 +11588,7 @@
         <v>0.30225556251139701</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -11602,7 +11599,7 @@
         <v>0.30453505035585898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -11613,7 +11610,7 @@
         <v>0.29441937543381203</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -11624,7 +11621,7 @@
         <v>0.29938049893952201</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -11635,7 +11632,7 @@
         <v>0.30198767465833298</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -11646,7 +11643,7 @@
         <v>0.29452133244947898</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -11657,7 +11654,7 @@
         <v>0.30226636207287</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -11668,7 +11665,7 @@
         <v>0.30276185184620003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -11679,7 +11676,7 @@
         <v>0.30565983998385898</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -11690,7 +11687,7 @@
         <v>0.30235700258888798</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -11701,7 +11698,7 @@
         <v>0.30470031507930101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -11712,7 +11709,7 @@
         <v>0.30681032275950298</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -11723,7 +11720,7 @@
         <v>0.31003085423784599</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -11734,7 +11731,7 @@
         <v>0.30130891367381502</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -11745,7 +11742,7 @@
         <v>0.141175020925183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -11756,7 +11753,7 @@
         <v>0.13910706901585701</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -11767,7 +11764,7 @@
         <v>0.14173595580689399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -11778,7 +11775,7 @@
         <v>0.141258173819516</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
@@ -11789,7 +11786,7 @@
         <v>0.142207734258748</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -11800,7 +11797,7 @@
         <v>0.13801119003128501</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -11811,7 +11808,7 @@
         <v>0.14302506923553299</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -11822,7 +11819,7 @@
         <v>0.171876620266287</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -11833,7 +11830,7 @@
         <v>0.17507983789020901</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -11844,7 +11841,7 @@
         <v>0.17353748848485201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -11855,7 +11852,7 @@
         <v>0.17399520336378199</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -11866,7 +11863,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -11877,7 +11874,7 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -11888,7 +11885,7 @@
         <v>0.17111359499762699</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -11899,7 +11896,7 @@
         <v>0.174442312499583</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -11910,7 +11907,7 @@
         <v>0.17165345419397299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -11921,7 +11918,7 @@
         <v>0.17188594050678699</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -11932,7 +11929,7 @@
         <v>0.17182639857690499</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -11943,7 +11940,7 @@
         <v>0.173011271970926</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -11954,7 +11951,7 @@
         <v>0.173393882992014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -11965,7 +11962,7 @@
         <v>0.17255170638235601</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -11976,7 +11973,7 @@
         <v>0.176156057962948</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -11987,7 +11984,7 @@
         <v>0.17277891898827699</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -11998,7 +11995,7 @@
         <v>0.173614948750792</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -12009,7 +12006,7 @@
         <v>0.17607067167010601</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -12020,7 +12017,7 @@
         <v>0.17040120856414201</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -12031,7 +12028,7 @@
         <v>0.17423160269966501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -12042,7 +12039,7 @@
         <v>0.174369956316375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -12053,7 +12050,7 @@
         <v>0.17111424613243301</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -12064,7 +12061,7 @@
         <v>0.174141819699693</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -12075,7 +12072,7 @@
         <v>0.17027613633024699</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -12086,7 +12083,7 @@
         <v>0.17305899861083601</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -12097,7 +12094,7 @@
         <v>0.169629744786672</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -12108,7 +12105,7 @@
         <v>0.17362236751906199</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -12119,7 +12116,7 @@
         <v>0.17378947989454699</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -12130,7 +12127,7 @@
         <v>0.17301730214639</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -12141,7 +12138,7 @@
         <v>0.17294290042990301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -12152,7 +12149,7 @@
         <v>0.17314296764265499</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -12163,7 +12160,7 @@
         <v>0.26702709086345899</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -12174,7 +12171,7 @@
         <v>0.26377604366503299</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -12185,7 +12182,7 @@
         <v>0.26272554597887199</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -12196,7 +12193,7 @@
         <v>0.26788317969509901</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -12207,7 +12204,7 @@
         <v>0.26503400399869398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -12218,7 +12215,7 @@
         <v>0.26673897966627602</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -12229,7 +12226,7 @@
         <v>0.26807575946030698</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -12240,7 +12237,7 @@
         <v>0.266570039729353</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -12251,7 +12248,7 @@
         <v>0.27166172606546901</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -12262,7 +12259,7 @@
         <v>0.26522605962651602</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -12273,7 +12270,7 @@
         <v>0.27094063293660098</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -12284,7 +12281,7 @@
         <v>0.26838563360762802</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -12295,7 +12292,7 @@
         <v>0.26226006746867903</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -12306,7 +12303,7 @@
         <v>0.26283415625491802</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -12317,7 +12314,7 @@
         <v>0.265891536409124</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -12328,7 +12325,7 @@
         <v>0.26086999753535101</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -12339,7 +12336,7 @@
         <v>0.264030412441006</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -12350,7 +12347,7 @@
         <v>0.26104421609513101</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -12361,7 +12358,7 @@
         <v>0.26790761730572898</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -12372,7 +12369,7 @@
         <v>0.26200964452208297</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -12383,7 +12380,7 @@
         <v>0.26657014430711701</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>90</v>
       </c>
@@ -12394,7 +12391,7 @@
         <v>0.264335730958146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>91</v>
       </c>
@@ -12405,7 +12402,7 @@
         <v>0.26876048744697101</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>92</v>
       </c>
@@ -12416,7 +12413,7 @@
         <v>0.26514897700620299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>93</v>
       </c>
@@ -12427,7 +12424,7 @@
         <v>0.26219390887345601</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>94</v>
       </c>
@@ -12438,7 +12435,7 @@
         <v>0.26184487099436499</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>95</v>
       </c>
@@ -12449,7 +12446,7 @@
         <v>0.26409583467590397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>96</v>
       </c>
@@ -12460,7 +12457,7 @@
         <v>0.26424448419416702</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>97</v>
       </c>
@@ -12471,7 +12468,7 @@
         <v>0.26363414452799</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>98</v>
       </c>
@@ -12482,7 +12479,7 @@
         <v>0.26464837628465498</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>99</v>
       </c>
@@ -12493,7 +12490,7 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>107</v>
       </c>
@@ -12504,7 +12501,7 @@
         <v>0.23820566920665201</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>108</v>
       </c>
@@ -12515,7 +12512,7 @@
         <v>0.23716854436609899</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>109</v>
       </c>
@@ -12526,7 +12523,7 @@
         <v>0.24334889035587701</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>110</v>
       </c>
@@ -12537,7 +12534,7 @@
         <v>0.24139693907330401</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>111</v>
       </c>
@@ -12548,7 +12545,7 @@
         <v>0.24177140642297701</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>112</v>
       </c>
@@ -12559,7 +12556,7 @@
         <v>0.24611015618375001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>113</v>
       </c>
@@ -12570,7 +12567,7 @@
         <v>0.24482638982888399</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>114</v>
       </c>
@@ -12581,7 +12578,7 @@
         <v>0.24047022478348701</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>115</v>
       </c>
@@ -12592,7 +12589,7 @@
         <v>0.24076714972723101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>116</v>
       </c>
@@ -12603,7 +12600,7 @@
         <v>0.244370206125226</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>117</v>
       </c>
@@ -12614,7 +12611,7 @@
         <v>0.24313993631303599</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
@@ -12625,7 +12622,7 @@
         <v>0.240076934656237</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
@@ -12636,7 +12633,7 @@
         <v>0.242245334794052</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -12647,7 +12644,7 @@
         <v>0.24081642222489599</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -12658,7 +12655,7 @@
         <v>0.23946128860629701</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>122</v>
       </c>
@@ -12669,7 +12666,7 @@
         <v>0.24067136591591201</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -12680,7 +12677,7 @@
         <v>0.241804540636641</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -12691,7 +12688,7 @@
         <v>0.237876942608618</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -12702,7 +12699,7 @@
         <v>0.241838145831969</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>126</v>
       </c>
@@ -12713,7 +12710,7 @@
         <v>0.24402502768845699</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>127</v>
       </c>
@@ -12724,7 +12721,7 @@
         <v>0.23989744417664499</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>128</v>
       </c>
@@ -12735,7 +12732,7 @@
         <v>0.240176182150968</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>129</v>
       </c>
@@ -12746,7 +12743,7 @@
         <v>0.238939795428251</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -12757,7 +12754,7 @@
         <v>0.23962573892411401</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -12768,7 +12765,7 @@
         <v>0.24176111907040099</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
         <v>132</v>
       </c>
@@ -12779,7 +12776,7 @@
         <v>0.24348653683848701</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1" t="s">
         <v>133</v>
       </c>
@@ -12790,7 +12787,7 @@
         <v>0.24073031648363399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
         <v>134</v>
       </c>
@@ -12801,7 +12798,7 @@
         <v>0.24558776594854301</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
         <v>135</v>
       </c>
@@ -12812,7 +12809,7 @@
         <v>0.239185337596831</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1" t="s">
         <v>136</v>
       </c>
@@ -12823,7 +12820,7 @@
         <v>0.241717931493385</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>137</v>
       </c>
@@ -12834,7 +12831,7 @@
         <v>0.24138266998260599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
         <v>138</v>
       </c>
@@ -12845,7 +12842,7 @@
         <v>0.24367652321245201</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="1" t="s">
         <v>139</v>
       </c>
@@ -12856,7 +12853,7 @@
         <v>0.22233607124480101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1" t="s">
         <v>140</v>
       </c>
@@ -12867,7 +12864,7 @@
         <v>0.222916111013889</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1" t="s">
         <v>141</v>
       </c>
@@ -12878,7 +12875,7 @@
         <v>0.21978080516705001</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="1" t="s">
         <v>142</v>
       </c>
@@ -12889,7 +12886,7 @@
         <v>0.21701744510815299</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1" t="s">
         <v>143</v>
       </c>
@@ -12900,7 +12897,7 @@
         <v>0.22292724198768199</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
@@ -12911,7 +12908,7 @@
         <v>0.222109442813166</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1" t="s">
         <v>145</v>
       </c>
@@ -12922,7 +12919,7 @@
         <v>0.221905259897859</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1" t="s">
         <v>146</v>
       </c>
@@ -12933,7 +12930,7 @@
         <v>0.21899661326540701</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1" t="s">
         <v>147</v>
       </c>
@@ -12944,7 +12941,7 @@
         <v>0.21885786728813</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -12955,7 +12952,7 @@
         <v>0.21579488523700499</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -12966,7 +12963,7 @@
         <v>0.220755926487161</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1" t="s">
         <v>150</v>
       </c>
@@ -12977,7 +12974,7 @@
         <v>0.22011228616490899</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1" t="s">
         <v>151</v>
       </c>
@@ -12988,7 +12985,7 @@
         <v>0.21961259407713499</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1" t="s">
         <v>152</v>
       </c>
@@ -12999,7 +12996,7 @@
         <v>0.22007796981835101</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -13010,7 +13007,7 @@
         <v>0.21807344865282799</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1" t="s">
         <v>154</v>
       </c>
@@ -13021,7 +13018,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
@@ -13032,7 +13029,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1" t="s">
         <v>156</v>
       </c>
@@ -13043,7 +13040,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1" t="s">
         <v>157</v>
       </c>
@@ -13054,7 +13051,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1" t="s">
         <v>158</v>
       </c>
@@ -13065,7 +13062,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1" t="s">
         <v>159</v>
       </c>
@@ -13076,7 +13073,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1" t="s">
         <v>160</v>
       </c>
@@ -13087,7 +13084,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1" t="s">
         <v>161</v>
       </c>
@@ -13098,7 +13095,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1" t="s">
         <v>162</v>
       </c>
@@ -13109,7 +13106,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1" t="s">
         <v>163</v>
       </c>
@@ -13120,7 +13117,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1" t="s">
         <v>164</v>
       </c>
@@ -13131,7 +13128,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="1" t="s">
         <v>165</v>
       </c>
@@ -13142,7 +13139,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1" t="s">
         <v>166</v>
       </c>
@@ -13153,7 +13150,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -13164,7 +13161,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="1" t="s">
         <v>168</v>
       </c>
@@ -13175,7 +13172,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1" t="s">
         <v>169</v>
       </c>
@@ -13186,7 +13183,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1" t="s">
         <v>170</v>
       </c>
@@ -13197,7 +13194,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1" t="s">
         <v>171</v>
       </c>
@@ -13208,7 +13205,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1" t="s">
         <v>172</v>
       </c>
@@ -13219,7 +13216,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="1" t="s">
         <v>173</v>
       </c>
@@ -13239,13 +13236,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.41796875" customWidth="1"/>
+    <col min="2" max="2" width="11.578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -13254,7 +13251,7 @@
         <v>1.0410422795260443E-3</v>
       </c>
       <c r="C1">
-        <f t="shared" ref="C1:K1" si="0">_xlfn.STDEV.S(C4:C39)/SQRT(COUNT(C4:C39))</f>
+        <f t="shared" ref="C1:H1" si="0">_xlfn.STDEV.S(C4:C39)/SQRT(COUNT(C4:C39))</f>
         <v>9.3859041068293373E-4</v>
       </c>
       <c r="D1">
@@ -13282,7 +13279,7 @@
         <v>2.8613971962500952E-4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -13291,7 +13288,7 @@
         <v>0.77222061447474444</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:K2" si="2">100*C1/AVERAGE(C4:C39)</f>
+        <f t="shared" ref="C2:H2" si="2">100*C1/AVERAGE(C4:C39)</f>
         <v>0.31059913870542799</v>
       </c>
       <c r="D2">
@@ -13319,7 +13316,7 @@
         <v>0.12997532261023939</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -13350,7 +13347,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1</v>
       </c>
@@ -13381,7 +13378,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>2</v>
       </c>
@@ -13412,7 +13409,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>3</v>
       </c>
@@ -13443,7 +13440,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>4</v>
       </c>
@@ -13474,7 +13471,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>5</v>
       </c>
@@ -13505,7 +13502,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>6</v>
       </c>
@@ -13532,7 +13529,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>7</v>
       </c>
@@ -13557,7 +13554,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>8</v>
       </c>
@@ -13580,7 +13577,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>9</v>
       </c>
@@ -13603,7 +13600,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>10</v>
       </c>
@@ -13626,7 +13623,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>11</v>
       </c>
@@ -13649,7 +13646,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>12</v>
       </c>
@@ -13672,7 +13669,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>13</v>
       </c>
@@ -13695,7 +13692,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>14</v>
       </c>
@@ -13718,7 +13715,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>15</v>
       </c>
@@ -13741,7 +13738,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>16</v>
       </c>
@@ -13763,7 +13760,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>17</v>
       </c>
@@ -13785,7 +13782,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>18</v>
       </c>
@@ -13807,7 +13804,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>19</v>
       </c>
@@ -13827,7 +13824,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>20</v>
       </c>
@@ -13847,7 +13844,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>21</v>
       </c>
@@ -13866,7 +13863,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>22</v>
       </c>
@@ -13885,7 +13882,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>23</v>
       </c>
@@ -13904,7 +13901,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>24</v>
       </c>
@@ -13923,7 +13920,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>25</v>
       </c>
@@ -13942,7 +13939,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>26</v>
       </c>
@@ -13958,7 +13955,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>27</v>
       </c>
@@ -13974,7 +13971,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>28</v>
       </c>
@@ -13990,7 +13987,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>29</v>
       </c>
@@ -14006,7 +14003,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>30</v>
       </c>
@@ -14022,7 +14019,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>31</v>
       </c>
@@ -14038,7 +14035,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>32</v>
       </c>
@@ -14051,7 +14048,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>33</v>
       </c>
@@ -14060,7 +14057,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>34</v>
       </c>
@@ -14069,7 +14066,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>35</v>
       </c>
@@ -14078,7 +14075,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>36</v>
       </c>
@@ -14094,12 +14091,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -14108,7 +14105,7 @@
         <v>2.5848896936811527E-2</v>
       </c>
       <c r="C1">
-        <f t="shared" ref="C1:K1" si="0">_xlfn.STDEV.S(C4:C39)/SQRT(COUNT(C4:C39))</f>
+        <f t="shared" ref="C1:H1" si="0">_xlfn.STDEV.S(C4:C39)/SQRT(COUNT(C4:C39))</f>
         <v>2.1432894191151058E-2</v>
       </c>
       <c r="D1">
@@ -14136,7 +14133,7 @@
         <v>1.4794192860515082E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -14145,7 +14142,7 @@
         <v>0.31448069643187493</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:J2" si="2">100*C1/AVERAGE(C4:C39)</f>
+        <f t="shared" ref="C2:H2" si="2">100*C1/AVERAGE(C4:C39)</f>
         <v>0.116432955776871</v>
       </c>
       <c r="D2">
@@ -14173,7 +14170,7 @@
         <v>0.1090690310547095</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -14204,7 +14201,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1</v>
       </c>
@@ -14235,7 +14232,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>2</v>
       </c>
@@ -14266,7 +14263,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>3</v>
       </c>
@@ -14297,7 +14294,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>4</v>
       </c>
@@ -14328,7 +14325,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>5</v>
       </c>
@@ -14359,7 +14356,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>6</v>
       </c>
@@ -14386,7 +14383,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>7</v>
       </c>
@@ -14411,7 +14408,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>8</v>
       </c>
@@ -14434,7 +14431,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>9</v>
       </c>
@@ -14457,7 +14454,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>10</v>
       </c>
@@ -14480,7 +14477,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>11</v>
       </c>
@@ -14503,7 +14500,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>12</v>
       </c>
@@ -14526,7 +14523,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>13</v>
       </c>
@@ -14549,7 +14546,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>14</v>
       </c>
@@ -14572,7 +14569,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>15</v>
       </c>
@@ -14595,7 +14592,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>16</v>
       </c>
@@ -14617,7 +14614,7 @@
         <v>13.5963637628518</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>17</v>
       </c>
@@ -14639,7 +14636,7 @@
         <v>13.6061621269385</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>18</v>
       </c>
@@ -14661,7 +14658,7 @@
         <v>13.564508484015001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>19</v>
       </c>
@@ -14681,7 +14678,7 @@
         <v>13.566012885219999</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>20</v>
       </c>
@@ -14701,7 +14698,7 @@
         <v>13.677050331463599</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>21</v>
       </c>
@@ -14720,7 +14717,7 @@
         <v>13.697864550150999</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>22</v>
       </c>
@@ -14739,7 +14736,7 @@
         <v>13.521765815989101</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>23</v>
       </c>
@@ -14758,7 +14755,7 @@
         <v>13.5769688965988</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>24</v>
       </c>
@@ -14777,7 +14774,7 @@
         <v>13.480301532390399</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>25</v>
       </c>
@@ -14796,7 +14793,7 @@
         <v>13.457843174234499</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>26</v>
       </c>
@@ -14812,7 +14809,7 @@
         <v>13.4601858284096</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>27</v>
       </c>
@@ -14828,7 +14825,7 @@
         <v>13.441398970797801</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>28</v>
       </c>
@@ -14844,7 +14841,7 @@
         <v>13.4597843604533</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>29</v>
       </c>
@@ -14860,7 +14857,7 @@
         <v>13.5606966844732</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>30</v>
       </c>
@@ -14876,7 +14873,7 @@
         <v>13.566424750775999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>31</v>
       </c>
@@ -14892,7 +14889,7 @@
         <v>13.677756444678201</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>32</v>
       </c>
@@ -14905,7 +14902,7 @@
         <v>13.7089668474497</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>33</v>
       </c>
@@ -14914,7 +14911,7 @@
         <v>13.5896342791272</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>34</v>
       </c>
@@ -14923,7 +14920,7 @@
         <v>13.672859971194899</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>35</v>
       </c>
@@ -14932,7 +14929,7 @@
         <v>13.4234538610926</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>36</v>
       </c>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfw\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC282DF3-576D-4027-BB26-43B9829CDE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216C52B0-6B66-42F4-B625-F660FE9A39F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2206,7 +2209,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2214,6 +2216,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4651,7 +4654,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4659,6 +4661,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5155,7 +5158,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5163,6 +5165,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7600,7 +7603,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7608,6 +7610,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8101,7 +8104,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8109,6 +8111,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10933,10 +10936,10 @@
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>319087</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>428625</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11382,9 +11385,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
   <dimension ref="A1:N160"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11416,7 +11419,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -11458,7 +11461,7 @@
         <v>2.4909699122220328E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -11500,7 +11503,7 @@
         <v>3.9061146219856075E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -11511,7 +11514,7 @@
         <v>0.13701539714226199</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -11522,7 +11525,7 @@
         <v>0.13611960900852699</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -11533,7 +11536,7 @@
         <v>0.13627945937632699</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -11544,7 +11547,7 @@
         <v>0.30390235043574698</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -11555,7 +11558,7 @@
         <v>0.30438419283964002</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -11566,7 +11569,7 @@
         <v>0.297161130585052</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -11577,7 +11580,7 @@
         <v>0.30092447877826201</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -11588,7 +11591,7 @@
         <v>0.30225556251139701</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -11599,7 +11602,7 @@
         <v>0.30453505035585898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -11610,7 +11613,7 @@
         <v>0.29441937543381203</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -11621,7 +11624,7 @@
         <v>0.29938049893952201</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -11632,7 +11635,7 @@
         <v>0.30198767465833298</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -11643,7 +11646,7 @@
         <v>0.29452133244947898</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -11654,7 +11657,7 @@
         <v>0.30226636207287</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -11665,7 +11668,7 @@
         <v>0.30276185184620003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -11676,7 +11679,7 @@
         <v>0.30565983998385898</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -11687,7 +11690,7 @@
         <v>0.30235700258888798</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -11698,7 +11701,7 @@
         <v>0.30470031507930101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -11709,7 +11712,7 @@
         <v>0.30681032275950298</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -11720,7 +11723,7 @@
         <v>0.31003085423784599</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -11731,7 +11734,7 @@
         <v>0.30130891367381502</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -11742,7 +11745,7 @@
         <v>0.141175020925183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -11753,7 +11756,7 @@
         <v>0.13910706901585701</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -11764,7 +11767,7 @@
         <v>0.14173595580689399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -11775,7 +11778,7 @@
         <v>0.141258173819516</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
@@ -11786,7 +11789,7 @@
         <v>0.142207734258748</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -11797,7 +11800,7 @@
         <v>0.13801119003128501</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -11808,7 +11811,7 @@
         <v>0.14302506923553299</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -11819,7 +11822,7 @@
         <v>0.171876620266287</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -11830,7 +11833,7 @@
         <v>0.17507983789020901</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -11841,7 +11844,7 @@
         <v>0.17353748848485201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -11852,7 +11855,7 @@
         <v>0.17399520336378199</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -11863,7 +11866,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -11874,7 +11877,7 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -11885,7 +11888,7 @@
         <v>0.17111359499762699</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -11896,7 +11899,7 @@
         <v>0.174442312499583</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -11907,7 +11910,7 @@
         <v>0.17165345419397299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -11918,7 +11921,7 @@
         <v>0.17188594050678699</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -11929,7 +11932,7 @@
         <v>0.17182639857690499</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -11940,7 +11943,7 @@
         <v>0.173011271970926</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -11951,7 +11954,7 @@
         <v>0.173393882992014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -11962,7 +11965,7 @@
         <v>0.17255170638235601</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -11973,7 +11976,7 @@
         <v>0.176156057962948</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -11984,7 +11987,7 @@
         <v>0.17277891898827699</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -11995,7 +11998,7 @@
         <v>0.173614948750792</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -12006,7 +12009,7 @@
         <v>0.17607067167010601</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -12017,7 +12020,7 @@
         <v>0.17040120856414201</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -12028,7 +12031,7 @@
         <v>0.17423160269966501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -12039,7 +12042,7 @@
         <v>0.174369956316375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -12050,7 +12053,7 @@
         <v>0.17111424613243301</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -12061,7 +12064,7 @@
         <v>0.174141819699693</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -12072,7 +12075,7 @@
         <v>0.17027613633024699</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -12083,7 +12086,7 @@
         <v>0.17305899861083601</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -12094,7 +12097,7 @@
         <v>0.169629744786672</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -12105,7 +12108,7 @@
         <v>0.17362236751906199</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -12116,7 +12119,7 @@
         <v>0.17378947989454699</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -12127,7 +12130,7 @@
         <v>0.17301730214639</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -12138,7 +12141,7 @@
         <v>0.17294290042990301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -12149,7 +12152,7 @@
         <v>0.17314296764265499</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -12160,7 +12163,7 @@
         <v>0.26702709086345899</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -12171,7 +12174,7 @@
         <v>0.26377604366503299</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -12182,7 +12185,7 @@
         <v>0.26272554597887199</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -12193,7 +12196,7 @@
         <v>0.26788317969509901</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -12204,7 +12207,7 @@
         <v>0.26503400399869398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -12215,7 +12218,7 @@
         <v>0.26673897966627602</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -12226,7 +12229,7 @@
         <v>0.26807575946030698</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -12237,7 +12240,7 @@
         <v>0.266570039729353</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -12248,7 +12251,7 @@
         <v>0.27166172606546901</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -12259,7 +12262,7 @@
         <v>0.26522605962651602</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -12270,7 +12273,7 @@
         <v>0.27094063293660098</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -12281,7 +12284,7 @@
         <v>0.26838563360762802</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -12292,7 +12295,7 @@
         <v>0.26226006746867903</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -12303,7 +12306,7 @@
         <v>0.26283415625491802</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -12314,7 +12317,7 @@
         <v>0.265891536409124</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -12325,7 +12328,7 @@
         <v>0.26086999753535101</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -12336,7 +12339,7 @@
         <v>0.264030412441006</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -12347,7 +12350,7 @@
         <v>0.26104421609513101</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -12358,7 +12361,7 @@
         <v>0.26790761730572898</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -12369,7 +12372,7 @@
         <v>0.26200964452208297</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -12380,7 +12383,7 @@
         <v>0.26657014430711701</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>90</v>
       </c>
@@ -12391,7 +12394,7 @@
         <v>0.264335730958146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>91</v>
       </c>
@@ -12402,7 +12405,7 @@
         <v>0.26876048744697101</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>92</v>
       </c>
@@ -12413,7 +12416,7 @@
         <v>0.26514897700620299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>93</v>
       </c>
@@ -12424,7 +12427,7 @@
         <v>0.26219390887345601</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>94</v>
       </c>
@@ -12435,7 +12438,7 @@
         <v>0.26184487099436499</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>95</v>
       </c>
@@ -12446,7 +12449,7 @@
         <v>0.26409583467590397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>96</v>
       </c>
@@ -12457,7 +12460,7 @@
         <v>0.26424448419416702</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>97</v>
       </c>
@@ -12468,7 +12471,7 @@
         <v>0.26363414452799</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>98</v>
       </c>
@@ -12479,7 +12482,7 @@
         <v>0.26464837628465498</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>99</v>
       </c>
@@ -12490,7 +12493,7 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>107</v>
       </c>
@@ -12501,7 +12504,7 @@
         <v>0.23820566920665201</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>108</v>
       </c>
@@ -12512,7 +12515,7 @@
         <v>0.23716854436609899</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>109</v>
       </c>
@@ -12523,7 +12526,7 @@
         <v>0.24334889035587701</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>110</v>
       </c>
@@ -12534,7 +12537,7 @@
         <v>0.24139693907330401</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>111</v>
       </c>
@@ -12545,7 +12548,7 @@
         <v>0.24177140642297701</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>112</v>
       </c>
@@ -12556,7 +12559,7 @@
         <v>0.24611015618375001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>113</v>
       </c>
@@ -12567,7 +12570,7 @@
         <v>0.24482638982888399</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>114</v>
       </c>
@@ -12578,7 +12581,7 @@
         <v>0.24047022478348701</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>115</v>
       </c>
@@ -12589,7 +12592,7 @@
         <v>0.24076714972723101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>116</v>
       </c>
@@ -12600,7 +12603,7 @@
         <v>0.244370206125226</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>117</v>
       </c>
@@ -12611,7 +12614,7 @@
         <v>0.24313993631303599</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
@@ -12622,7 +12625,7 @@
         <v>0.240076934656237</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
@@ -12633,7 +12636,7 @@
         <v>0.242245334794052</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -12644,7 +12647,7 @@
         <v>0.24081642222489599</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -12655,7 +12658,7 @@
         <v>0.23946128860629701</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>122</v>
       </c>
@@ -12666,7 +12669,7 @@
         <v>0.24067136591591201</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -12677,7 +12680,7 @@
         <v>0.241804540636641</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -12688,7 +12691,7 @@
         <v>0.237876942608618</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -12699,7 +12702,7 @@
         <v>0.241838145831969</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>126</v>
       </c>
@@ -12710,7 +12713,7 @@
         <v>0.24402502768845699</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>127</v>
       </c>
@@ -12721,7 +12724,7 @@
         <v>0.23989744417664499</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>128</v>
       </c>
@@ -12732,7 +12735,7 @@
         <v>0.240176182150968</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>129</v>
       </c>
@@ -12743,7 +12746,7 @@
         <v>0.238939795428251</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -12754,7 +12757,7 @@
         <v>0.23962573892411401</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -12765,7 +12768,7 @@
         <v>0.24176111907040099</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>132</v>
       </c>
@@ -12776,7 +12779,7 @@
         <v>0.24348653683848701</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>133</v>
       </c>
@@ -12787,7 +12790,7 @@
         <v>0.24073031648363399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>134</v>
       </c>
@@ -12798,7 +12801,7 @@
         <v>0.24558776594854301</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>135</v>
       </c>
@@ -12809,7 +12812,7 @@
         <v>0.239185337596831</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>136</v>
       </c>
@@ -12820,7 +12823,7 @@
         <v>0.241717931493385</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>137</v>
       </c>
@@ -12831,7 +12834,7 @@
         <v>0.24138266998260599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>138</v>
       </c>
@@ -12842,7 +12845,7 @@
         <v>0.24367652321245201</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>139</v>
       </c>
@@ -12853,7 +12856,7 @@
         <v>0.22233607124480101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>140</v>
       </c>
@@ -12864,7 +12867,7 @@
         <v>0.222916111013889</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>141</v>
       </c>
@@ -12875,7 +12878,7 @@
         <v>0.21978080516705001</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>142</v>
       </c>
@@ -12886,7 +12889,7 @@
         <v>0.21701744510815299</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>143</v>
       </c>
@@ -12897,7 +12900,7 @@
         <v>0.22292724198768199</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
@@ -12908,7 +12911,7 @@
         <v>0.222109442813166</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>145</v>
       </c>
@@ -12919,7 +12922,7 @@
         <v>0.221905259897859</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>146</v>
       </c>
@@ -12930,7 +12933,7 @@
         <v>0.21899661326540701</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>147</v>
       </c>
@@ -12941,7 +12944,7 @@
         <v>0.21885786728813</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -12952,7 +12955,7 @@
         <v>0.21579488523700499</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -12963,7 +12966,7 @@
         <v>0.220755926487161</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>150</v>
       </c>
@@ -12974,7 +12977,7 @@
         <v>0.22011228616490899</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>151</v>
       </c>
@@ -12985,7 +12988,7 @@
         <v>0.21961259407713499</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>152</v>
       </c>
@@ -12996,7 +12999,7 @@
         <v>0.22007796981835101</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -13007,7 +13010,7 @@
         <v>0.21807344865282799</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>154</v>
       </c>
@@ -13018,7 +13021,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
@@ -13029,7 +13032,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>156</v>
       </c>
@@ -13040,7 +13043,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>157</v>
       </c>
@@ -13051,7 +13054,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>158</v>
       </c>
@@ -13062,7 +13065,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>159</v>
       </c>
@@ -13073,7 +13076,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>160</v>
       </c>
@@ -13084,7 +13087,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>161</v>
       </c>
@@ -13095,7 +13098,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>162</v>
       </c>
@@ -13106,7 +13109,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>163</v>
       </c>
@@ -13117,7 +13120,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>164</v>
       </c>
@@ -13128,7 +13131,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>165</v>
       </c>
@@ -13139,7 +13142,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>166</v>
       </c>
@@ -13150,7 +13153,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -13161,7 +13164,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>168</v>
       </c>
@@ -13172,7 +13175,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>169</v>
       </c>
@@ -13183,7 +13186,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>170</v>
       </c>
@@ -13194,7 +13197,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>171</v>
       </c>
@@ -13205,7 +13208,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>172</v>
       </c>
@@ -13216,7 +13219,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>173</v>
       </c>
@@ -13236,13 +13239,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="11.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>2.8613971962500952E-4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -13316,7 +13319,7 @@
         <v>0.12997532261023939</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -13347,7 +13350,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -13378,7 +13381,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -13409,7 +13412,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -13440,7 +13443,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -13471,7 +13474,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -13502,7 +13505,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -13529,7 +13532,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -13554,7 +13557,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -13577,7 +13580,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -13600,7 +13603,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -13623,7 +13626,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -13646,7 +13649,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -13669,7 +13672,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -13692,7 +13695,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -13715,7 +13718,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -13738,7 +13741,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -13760,7 +13763,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -13782,7 +13785,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -13804,7 +13807,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -13824,7 +13827,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -13844,7 +13847,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -13863,7 +13866,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -13882,7 +13885,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -13901,7 +13904,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -13920,7 +13923,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -13939,7 +13942,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -13955,7 +13958,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -13971,7 +13974,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -13987,7 +13990,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -14003,7 +14006,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -14019,7 +14022,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -14035,7 +14038,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -14048,7 +14051,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -14057,7 +14060,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -14066,7 +14069,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -14075,7 +14078,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -14091,12 +14094,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.68359375" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -14133,7 +14136,7 @@
         <v>1.4794192860515082E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -14170,7 +14173,7 @@
         <v>0.1090690310547095</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -14201,7 +14204,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -14232,7 +14235,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -14263,7 +14266,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -14294,7 +14297,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -14325,7 +14328,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -14356,7 +14359,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -14383,7 +14386,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -14408,7 +14411,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -14431,7 +14434,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -14454,7 +14457,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -14477,7 +14480,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -14500,7 +14503,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -14523,7 +14526,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -14546,7 +14549,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -14569,7 +14572,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -14592,7 +14595,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -14614,7 +14617,7 @@
         <v>13.5963637628518</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -14636,7 +14639,7 @@
         <v>13.6061621269385</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -14658,7 +14661,7 @@
         <v>13.564508484015001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -14678,7 +14681,7 @@
         <v>13.566012885219999</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -14698,7 +14701,7 @@
         <v>13.677050331463599</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -14717,7 +14720,7 @@
         <v>13.697864550150999</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -14736,7 +14739,7 @@
         <v>13.521765815989101</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -14755,7 +14758,7 @@
         <v>13.5769688965988</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -14774,7 +14777,7 @@
         <v>13.480301532390399</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -14793,7 +14796,7 @@
         <v>13.457843174234499</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -14809,7 +14812,7 @@
         <v>13.4601858284096</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -14825,7 +14828,7 @@
         <v>13.441398970797801</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -14841,7 +14844,7 @@
         <v>13.4597843604533</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -14857,7 +14860,7 @@
         <v>13.5606966844732</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -14873,7 +14876,7 @@
         <v>13.566424750775999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -14889,7 +14892,7 @@
         <v>13.677756444678201</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -14902,7 +14905,7 @@
         <v>13.7089668474497</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -14911,7 +14914,7 @@
         <v>13.5896342791272</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -14920,7 +14923,7 @@
         <v>13.672859971194899</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -14929,7 +14932,7 @@
         <v>13.4234538610926</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216C52B0-6B66-42F4-B625-F660FE9A39F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89841AF0-08A6-45CF-91EC-016C82C56019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="243">
   <si>
     <t>Date</t>
   </si>
@@ -564,6 +564,210 @@
   </si>
   <si>
     <t>Jul7,2026</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-04-19PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-13-04PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-23-13PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-33-05PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-45-35PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-28-32PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-38-22PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-48-06PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-56-02PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-06-11PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-15-37PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-24-59PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-35-16PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-43-10PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-55-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-03-23PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-11-24PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-19-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-27-25PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-36-17PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-44-12PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-52-06PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-00-09PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-08-00PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-16-03PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-25-55PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-34-13PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-42-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-55-05PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-02-57PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-10-49PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-18-47PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-26-36AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-36-23AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-47-02AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-01-15AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-09-20AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-17-22AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-25-55AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-43-59AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-51-58AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-08-01PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-16-09PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-24-11PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-36-13PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-44-32PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-52-26PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-01-10PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-09-54PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-18-10PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-32-09PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-44-19PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-55-45PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-03-45PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-11-46PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-22-27PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-30-42PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-40-05PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-48-12PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-56-12PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-04-17PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-15-03PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-25-49PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-38-53PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-46-49PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-54-43PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+4-02-42PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+4-10-46PM</t>
   </si>
 </sst>
 </file>
@@ -2030,6 +2234,528 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-86B6-4279-B582-2279D2E3FD28}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>8-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$161:$B$192</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2.07892749786477</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0663834161140699</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0628293519735901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.07368391485078</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1039341660075501</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0673577404721302</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0619952490668201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.05981399507903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0609859200885801</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.0594671215384501</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.07614752547159</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0785120893459799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.0891336228459898</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.0903682617926802</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.10180294618258</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.1021592068839001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1003895957887599</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.0968436651486999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.0879161684316299</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.0889443536633001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.0788690207312501</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.0777810140456099</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.0773479287857999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0750460102786898</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.07579422159953</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.0691590991764399</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.0830929433282899</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.0711249818440698</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.0663816479454802</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.0640815890017499</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.0662267195881898</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.0714341542752299</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$161:$C$192</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>3.30028948262861E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3489889357849002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.34050697248311E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3663016244114899E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3862208744561598E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3371230140689601E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.3958687307630298E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.3717539743101703E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4019624541611997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.30325465399912E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.3342495220022902E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.3765726933882197E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.3827431022495302E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.2562436603975398E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.3936476228758998E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3445511192293297E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.3061817051389601E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.35542069970673E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.4176849718869903E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.3607525034085699E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.3291217503168297E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3587626783338299E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.3498059501305001E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.3612378265113999E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.36767838831264E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.4205246508627503E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.33159042246957E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.4310317322257401E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.4082317162395397E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.3309537312556703E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.2808961198641698E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.3324024754485697E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A036-4546-BBC9-4080821F7EE7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>9-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$193:$B$228</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>2.5011187965916499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5056585895299199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.48638142466051</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4855190794760902</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5074216201399602</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4877440696740298</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4798485643611698</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5040935191620002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5154540630727702</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.5215314979177399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5255084560658201</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.5217723144817001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5063570266102602</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.5171411510981598</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.5186758172382802</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.54554864229272</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.54463980757486</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.5166341388295401</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.52355147173308</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.5237166224547098</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5134774644318001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.52756872312878</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.51132793852284</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5199495004271499</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.5099318931845498</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.5170794909418999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.5205441270179501</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.5256694865405498</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.5268785167168302</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.5179187778053098</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5003481091105</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.5011416069930501</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.49799819651472</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.5008140111194899</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.4996354690281701</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.4937831454353199</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$193:$C$228</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>4.0620494830716898E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0445250720025597E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0191516108636097E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0970033814296203E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.04373053253217E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0649065132095999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.9533611139950402E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0155853483306803E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0445594269577098E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.9604033537862203E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.0174033834531497E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.1231746357817303E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0336571538600499E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.0359240284840503E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.0249713225980401E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.0520690948023297E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.02329856985481E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.0144847093634903E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.0409209035940002E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.10395989464786E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.98714030158333E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.98908146812504E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.0524916971605499E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.0390455654384101E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.1071400769317298E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.0178381373720602E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.0702941996408802E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.01385052767382E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.0018008651341898E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.9989666024372497E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.0322645046764097E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.0532664600090897E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.06963104125408E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.1172181601451197E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.9836921294789503E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.0347554180400501E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A036-4546-BBC9-4080821F7EE7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11384,7 +12110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -13228,6 +13954,754 @@
       </c>
       <c r="C160" s="1">
         <v>0.22158291221496201</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B161" s="1">
+        <v>2.07892749786477</v>
+      </c>
+      <c r="C161" s="1">
+        <v>3.30028948262861E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B162" s="1">
+        <v>2.0663834161140699</v>
+      </c>
+      <c r="C162" s="1">
+        <v>3.3489889357849002E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B163" s="1">
+        <v>2.0628293519735901</v>
+      </c>
+      <c r="C163" s="1">
+        <v>3.34050697248311E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B164" s="1">
+        <v>2.07368391485078</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3.3663016244114899E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B165" s="1">
+        <v>2.1039341660075501</v>
+      </c>
+      <c r="C165" s="1">
+        <v>3.3862208744561598E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B166" s="1">
+        <v>2.0673577404721302</v>
+      </c>
+      <c r="C166" s="1">
+        <v>3.3371230140689601E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B167" s="1">
+        <v>2.0619952490668201</v>
+      </c>
+      <c r="C167" s="1">
+        <v>3.3958687307630298E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B168" s="1">
+        <v>2.05981399507903</v>
+      </c>
+      <c r="C168" s="1">
+        <v>3.3717539743101703E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B169" s="1">
+        <v>2.0609859200885801</v>
+      </c>
+      <c r="C169" s="1">
+        <v>3.4019624541611997E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B170" s="1">
+        <v>2.0594671215384501</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3.30325465399912E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B171" s="1">
+        <v>2.07614752547159</v>
+      </c>
+      <c r="C171" s="1">
+        <v>3.3342495220022902E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B172" s="1">
+        <v>2.0785120893459799</v>
+      </c>
+      <c r="C172" s="1">
+        <v>3.3765726933882197E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B173" s="1">
+        <v>2.0891336228459898</v>
+      </c>
+      <c r="C173" s="1">
+        <v>3.3827431022495302E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B174" s="1">
+        <v>2.0903682617926802</v>
+      </c>
+      <c r="C174" s="1">
+        <v>3.2562436603975398E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B175" s="1">
+        <v>2.10180294618258</v>
+      </c>
+      <c r="C175" s="1">
+        <v>3.3936476228758998E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B176" s="1">
+        <v>2.1021592068839001</v>
+      </c>
+      <c r="C176" s="1">
+        <v>3.3445511192293297E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B177" s="1">
+        <v>2.1003895957887599</v>
+      </c>
+      <c r="C177" s="1">
+        <v>3.3061817051389601E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B178" s="1">
+        <v>2.0968436651486999</v>
+      </c>
+      <c r="C178" s="1">
+        <v>3.35542069970673E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B179" s="1">
+        <v>2.0879161684316299</v>
+      </c>
+      <c r="C179" s="1">
+        <v>3.4176849718869903E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B180" s="1">
+        <v>2.0889443536633001</v>
+      </c>
+      <c r="C180" s="1">
+        <v>3.3607525034085699E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B181" s="1">
+        <v>2.0788690207312501</v>
+      </c>
+      <c r="C181" s="1">
+        <v>3.3291217503168297E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B182" s="1">
+        <v>2.0777810140456099</v>
+      </c>
+      <c r="C182" s="1">
+        <v>3.3587626783338299E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B183" s="1">
+        <v>2.0773479287857999</v>
+      </c>
+      <c r="C183" s="1">
+        <v>3.3498059501305001E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B184" s="1">
+        <v>2.0750460102786898</v>
+      </c>
+      <c r="C184" s="1">
+        <v>3.3612378265113999E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B185" s="1">
+        <v>2.07579422159953</v>
+      </c>
+      <c r="C185" s="1">
+        <v>3.36767838831264E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B186" s="1">
+        <v>2.0691590991764399</v>
+      </c>
+      <c r="C186" s="1">
+        <v>3.4205246508627503E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B187" s="1">
+        <v>2.0830929433282899</v>
+      </c>
+      <c r="C187" s="1">
+        <v>3.33159042246957E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B188" s="1">
+        <v>2.0711249818440698</v>
+      </c>
+      <c r="C188" s="1">
+        <v>3.4310317322257401E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B189" s="1">
+        <v>2.0663816479454802</v>
+      </c>
+      <c r="C189" s="1">
+        <v>3.4082317162395397E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B190" s="1">
+        <v>2.0640815890017499</v>
+      </c>
+      <c r="C190" s="1">
+        <v>3.3309537312556703E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191" s="1">
+        <v>2.0662267195881898</v>
+      </c>
+      <c r="C191" s="1">
+        <v>3.2808961198641698E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" s="1">
+        <v>2.0714341542752299</v>
+      </c>
+      <c r="C192" s="1">
+        <v>3.3324024754485697E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B193" s="1">
+        <v>2.5011187965916499</v>
+      </c>
+      <c r="C193" s="1">
+        <v>4.0620494830716898E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B194" s="1">
+        <v>2.5056585895299199</v>
+      </c>
+      <c r="C194" s="1">
+        <v>4.0445250720025597E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B195" s="1">
+        <v>2.48638142466051</v>
+      </c>
+      <c r="C195" s="1">
+        <v>4.0191516108636097E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B196" s="1">
+        <v>2.4855190794760902</v>
+      </c>
+      <c r="C196" s="1">
+        <v>4.0970033814296203E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B197" s="1">
+        <v>2.5074216201399602</v>
+      </c>
+      <c r="C197" s="1">
+        <v>4.04373053253217E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B198" s="1">
+        <v>2.4877440696740298</v>
+      </c>
+      <c r="C198" s="1">
+        <v>4.0649065132095999E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B199" s="1">
+        <v>2.4798485643611698</v>
+      </c>
+      <c r="C199" s="1">
+        <v>3.9533611139950402E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B200" s="1">
+        <v>2.5040935191620002</v>
+      </c>
+      <c r="C200" s="1">
+        <v>4.0155853483306803E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B201" s="1">
+        <v>2.5154540630727702</v>
+      </c>
+      <c r="C201" s="1">
+        <v>4.0445594269577098E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B202" s="1">
+        <v>2.5215314979177399</v>
+      </c>
+      <c r="C202" s="1">
+        <v>3.9604033537862203E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B203" s="1">
+        <v>2.5255084560658201</v>
+      </c>
+      <c r="C203" s="1">
+        <v>4.0174033834531497E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B204" s="1">
+        <v>2.5217723144817001</v>
+      </c>
+      <c r="C204" s="1">
+        <v>4.1231746357817303E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B205" s="1">
+        <v>2.5063570266102602</v>
+      </c>
+      <c r="C205" s="1">
+        <v>4.0336571538600499E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B206" s="1">
+        <v>2.5171411510981598</v>
+      </c>
+      <c r="C206" s="1">
+        <v>4.0359240284840503E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B207" s="1">
+        <v>2.5186758172382802</v>
+      </c>
+      <c r="C207" s="1">
+        <v>4.0249713225980401E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B208" s="1">
+        <v>2.54554864229272</v>
+      </c>
+      <c r="C208" s="1">
+        <v>4.0520690948023297E-2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B209" s="1">
+        <v>2.54463980757486</v>
+      </c>
+      <c r="C209" s="1">
+        <v>4.02329856985481E-2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B210" s="1">
+        <v>2.5166341388295401</v>
+      </c>
+      <c r="C210" s="1">
+        <v>4.0144847093634903E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B211" s="1">
+        <v>2.52355147173308</v>
+      </c>
+      <c r="C211" s="1">
+        <v>4.0409209035940002E-2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B212" s="1">
+        <v>2.5237166224547098</v>
+      </c>
+      <c r="C212" s="1">
+        <v>4.10395989464786E-2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B213" s="1">
+        <v>2.5134774644318001</v>
+      </c>
+      <c r="C213" s="1">
+        <v>3.98714030158333E-2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B214" s="1">
+        <v>2.52756872312878</v>
+      </c>
+      <c r="C214" s="1">
+        <v>3.98908146812504E-2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B215" s="1">
+        <v>2.51132793852284</v>
+      </c>
+      <c r="C215" s="1">
+        <v>4.0524916971605499E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B216" s="1">
+        <v>2.5199495004271499</v>
+      </c>
+      <c r="C216" s="1">
+        <v>4.0390455654384101E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B217" s="1">
+        <v>2.5099318931845498</v>
+      </c>
+      <c r="C217" s="1">
+        <v>4.1071400769317298E-2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B218" s="1">
+        <v>2.5170794909418999</v>
+      </c>
+      <c r="C218" s="1">
+        <v>4.0178381373720602E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B219" s="1">
+        <v>2.5205441270179501</v>
+      </c>
+      <c r="C219" s="1">
+        <v>4.0702941996408802E-2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B220" s="1">
+        <v>2.5256694865405498</v>
+      </c>
+      <c r="C220" s="1">
+        <v>4.01385052767382E-2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B221" s="1">
+        <v>2.5268785167168302</v>
+      </c>
+      <c r="C221" s="1">
+        <v>4.0018008651341898E-2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B222" s="1">
+        <v>2.5179187778053098</v>
+      </c>
+      <c r="C222" s="1">
+        <v>3.9989666024372497E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B223" s="1">
+        <v>2.5003481091105</v>
+      </c>
+      <c r="C223" s="1">
+        <v>4.0322645046764097E-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B224" s="1">
+        <v>2.5011416069930501</v>
+      </c>
+      <c r="C224" s="1">
+        <v>4.0532664600090897E-2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B225" s="1">
+        <v>2.49799819651472</v>
+      </c>
+      <c r="C225" s="1">
+        <v>4.06963104125408E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B226" s="1">
+        <v>2.5008140111194899</v>
+      </c>
+      <c r="C226" s="1">
+        <v>4.1172181601451197E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B227" s="1">
+        <v>2.4996354690281701</v>
+      </c>
+      <c r="C227" s="1">
+        <v>3.9836921294789503E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B228" s="1">
+        <v>2.4937831454353199</v>
+      </c>
+      <c r="C228" s="1">
+        <v>4.0347554180400501E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89841AF0-08A6-45CF-91EC-016C82C56019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00EAA6A-9BD9-4982-81BC-A7E07BF818FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00EAA6A-9BD9-4982-81BC-A7E07BF818FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9689E346-71C4-448B-B7D6-BFE2F6FAAC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="243">
-  <si>
-    <t>Date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="240">
   <si>
     <t>May22,2026+11-50-22AM</t>
   </si>
@@ -132,12 +129,6 @@
   </si>
   <si>
     <t>May29,2026+12-51-01PM</t>
-  </si>
-  <si>
-    <t>Alpha 456</t>
-  </si>
-  <si>
-    <t>Alpha 894</t>
   </si>
   <si>
     <t>Number</t>
@@ -11656,16 +11647,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>428625</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12114,40 +12105,34 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
       <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>8.1314875900026795</v>
@@ -12156,7 +12141,7 @@
         <v>0.13284709830915301</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <f>'894'!B1</f>
@@ -12189,7 +12174,7 @@
     </row>
     <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>8.2055994032900799</v>
@@ -12198,7 +12183,7 @@
         <v>0.13179599174591999</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H3">
         <f>'456'!B1</f>
@@ -12231,7 +12216,7 @@
     </row>
     <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>8.2176590050244904</v>
@@ -12242,7 +12227,7 @@
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>8.2690216688035498</v>
@@ -12253,7 +12238,7 @@
     </row>
     <row r="6" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>8.2739805096279504</v>
@@ -12264,7 +12249,7 @@
     </row>
     <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>18.481531830496198</v>
@@ -12275,7 +12260,7 @@
     </row>
     <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>18.346083770183299</v>
@@ -12286,7 +12271,7 @@
     </row>
     <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>18.452491695077299</v>
@@ -12297,7 +12282,7 @@
     </row>
     <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>18.351915434355199</v>
@@ -12308,7 +12293,7 @@
     </row>
     <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>18.337397032620899</v>
@@ -12319,7 +12304,7 @@
     </row>
     <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>18.232394257417202</v>
@@ -12330,7 +12315,7 @@
     </row>
     <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>18.415074041865601</v>
@@ -12341,7 +12326,7 @@
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>18.341941017083698</v>
@@ -12352,7 +12337,7 @@
     </row>
     <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>18.237027996635099</v>
@@ -12363,7 +12348,7 @@
     </row>
     <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>18.531243546545401</v>
@@ -12374,7 +12359,7 @@
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>18.412716855394802</v>
@@ -12385,7 +12370,7 @@
     </row>
     <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>18.4923898758226</v>
@@ -12396,7 +12381,7 @@
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1">
         <v>18.515382021503999</v>
@@ -12407,7 +12392,7 @@
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>18.391192672959299</v>
@@ -12418,7 +12403,7 @@
     </row>
     <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
         <v>18.551612310419799</v>
@@ -12429,7 +12414,7 @@
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>18.393990200449998</v>
@@ -12440,7 +12425,7 @@
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>18.450034969079201</v>
@@ -12451,7 +12436,7 @@
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>18.408277105199002</v>
@@ -12462,7 +12447,7 @@
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1">
         <v>8.5701060942568006</v>
@@ -12473,7 +12458,7 @@
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="1">
         <v>8.5447049809269604</v>
@@ -12484,7 +12469,7 @@
     </row>
     <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1">
         <v>8.4017872832855591</v>
@@ -12495,7 +12480,7 @@
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1">
         <v>8.4035403242380404</v>
@@ -12506,7 +12491,7 @@
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="1">
         <v>8.5185527459719204</v>
@@ -12517,7 +12502,7 @@
     </row>
     <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="1">
         <v>8.5260980793629599</v>
@@ -12528,7 +12513,7 @@
     </row>
     <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="1">
         <v>8.4894844505278897</v>
@@ -12539,7 +12524,7 @@
     </row>
     <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B32" s="1">
         <v>10.6221259181231</v>
@@ -12550,7 +12535,7 @@
     </row>
     <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B33" s="1">
         <v>10.735748783007899</v>
@@ -12561,7 +12546,7 @@
     </row>
     <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B34" s="1">
         <v>10.566758158407101</v>
@@ -12572,7 +12557,7 @@
     </row>
     <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B35" s="1">
         <v>10.631078078007899</v>
@@ -12583,7 +12568,7 @@
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1">
         <v>10.634659592750699</v>
@@ -12594,7 +12579,7 @@
     </row>
     <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B37" s="1">
         <v>10.672389702778499</v>
@@ -12605,7 +12590,7 @@
     </row>
     <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B38" s="1">
         <v>10.624260123408201</v>
@@ -12616,7 +12601,7 @@
     </row>
     <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B39" s="1">
         <v>10.518782041710701</v>
@@ -12627,7 +12612,7 @@
     </row>
     <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B40" s="1">
         <v>10.635277697575599</v>
@@ -12638,7 +12623,7 @@
     </row>
     <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B41" s="1">
         <v>10.703364754206801</v>
@@ -12649,7 +12634,7 @@
     </row>
     <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B42" s="1">
         <v>10.6888204197401</v>
@@ -12660,7 +12645,7 @@
     </row>
     <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B43" s="1">
         <v>10.707744909524299</v>
@@ -12671,7 +12656,7 @@
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B44" s="1">
         <v>10.731647561909099</v>
@@ -12682,7 +12667,7 @@
     </row>
     <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B45" s="1">
         <v>10.743488692224201</v>
@@ -12693,7 +12678,7 @@
     </row>
     <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B46" s="1">
         <v>10.7190641789712</v>
@@ -12704,7 +12689,7 @@
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B47" s="1">
         <v>10.7246119730962</v>
@@ -12715,7 +12700,7 @@
     </row>
     <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B48" s="1">
         <v>10.854434693120901</v>
@@ -12726,7 +12711,7 @@
     </row>
     <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B49" s="1">
         <v>10.706374987729699</v>
@@ -12737,7 +12722,7 @@
     </row>
     <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B50" s="1">
         <v>10.637698363317099</v>
@@ -12748,7 +12733,7 @@
     </row>
     <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B51" s="1">
         <v>10.739175433178</v>
@@ -12759,7 +12744,7 @@
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B52" s="1">
         <v>10.686605164880801</v>
@@ -12770,7 +12755,7 @@
     </row>
     <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B53" s="1">
         <v>10.6515045746171</v>
@@ -12781,7 +12766,7 @@
     </row>
     <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B54" s="1">
         <v>10.701321936698699</v>
@@ -12792,7 +12777,7 @@
     </row>
     <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B55" s="1">
         <v>10.605269760878899</v>
@@ -12803,7 +12788,7 @@
     </row>
     <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B56" s="1">
         <v>10.5803727434901</v>
@@ -12814,7 +12799,7 @@
     </row>
     <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B57" s="1">
         <v>10.576268807422901</v>
@@ -12825,7 +12810,7 @@
     </row>
     <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1">
         <v>10.5196221348473</v>
@@ -12836,7 +12821,7 @@
     </row>
     <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B59" s="1">
         <v>10.558405934335401</v>
@@ -12847,7 +12832,7 @@
     </row>
     <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B60" s="1">
         <v>10.633836662036201</v>
@@ -12858,7 +12843,7 @@
     </row>
     <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B61" s="1">
         <v>10.6134173334769</v>
@@ -12869,7 +12854,7 @@
     </row>
     <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B62" s="1">
         <v>10.660587486404401</v>
@@ -12880,7 +12865,7 @@
     </row>
     <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B63" s="1">
         <v>16.4455493987636</v>
@@ -12891,7 +12876,7 @@
     </row>
     <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B64" s="1">
         <v>16.204494346869399</v>
@@ -12902,7 +12887,7 @@
     </row>
     <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B65" s="1">
         <v>16.286326741643599</v>
@@ -12913,7 +12898,7 @@
     </row>
     <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B66" s="1">
         <v>16.207702786854899</v>
@@ -12924,7 +12909,7 @@
     </row>
     <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1">
         <v>16.458700382311001</v>
@@ -12935,7 +12920,7 @@
     </row>
     <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B68" s="1">
         <v>16.462078937325401</v>
@@ -12946,7 +12931,7 @@
     </row>
     <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B69" s="1">
         <v>16.471494559838</v>
@@ -12957,7 +12942,7 @@
     </row>
     <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B70" s="1">
         <v>16.339485818946901</v>
@@ -12968,7 +12953,7 @@
     </row>
     <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B71" s="1">
         <v>16.355055381852601</v>
@@ -12979,7 +12964,7 @@
     </row>
     <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B72" s="1">
         <v>16.3595891765879</v>
@@ -12990,7 +12975,7 @@
     </row>
     <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B73" s="1">
         <v>16.2164791072151</v>
@@ -13001,7 +12986,7 @@
     </row>
     <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B74" s="1">
         <v>16.261548141097599</v>
@@ -13012,7 +12997,7 @@
     </row>
     <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B75" s="1">
         <v>16.384810735183699</v>
@@ -13023,7 +13008,7 @@
     </row>
     <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B76" s="1">
         <v>16.350623841514199</v>
@@ -13034,7 +13019,7 @@
     </row>
     <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B77" s="1">
         <v>16.187723396986499</v>
@@ -13045,7 +13030,7 @@
     </row>
     <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B78" s="1">
         <v>16.3038309514011</v>
@@ -13056,7 +13041,7 @@
     </row>
     <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B79" s="1">
         <v>16.164613922247401</v>
@@ -13067,7 +13052,7 @@
     </row>
     <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B80" s="1">
         <v>16.240097105116</v>
@@ -13078,7 +13063,7 @@
     </row>
     <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B81" s="1">
         <v>16.2518971233978</v>
@@ -13089,7 +13074,7 @@
     </row>
     <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B82" s="1">
         <v>16.381371335960701</v>
@@ -13100,7 +13085,7 @@
     </row>
     <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B83" s="1">
         <v>16.378295734472999</v>
@@ -13111,7 +13096,7 @@
     </row>
     <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B84" s="1">
         <v>16.444871536786899</v>
@@ -13122,7 +13107,7 @@
     </row>
     <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B85" s="1">
         <v>16.377685606618101</v>
@@ -13133,7 +13118,7 @@
     </row>
     <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B86" s="1">
         <v>16.370821349538001</v>
@@ -13144,7 +13129,7 @@
     </row>
     <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B87" s="1">
         <v>16.147989198104199</v>
@@ -13155,7 +13140,7 @@
     </row>
     <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B88" s="1">
         <v>16.418772327555299</v>
@@ -13166,7 +13151,7 @@
     </row>
     <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B89" s="1">
         <v>16.352237501405199</v>
@@ -13177,7 +13162,7 @@
     </row>
     <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B90" s="1">
         <v>16.311710862235199</v>
@@ -13188,7 +13173,7 @@
     </row>
     <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B91" s="1">
         <v>16.368589028451201</v>
@@ -13199,7 +13184,7 @@
     </row>
     <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B92" s="1">
         <v>16.289962255694199</v>
@@ -13210,7 +13195,7 @@
     </row>
     <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B93" s="1">
         <v>16.347944436289598</v>
@@ -13221,7 +13206,7 @@
     </row>
     <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B94" s="1">
         <v>14.758704239534</v>
@@ -13232,7 +13217,7 @@
     </row>
     <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B95" s="1">
         <v>14.484299654433</v>
@@ -13243,7 +13228,7 @@
     </row>
     <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B96" s="1">
         <v>14.9651380437949</v>
@@ -13254,7 +13239,7 @@
     </row>
     <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B97" s="1">
         <v>14.874006519279099</v>
@@ -13265,7 +13250,7 @@
     </row>
     <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B98" s="1">
         <v>14.848372496325201</v>
@@ -13276,7 +13261,7 @@
     </row>
     <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B99" s="1">
         <v>14.899698212446999</v>
@@ -13287,7 +13272,7 @@
     </row>
     <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B100" s="1">
         <v>14.810888493288999</v>
@@ -13298,7 +13283,7 @@
     </row>
     <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B101" s="1">
         <v>14.679244556567999</v>
@@ -13309,7 +13294,7 @@
     </row>
     <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B102" s="1">
         <v>14.738029844308899</v>
@@ -13320,7 +13305,7 @@
     </row>
     <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B103" s="1">
         <v>15.006235992571201</v>
@@ -13331,7 +13316,7 @@
     </row>
     <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B104" s="1">
         <v>14.931755049277101</v>
@@ -13342,7 +13327,7 @@
     </row>
     <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B105" s="1">
         <v>14.877675513746899</v>
@@ -13353,7 +13338,7 @@
     </row>
     <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B106" s="1">
         <v>14.746074117484801</v>
@@ -13364,7 +13349,7 @@
     </row>
     <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B107" s="1">
         <v>14.640937142556799</v>
@@ -13375,7 +13360,7 @@
     </row>
     <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B108" s="1">
         <v>14.631998174448899</v>
@@ -13386,7 +13371,7 @@
     </row>
     <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B109" s="1">
         <v>14.6724748610003</v>
@@ -13397,7 +13382,7 @@
     </row>
     <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B110" s="1">
         <v>14.5414739371093</v>
@@ -13408,7 +13393,7 @@
     </row>
     <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B111" s="1">
         <v>14.8098620908903</v>
@@ -13419,7 +13404,7 @@
     </row>
     <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B112" s="1">
         <v>14.5919542716605</v>
@@ -13430,7 +13415,7 @@
     </row>
     <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B113" s="1">
         <v>14.5587210638217</v>
@@ -13441,7 +13426,7 @@
     </row>
     <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B114" s="1">
         <v>14.659733641213601</v>
@@ -13452,7 +13437,7 @@
     </row>
     <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B115" s="1">
         <v>14.5682516009454</v>
@@ -13463,7 +13448,7 @@
     </row>
     <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B116" s="1">
         <v>14.6781335911072</v>
@@ -13474,7 +13459,7 @@
     </row>
     <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B117" s="1">
         <v>14.6663906133572</v>
@@ -13485,7 +13470,7 @@
     </row>
     <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B118" s="1">
         <v>15.0131194102626</v>
@@ -13496,7 +13481,7 @@
     </row>
     <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B119" s="1">
         <v>14.811961578394801</v>
@@ -13507,7 +13492,7 @@
     </row>
     <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B120" s="1">
         <v>14.838220774801099</v>
@@ -13518,7 +13503,7 @@
     </row>
     <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B121" s="1">
         <v>14.8799215035865</v>
@@ -13529,7 +13514,7 @@
     </row>
     <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B122" s="1">
         <v>14.8939719894331</v>
@@ -13540,7 +13525,7 @@
     </row>
     <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B123" s="1">
         <v>14.7270416756588</v>
@@ -13551,7 +13536,7 @@
     </row>
     <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B124" s="1">
         <v>14.880778969601799</v>
@@ -13562,7 +13547,7 @@
     </row>
     <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B125" s="1">
         <v>14.8237912164245</v>
@@ -13573,7 +13558,7 @@
     </row>
     <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B126" s="1">
         <v>13.5587346114607</v>
@@ -13584,7 +13569,7 @@
     </row>
     <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B127" s="1">
         <v>13.6287894663453</v>
@@ -13595,7 +13580,7 @@
     </row>
     <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B128" s="1">
         <v>13.564281814943399</v>
@@ -13606,7 +13591,7 @@
     </row>
     <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B129" s="1">
         <v>13.588373998833699</v>
@@ -13617,7 +13602,7 @@
     </row>
     <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B130" s="1">
         <v>13.4847013836913</v>
@@ -13628,7 +13613,7 @@
     </row>
     <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B131" s="1">
         <v>13.493443306898801</v>
@@ -13639,7 +13624,7 @@
     </row>
     <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B132" s="1">
         <v>13.693036667407799</v>
@@ -13650,7 +13635,7 @@
     </row>
     <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B133" s="1">
         <v>13.6672309767879</v>
@@ -13661,7 +13646,7 @@
     </row>
     <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B134" s="1">
         <v>13.6270332177755</v>
@@ -13672,7 +13657,7 @@
     </row>
     <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B135" s="1">
         <v>13.5711113836892</v>
@@ -13683,7 +13668,7 @@
     </row>
     <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B136" s="1">
         <v>13.600332344222</v>
@@ -13694,7 +13679,7 @@
     </row>
     <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B137" s="1">
         <v>13.5009743955892</v>
@@ -13705,7 +13690,7 @@
     </row>
     <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B138" s="1">
         <v>13.597133836560999</v>
@@ -13716,7 +13701,7 @@
     </row>
     <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B139" s="1">
         <v>13.345801926629401</v>
@@ -13727,7 +13712,7 @@
     </row>
     <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B140" s="1">
         <v>13.5152469728806</v>
@@ -13738,7 +13723,7 @@
     </row>
     <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B141" s="1">
         <v>13.5963637628518</v>
@@ -13749,7 +13734,7 @@
     </row>
     <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B142" s="1">
         <v>13.6061621269385</v>
@@ -13760,7 +13745,7 @@
     </row>
     <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B143" s="1">
         <v>13.564508484015001</v>
@@ -13771,7 +13756,7 @@
     </row>
     <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B144" s="1">
         <v>13.566012885219999</v>
@@ -13782,7 +13767,7 @@
     </row>
     <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B145" s="1">
         <v>13.677050331463599</v>
@@ -13793,7 +13778,7 @@
     </row>
     <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B146" s="1">
         <v>13.697864550150999</v>
@@ -13804,7 +13789,7 @@
     </row>
     <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B147" s="1">
         <v>13.521765815989101</v>
@@ -13815,7 +13800,7 @@
     </row>
     <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B148" s="1">
         <v>13.5769688965988</v>
@@ -13826,7 +13811,7 @@
     </row>
     <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B149" s="1">
         <v>13.480301532390399</v>
@@ -13837,7 +13822,7 @@
     </row>
     <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B150" s="1">
         <v>13.457843174234499</v>
@@ -13848,7 +13833,7 @@
     </row>
     <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B151" s="1">
         <v>13.4601858284096</v>
@@ -13859,7 +13844,7 @@
     </row>
     <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B152" s="1">
         <v>13.441398970797801</v>
@@ -13870,7 +13855,7 @@
     </row>
     <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B153" s="1">
         <v>13.4597843604533</v>
@@ -13881,7 +13866,7 @@
     </row>
     <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B154" s="1">
         <v>13.5606966844732</v>
@@ -13892,7 +13877,7 @@
     </row>
     <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B155" s="1">
         <v>13.566424750775999</v>
@@ -13903,7 +13888,7 @@
     </row>
     <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B156" s="1">
         <v>13.677756444678201</v>
@@ -13914,7 +13899,7 @@
     </row>
     <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B157" s="1">
         <v>13.7089668474497</v>
@@ -13925,7 +13910,7 @@
     </row>
     <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B158" s="1">
         <v>13.5896342791272</v>
@@ -13936,7 +13921,7 @@
     </row>
     <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B159" s="1">
         <v>13.672859971194899</v>
@@ -13947,7 +13932,7 @@
     </row>
     <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B160" s="1">
         <v>13.4234538610926</v>
@@ -13958,7 +13943,7 @@
     </row>
     <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B161" s="1">
         <v>2.07892749786477</v>
@@ -13969,7 +13954,7 @@
     </row>
     <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B162" s="1">
         <v>2.0663834161140699</v>
@@ -13980,7 +13965,7 @@
     </row>
     <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B163" s="1">
         <v>2.0628293519735901</v>
@@ -13991,7 +13976,7 @@
     </row>
     <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B164" s="1">
         <v>2.07368391485078</v>
@@ -14002,7 +13987,7 @@
     </row>
     <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B165" s="1">
         <v>2.1039341660075501</v>
@@ -14013,7 +13998,7 @@
     </row>
     <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B166" s="1">
         <v>2.0673577404721302</v>
@@ -14024,7 +14009,7 @@
     </row>
     <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B167" s="1">
         <v>2.0619952490668201</v>
@@ -14035,7 +14020,7 @@
     </row>
     <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B168" s="1">
         <v>2.05981399507903</v>
@@ -14046,7 +14031,7 @@
     </row>
     <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B169" s="1">
         <v>2.0609859200885801</v>
@@ -14057,7 +14042,7 @@
     </row>
     <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B170" s="1">
         <v>2.0594671215384501</v>
@@ -14068,7 +14053,7 @@
     </row>
     <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B171" s="1">
         <v>2.07614752547159</v>
@@ -14079,7 +14064,7 @@
     </row>
     <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B172" s="1">
         <v>2.0785120893459799</v>
@@ -14090,7 +14075,7 @@
     </row>
     <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B173" s="1">
         <v>2.0891336228459898</v>
@@ -14101,7 +14086,7 @@
     </row>
     <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B174" s="1">
         <v>2.0903682617926802</v>
@@ -14112,7 +14097,7 @@
     </row>
     <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B175" s="1">
         <v>2.10180294618258</v>
@@ -14123,7 +14108,7 @@
     </row>
     <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B176" s="1">
         <v>2.1021592068839001</v>
@@ -14134,7 +14119,7 @@
     </row>
     <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B177" s="1">
         <v>2.1003895957887599</v>
@@ -14145,7 +14130,7 @@
     </row>
     <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B178" s="1">
         <v>2.0968436651486999</v>
@@ -14156,7 +14141,7 @@
     </row>
     <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B179" s="1">
         <v>2.0879161684316299</v>
@@ -14167,7 +14152,7 @@
     </row>
     <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B180" s="1">
         <v>2.0889443536633001</v>
@@ -14178,7 +14163,7 @@
     </row>
     <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B181" s="1">
         <v>2.0788690207312501</v>
@@ -14189,7 +14174,7 @@
     </row>
     <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B182" s="1">
         <v>2.0777810140456099</v>
@@ -14200,7 +14185,7 @@
     </row>
     <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B183" s="1">
         <v>2.0773479287857999</v>
@@ -14211,7 +14196,7 @@
     </row>
     <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B184" s="1">
         <v>2.0750460102786898</v>
@@ -14222,7 +14207,7 @@
     </row>
     <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B185" s="1">
         <v>2.07579422159953</v>
@@ -14233,7 +14218,7 @@
     </row>
     <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B186" s="1">
         <v>2.0691590991764399</v>
@@ -14244,7 +14229,7 @@
     </row>
     <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B187" s="1">
         <v>2.0830929433282899</v>
@@ -14255,7 +14240,7 @@
     </row>
     <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B188" s="1">
         <v>2.0711249818440698</v>
@@ -14266,7 +14251,7 @@
     </row>
     <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B189" s="1">
         <v>2.0663816479454802</v>
@@ -14277,7 +14262,7 @@
     </row>
     <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B190" s="1">
         <v>2.0640815890017499</v>
@@ -14288,7 +14273,7 @@
     </row>
     <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B191" s="1">
         <v>2.0662267195881898</v>
@@ -14299,7 +14284,7 @@
     </row>
     <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B192" s="1">
         <v>2.0714341542752299</v>
@@ -14310,7 +14295,7 @@
     </row>
     <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B193" s="1">
         <v>2.5011187965916499</v>
@@ -14321,7 +14306,7 @@
     </row>
     <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B194" s="1">
         <v>2.5056585895299199</v>
@@ -14332,7 +14317,7 @@
     </row>
     <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B195" s="1">
         <v>2.48638142466051</v>
@@ -14343,7 +14328,7 @@
     </row>
     <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B196" s="1">
         <v>2.4855190794760902</v>
@@ -14354,7 +14339,7 @@
     </row>
     <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B197" s="1">
         <v>2.5074216201399602</v>
@@ -14365,7 +14350,7 @@
     </row>
     <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B198" s="1">
         <v>2.4877440696740298</v>
@@ -14376,7 +14361,7 @@
     </row>
     <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B199" s="1">
         <v>2.4798485643611698</v>
@@ -14387,7 +14372,7 @@
     </row>
     <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B200" s="1">
         <v>2.5040935191620002</v>
@@ -14398,7 +14383,7 @@
     </row>
     <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B201" s="1">
         <v>2.5154540630727702</v>
@@ -14409,7 +14394,7 @@
     </row>
     <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B202" s="1">
         <v>2.5215314979177399</v>
@@ -14420,7 +14405,7 @@
     </row>
     <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B203" s="1">
         <v>2.5255084560658201</v>
@@ -14431,7 +14416,7 @@
     </row>
     <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B204" s="1">
         <v>2.5217723144817001</v>
@@ -14442,7 +14427,7 @@
     </row>
     <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B205" s="1">
         <v>2.5063570266102602</v>
@@ -14453,7 +14438,7 @@
     </row>
     <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B206" s="1">
         <v>2.5171411510981598</v>
@@ -14464,7 +14449,7 @@
     </row>
     <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B207" s="1">
         <v>2.5186758172382802</v>
@@ -14475,7 +14460,7 @@
     </row>
     <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B208" s="1">
         <v>2.54554864229272</v>
@@ -14486,7 +14471,7 @@
     </row>
     <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B209" s="1">
         <v>2.54463980757486</v>
@@ -14497,7 +14482,7 @@
     </row>
     <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B210" s="1">
         <v>2.5166341388295401</v>
@@ -14508,7 +14493,7 @@
     </row>
     <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B211" s="1">
         <v>2.52355147173308</v>
@@ -14519,7 +14504,7 @@
     </row>
     <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B212" s="1">
         <v>2.5237166224547098</v>
@@ -14530,7 +14515,7 @@
     </row>
     <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B213" s="1">
         <v>2.5134774644318001</v>
@@ -14541,7 +14526,7 @@
     </row>
     <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B214" s="1">
         <v>2.52756872312878</v>
@@ -14552,7 +14537,7 @@
     </row>
     <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B215" s="1">
         <v>2.51132793852284</v>
@@ -14563,7 +14548,7 @@
     </row>
     <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B216" s="1">
         <v>2.5199495004271499</v>
@@ -14574,7 +14559,7 @@
     </row>
     <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B217" s="1">
         <v>2.5099318931845498</v>
@@ -14585,7 +14570,7 @@
     </row>
     <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B218" s="1">
         <v>2.5170794909418999</v>
@@ -14596,7 +14581,7 @@
     </row>
     <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B219" s="1">
         <v>2.5205441270179501</v>
@@ -14607,7 +14592,7 @@
     </row>
     <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B220" s="1">
         <v>2.5256694865405498</v>
@@ -14618,7 +14603,7 @@
     </row>
     <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B221" s="1">
         <v>2.5268785167168302</v>
@@ -14629,7 +14614,7 @@
     </row>
     <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B222" s="1">
         <v>2.5179187778053098</v>
@@ -14640,7 +14625,7 @@
     </row>
     <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B223" s="1">
         <v>2.5003481091105</v>
@@ -14651,7 +14636,7 @@
     </row>
     <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B224" s="1">
         <v>2.5011416069930501</v>
@@ -14662,7 +14647,7 @@
     </row>
     <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B225" s="1">
         <v>2.49799819651472</v>
@@ -14673,7 +14658,7 @@
     </row>
     <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B226" s="1">
         <v>2.5008140111194899</v>
@@ -14684,7 +14669,7 @@
     </row>
     <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B227" s="1">
         <v>2.4996354690281701</v>
@@ -14695,7 +14680,7 @@
     </row>
     <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B228" s="1">
         <v>2.4937831454353199</v>
@@ -14721,7 +14706,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1">
         <f>_xlfn.STDEV.S(B4:B39)/SQRT(COUNT(B4:B39))</f>
@@ -14758,7 +14743,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <f>100*B1/AVERAGE(B4:B39)</f>
@@ -14795,31 +14780,31 @@
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -15575,7 +15560,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1">
         <f>_xlfn.STDEV.S(B4:B39)/SQRT(COUNT(B4:B39))</f>
@@ -15612,7 +15597,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <f>100*B1/AVERAGE(B4:B39)</f>
@@ -15649,31 +15634,31 @@
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9689E346-71C4-448B-B7D6-BFE2F6FAAC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF14773-0C0C-422C-BB11-EE17912AEF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="290">
   <si>
     <t>May22,2026+11-50-22AM</t>
   </si>
@@ -759,6 +759,156 @@
   </si>
   <si>
     <t>Jul09,2026+4-10-46PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+10-12-06AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+10-34-59AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+10-54-06AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+11-11-20AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+11-19-18AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+11-27-51AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+11-39-03AM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+12-12-01PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+12-21-13PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+12-29-13PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+12-38-19PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+12-58-04PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+1-07-47PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+1-21-29PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+1-34-28PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+1-42-33PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+1-52-37PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+2-05-19PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+2-17-27PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+2-55-51PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+3-41-08PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+3-52-31PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+4-02-38PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+4-10-40PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+4-42-25PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+5-21-33PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+5-31-01PM</t>
+  </si>
+  <si>
+    <t>Jul13,2026+5-39-08PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+12-14-44PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+12-26-20PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+12-34-37PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+12-45-58PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+12-55-14PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+2-38-28PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+2-48-47PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+2-57-45PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+3-05-52PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+3-18-29PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+3-41-29PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+4-11-34PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+4-20-19PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+4-29-37PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-02-47PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-11-12PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-24-44PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-32-49PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-40-48PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+5-56-32PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+6-06-06PM</t>
+  </si>
+  <si>
+    <t>Jul14,2026+6-16-24PM</t>
   </si>
 </sst>
 </file>
@@ -2747,6 +2897,420 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-A036-4546-BBC9-4080821F7EE7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>13-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$229:$B$256</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>4.0279639492061596</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0667523488381301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0183878243548996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0314213938624102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0505545969773804</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0517862191438496</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0424645012040497</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0243487276243002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0367409025359304</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0491156124478902</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.0406778045491096</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0437611760653196</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0356877834891698</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.0543291932026699</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.0440448461837999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.0482658159189198</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.0372658698111801</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.0430873829414802</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.0311378792119203</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.01331392262989</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.0578910745577002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.02794326730218</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.0616651770599299</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.02065487780051</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0194143809069702</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.0195181922825496</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.0060394450385299</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.03113906858741</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$229:$C$256</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>8.3409466599106696E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.3177485471750606E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3006037660706203E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3019038948826299E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.3723462750931996E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.3608574512507694E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.3118939745191397E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.3605447355610901E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.3418150740260003E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.3455841721042895E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.3276939213918696E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.3116670967641595E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.3363484131550397E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3757021233168596E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.3417811249936594E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.4025870340482506E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.2022959476588206E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.3225256404970693E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2797901589345094E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.4124029452458504E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.2524964266572395E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.3779837646985295E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.2884597799815607E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.3056026546302203E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.3119909910801301E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.29152163470048E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8.28084692004942E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.3334028420614895E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0A5E-41D6-B680-57131B471AE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:v>14-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$257:$B$278</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>5.2258479562069899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.1321123174082999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2437157298636796</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2504871284328898</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2503356968257</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.2336543988027202</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.2591832551717097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.2469052817766597</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.25892843081182</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.21286007784256</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2596778259212398</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2590212289624798</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.2296998738747797</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.2667771366869696</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2271473404603404</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.2172814151544804</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.2026205255307998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.2088502809019603</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.2306348705772896</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.2252366536496302</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.2416884024595696</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.2293252887733699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$257:$C$278</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.107867853594575</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.107552731189269</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10779387708665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.108339047437144</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.107577120583375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.108317067772985</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.108753685676204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.107673177325291</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.108229705876452</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.10760496944564001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.108210284447238</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.108391645730674</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.10781058117576001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.108326143627196</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.107921570762375</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.107638855603815</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.10699058330880699</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.10798594921653699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.107583539743761</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.108049349994359</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.107467389213943</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.10771292800641501</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0A5E-41D6-B680-57131B471AE9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12101,7 +12665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
-  <dimension ref="A1:N228"/>
+  <dimension ref="A1:N278"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -14687,6 +15251,556 @@
       </c>
       <c r="C228" s="1">
         <v>4.0347554180400501E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B229" s="1">
+        <v>4.0279639492061596</v>
+      </c>
+      <c r="C229" s="1">
+        <v>8.3409466599106696E-2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B230" s="1">
+        <v>4.0667523488381301</v>
+      </c>
+      <c r="C230" s="1">
+        <v>8.3177485471750606E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B231" s="1">
+        <v>4.0183878243548996</v>
+      </c>
+      <c r="C231" s="1">
+        <v>8.3006037660706203E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B232" s="1">
+        <v>4.0314213938624102</v>
+      </c>
+      <c r="C232" s="1">
+        <v>8.3019038948826299E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B233" s="1">
+        <v>4.0505545969773804</v>
+      </c>
+      <c r="C233" s="1">
+        <v>8.3723462750931996E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B234" s="1">
+        <v>4.0517862191438496</v>
+      </c>
+      <c r="C234" s="1">
+        <v>8.3608574512507694E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B235" s="1">
+        <v>4.0424645012040497</v>
+      </c>
+      <c r="C235" s="1">
+        <v>8.3118939745191397E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B236" s="1">
+        <v>4.0243487276243002</v>
+      </c>
+      <c r="C236" s="1">
+        <v>8.3605447355610901E-2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B237" s="1">
+        <v>4.0367409025359304</v>
+      </c>
+      <c r="C237" s="1">
+        <v>8.3418150740260003E-2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B238" s="1">
+        <v>4.0491156124478902</v>
+      </c>
+      <c r="C238" s="1">
+        <v>8.3455841721042895E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B239" s="1">
+        <v>4.0406778045491096</v>
+      </c>
+      <c r="C239" s="1">
+        <v>8.3276939213918696E-2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B240" s="1">
+        <v>4.0437611760653196</v>
+      </c>
+      <c r="C240" s="1">
+        <v>8.3116670967641595E-2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B241" s="1">
+        <v>4.0356877834891698</v>
+      </c>
+      <c r="C241" s="1">
+        <v>8.3363484131550397E-2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B242" s="1">
+        <v>4.0543291932026699</v>
+      </c>
+      <c r="C242" s="1">
+        <v>8.3757021233168596E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B243" s="1">
+        <v>4.0440448461837999</v>
+      </c>
+      <c r="C243" s="1">
+        <v>8.3417811249936594E-2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B244" s="1">
+        <v>4.0482658159189198</v>
+      </c>
+      <c r="C244" s="1">
+        <v>8.4025870340482506E-2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B245" s="1">
+        <v>4.0372658698111801</v>
+      </c>
+      <c r="C245" s="1">
+        <v>8.2022959476588206E-2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B246" s="1">
+        <v>4.0430873829414802</v>
+      </c>
+      <c r="C246" s="1">
+        <v>8.3225256404970693E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B247" s="1">
+        <v>4.0311378792119203</v>
+      </c>
+      <c r="C247" s="1">
+        <v>8.2797901589345094E-2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B248" s="1">
+        <v>4.01331392262989</v>
+      </c>
+      <c r="C248" s="1">
+        <v>8.4124029452458504E-2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B249" s="1">
+        <v>4.0578910745577002</v>
+      </c>
+      <c r="C249" s="1">
+        <v>8.2524964266572395E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B250" s="1">
+        <v>4.02794326730218</v>
+      </c>
+      <c r="C250" s="1">
+        <v>8.3779837646985295E-2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B251" s="1">
+        <v>4.0616651770599299</v>
+      </c>
+      <c r="C251" s="1">
+        <v>8.2884597799815607E-2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B252" s="1">
+        <v>4.02065487780051</v>
+      </c>
+      <c r="C252" s="1">
+        <v>8.3056026546302203E-2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B253" s="1">
+        <v>4.0194143809069702</v>
+      </c>
+      <c r="C253" s="1">
+        <v>8.3119909910801301E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B254" s="1">
+        <v>4.0195181922825496</v>
+      </c>
+      <c r="C254" s="1">
+        <v>8.29152163470048E-2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B255" s="1">
+        <v>4.0060394450385299</v>
+      </c>
+      <c r="C255" s="1">
+        <v>8.28084692004942E-2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B256" s="1">
+        <v>4.03113906858741</v>
+      </c>
+      <c r="C256" s="1">
+        <v>8.3334028420614895E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B257" s="1">
+        <v>5.2258479562069899</v>
+      </c>
+      <c r="C257" s="1">
+        <v>0.107867853594575</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B258" s="1">
+        <v>5.1321123174082999</v>
+      </c>
+      <c r="C258" s="1">
+        <v>0.107552731189269</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B259" s="1">
+        <v>5.2437157298636796</v>
+      </c>
+      <c r="C259" s="1">
+        <v>0.10779387708665</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B260" s="1">
+        <v>5.2504871284328898</v>
+      </c>
+      <c r="C260" s="1">
+        <v>0.108339047437144</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B261" s="1">
+        <v>5.2503356968257</v>
+      </c>
+      <c r="C261" s="1">
+        <v>0.107577120583375</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B262" s="1">
+        <v>5.2336543988027202</v>
+      </c>
+      <c r="C262" s="1">
+        <v>0.108317067772985</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B263" s="1">
+        <v>5.2591832551717097</v>
+      </c>
+      <c r="C263" s="1">
+        <v>0.108753685676204</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B264" s="1">
+        <v>5.2469052817766597</v>
+      </c>
+      <c r="C264" s="1">
+        <v>0.107673177325291</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B265" s="1">
+        <v>5.25892843081182</v>
+      </c>
+      <c r="C265" s="1">
+        <v>0.108229705876452</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B266" s="1">
+        <v>5.21286007784256</v>
+      </c>
+      <c r="C266" s="1">
+        <v>0.10760496944564001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B267" s="1">
+        <v>5.2596778259212398</v>
+      </c>
+      <c r="C267" s="1">
+        <v>0.108210284447238</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B268" s="1">
+        <v>5.2590212289624798</v>
+      </c>
+      <c r="C268" s="1">
+        <v>0.108391645730674</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B269" s="1">
+        <v>5.2296998738747797</v>
+      </c>
+      <c r="C269" s="1">
+        <v>0.10781058117576001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B270" s="1">
+        <v>5.2667771366869696</v>
+      </c>
+      <c r="C270" s="1">
+        <v>0.108326143627196</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B271" s="1">
+        <v>5.2271473404603404</v>
+      </c>
+      <c r="C271" s="1">
+        <v>0.107921570762375</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B272" s="1">
+        <v>5.2172814151544804</v>
+      </c>
+      <c r="C272" s="1">
+        <v>0.107638855603815</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B273" s="1">
+        <v>5.2026205255307998</v>
+      </c>
+      <c r="C273" s="1">
+        <v>0.10699058330880699</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B274" s="1">
+        <v>5.2088502809019603</v>
+      </c>
+      <c r="C274" s="1">
+        <v>0.10798594921653699</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B275" s="1">
+        <v>5.2306348705772896</v>
+      </c>
+      <c r="C275" s="1">
+        <v>0.107583539743761</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B276" s="1">
+        <v>5.2252366536496302</v>
+      </c>
+      <c r="C276" s="1">
+        <v>0.108049349994359</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B277" s="1">
+        <v>5.2416884024595696</v>
+      </c>
+      <c r="C277" s="1">
+        <v>0.107467389213943</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B278" s="1">
+        <v>5.2293252887733699</v>
+      </c>
+      <c r="C278" s="1">
+        <v>0.10771292800641501</v>
       </c>
     </row>
   </sheetData>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF14773-0C0C-422C-BB11-EE17912AEF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706F1DA-3F07-4242-8298-58FE87822F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3032,88 +3032,88 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="28"/>
                 <c:pt idx="0">
-                  <c:v>8.3409466599106696E-2</c:v>
+                  <c:v>6.4968524453632603E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.3177485471750606E-2</c:v>
+                  <c:v>6.4822401873769905E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.3006037660706203E-2</c:v>
+                  <c:v>6.4645386104361796E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.3019038948826299E-2</c:v>
+                  <c:v>6.4722728337579E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.3723462750931996E-2</c:v>
+                  <c:v>6.5198191332667299E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.3608574512507694E-2</c:v>
+                  <c:v>6.5118995543562194E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.3118939745191397E-2</c:v>
+                  <c:v>6.4744655225756606E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.3605447355610901E-2</c:v>
+                  <c:v>6.5055203385797997E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.3418150740260003E-2</c:v>
+                  <c:v>6.4948449195513402E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3455841721042895E-2</c:v>
+                  <c:v>6.4945497227791402E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.3276939213918696E-2</c:v>
+                  <c:v>6.4863395330163096E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.3116670967641595E-2</c:v>
+                  <c:v>6.4713449109524701E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.3363484131550397E-2</c:v>
+                  <c:v>6.4896125092345797E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.3757021233168596E-2</c:v>
+                  <c:v>6.5241502827778394E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.3417811249936594E-2</c:v>
+                  <c:v>6.4980468998503793E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.4025870340482506E-2</c:v>
+                  <c:v>6.5514217770456601E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.2022959476588206E-2</c:v>
+                  <c:v>6.3922916299629498E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.3225256404970693E-2</c:v>
+                  <c:v>6.4825237757855897E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.2797901589345094E-2</c:v>
+                  <c:v>6.4470305505123601E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.4124029452458504E-2</c:v>
+                  <c:v>6.5433699222487096E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.2524964266572395E-2</c:v>
+                  <c:v>6.4237906062167796E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.3779837646985295E-2</c:v>
+                  <c:v>6.51602437216873E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.2884597799815607E-2</c:v>
+                  <c:v>6.4591400893665399E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.3056026546302203E-2</c:v>
+                  <c:v>6.4621020370609905E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.3119909910801301E-2</c:v>
+                  <c:v>6.4713175919996493E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.29152163470048E-2</c:v>
+                  <c:v>6.4608197537483703E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>8.28084692004942E-2</c:v>
+                  <c:v>6.4507451500493501E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.3334028420614895E-2</c:v>
+                  <c:v>6.4884214968972106E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3239,70 +3239,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>0.107867853594575</c:v>
+                  <c:v>8.4098670481367904E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.107552731189269</c:v>
+                  <c:v>8.3770582022428597E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.10779387708665</c:v>
+                  <c:v>8.3930571430078399E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.108339047437144</c:v>
+                  <c:v>8.4386871474939104E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.107577120583375</c:v>
+                  <c:v>8.3779094698236606E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.108317067772985</c:v>
+                  <c:v>8.4368245251587398E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.108753685676204</c:v>
+                  <c:v>8.4640740114124396E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.107673177325291</c:v>
+                  <c:v>8.3819572528152295E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.108229705876452</c:v>
+                  <c:v>8.4298501986348195E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.10760496944564001</c:v>
+                  <c:v>8.3749879844150901E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.108210284447238</c:v>
+                  <c:v>8.4288203419773597E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.108391645730674</c:v>
+                  <c:v>8.4433783424020706E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.10781058117576001</c:v>
+                  <c:v>8.3978129655986694E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.108326143627196</c:v>
+                  <c:v>8.4391376865179599E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.107921570762375</c:v>
+                  <c:v>8.3986778727553404E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.107638855603815</c:v>
+                  <c:v>8.3700704517771493E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.10699058330880699</c:v>
+                  <c:v>8.3337504828946599E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.10798594921653699</c:v>
+                  <c:v>8.4048471187493506E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.107583539743761</c:v>
+                  <c:v>8.3859299335631896E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.108049349994359</c:v>
+                  <c:v>8.4150599797561301E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.107467389213943</c:v>
+                  <c:v>8.3705403747337398E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.10771292800641501</c:v>
+                  <c:v>8.38953398940607E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15261,7 +15261,7 @@
         <v>4.0279639492061596</v>
       </c>
       <c r="C229" s="1">
-        <v>8.3409466599106696E-2</v>
+        <v>6.4968524453632603E-2</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15272,7 +15272,7 @@
         <v>4.0667523488381301</v>
       </c>
       <c r="C230" s="1">
-        <v>8.3177485471750606E-2</v>
+        <v>6.4822401873769905E-2</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15283,7 +15283,7 @@
         <v>4.0183878243548996</v>
       </c>
       <c r="C231" s="1">
-        <v>8.3006037660706203E-2</v>
+        <v>6.4645386104361796E-2</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15294,7 +15294,7 @@
         <v>4.0314213938624102</v>
       </c>
       <c r="C232" s="1">
-        <v>8.3019038948826299E-2</v>
+        <v>6.4722728337579E-2</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15305,7 +15305,7 @@
         <v>4.0505545969773804</v>
       </c>
       <c r="C233" s="1">
-        <v>8.3723462750931996E-2</v>
+        <v>6.5198191332667299E-2</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15316,7 +15316,7 @@
         <v>4.0517862191438496</v>
       </c>
       <c r="C234" s="1">
-        <v>8.3608574512507694E-2</v>
+        <v>6.5118995543562194E-2</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15327,7 +15327,7 @@
         <v>4.0424645012040497</v>
       </c>
       <c r="C235" s="1">
-        <v>8.3118939745191397E-2</v>
+        <v>6.4744655225756606E-2</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15338,7 +15338,7 @@
         <v>4.0243487276243002</v>
       </c>
       <c r="C236" s="1">
-        <v>8.3605447355610901E-2</v>
+        <v>6.5055203385797997E-2</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15349,7 +15349,7 @@
         <v>4.0367409025359304</v>
       </c>
       <c r="C237" s="1">
-        <v>8.3418150740260003E-2</v>
+        <v>6.4948449195513402E-2</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15360,7 +15360,7 @@
         <v>4.0491156124478902</v>
       </c>
       <c r="C238" s="1">
-        <v>8.3455841721042895E-2</v>
+        <v>6.4945497227791402E-2</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15371,7 +15371,7 @@
         <v>4.0406778045491096</v>
       </c>
       <c r="C239" s="1">
-        <v>8.3276939213918696E-2</v>
+        <v>6.4863395330163096E-2</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15382,7 +15382,7 @@
         <v>4.0437611760653196</v>
       </c>
       <c r="C240" s="1">
-        <v>8.3116670967641595E-2</v>
+        <v>6.4713449109524701E-2</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15393,7 +15393,7 @@
         <v>4.0356877834891698</v>
       </c>
       <c r="C241" s="1">
-        <v>8.3363484131550397E-2</v>
+        <v>6.4896125092345797E-2</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15404,7 +15404,7 @@
         <v>4.0543291932026699</v>
       </c>
       <c r="C242" s="1">
-        <v>8.3757021233168596E-2</v>
+        <v>6.5241502827778394E-2</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15415,7 +15415,7 @@
         <v>4.0440448461837999</v>
       </c>
       <c r="C243" s="1">
-        <v>8.3417811249936594E-2</v>
+        <v>6.4980468998503793E-2</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15426,7 +15426,7 @@
         <v>4.0482658159189198</v>
       </c>
       <c r="C244" s="1">
-        <v>8.4025870340482506E-2</v>
+        <v>6.5514217770456601E-2</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15437,7 +15437,7 @@
         <v>4.0372658698111801</v>
       </c>
       <c r="C245" s="1">
-        <v>8.2022959476588206E-2</v>
+        <v>6.3922916299629498E-2</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15448,7 +15448,7 @@
         <v>4.0430873829414802</v>
       </c>
       <c r="C246" s="1">
-        <v>8.3225256404970693E-2</v>
+        <v>6.4825237757855897E-2</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15459,7 +15459,7 @@
         <v>4.0311378792119203</v>
       </c>
       <c r="C247" s="1">
-        <v>8.2797901589345094E-2</v>
+        <v>6.4470305505123601E-2</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15470,7 +15470,7 @@
         <v>4.01331392262989</v>
       </c>
       <c r="C248" s="1">
-        <v>8.4124029452458504E-2</v>
+        <v>6.5433699222487096E-2</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15481,7 +15481,7 @@
         <v>4.0578910745577002</v>
       </c>
       <c r="C249" s="1">
-        <v>8.2524964266572395E-2</v>
+        <v>6.4237906062167796E-2</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15492,7 +15492,7 @@
         <v>4.02794326730218</v>
       </c>
       <c r="C250" s="1">
-        <v>8.3779837646985295E-2</v>
+        <v>6.51602437216873E-2</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15503,7 +15503,7 @@
         <v>4.0616651770599299</v>
       </c>
       <c r="C251" s="1">
-        <v>8.2884597799815607E-2</v>
+        <v>6.4591400893665399E-2</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15514,7 +15514,7 @@
         <v>4.02065487780051</v>
       </c>
       <c r="C252" s="1">
-        <v>8.3056026546302203E-2</v>
+        <v>6.4621020370609905E-2</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15525,7 +15525,7 @@
         <v>4.0194143809069702</v>
       </c>
       <c r="C253" s="1">
-        <v>8.3119909910801301E-2</v>
+        <v>6.4713175919996493E-2</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15536,7 +15536,7 @@
         <v>4.0195181922825496</v>
       </c>
       <c r="C254" s="1">
-        <v>8.29152163470048E-2</v>
+        <v>6.4608197537483703E-2</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15547,7 +15547,7 @@
         <v>4.0060394450385299</v>
       </c>
       <c r="C255" s="1">
-        <v>8.28084692004942E-2</v>
+        <v>6.4507451500493501E-2</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15558,7 +15558,7 @@
         <v>4.03113906858741</v>
       </c>
       <c r="C256" s="1">
-        <v>8.3334028420614895E-2</v>
+        <v>6.4884214968972106E-2</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15569,7 +15569,7 @@
         <v>5.2258479562069899</v>
       </c>
       <c r="C257" s="1">
-        <v>0.107867853594575</v>
+        <v>8.4098670481367904E-2</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15580,7 +15580,7 @@
         <v>5.1321123174082999</v>
       </c>
       <c r="C258" s="1">
-        <v>0.107552731189269</v>
+        <v>8.3770582022428597E-2</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15591,7 +15591,7 @@
         <v>5.2437157298636796</v>
       </c>
       <c r="C259" s="1">
-        <v>0.10779387708665</v>
+        <v>8.3930571430078399E-2</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15602,7 +15602,7 @@
         <v>5.2504871284328898</v>
       </c>
       <c r="C260" s="1">
-        <v>0.108339047437144</v>
+        <v>8.4386871474939104E-2</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15613,7 +15613,7 @@
         <v>5.2503356968257</v>
       </c>
       <c r="C261" s="1">
-        <v>0.107577120583375</v>
+        <v>8.3779094698236606E-2</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15624,7 +15624,7 @@
         <v>5.2336543988027202</v>
       </c>
       <c r="C262" s="1">
-        <v>0.108317067772985</v>
+        <v>8.4368245251587398E-2</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15635,7 +15635,7 @@
         <v>5.2591832551717097</v>
       </c>
       <c r="C263" s="1">
-        <v>0.108753685676204</v>
+        <v>8.4640740114124396E-2</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15646,7 +15646,7 @@
         <v>5.2469052817766597</v>
       </c>
       <c r="C264" s="1">
-        <v>0.107673177325291</v>
+        <v>8.3819572528152295E-2</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15657,7 +15657,7 @@
         <v>5.25892843081182</v>
       </c>
       <c r="C265" s="1">
-        <v>0.108229705876452</v>
+        <v>8.4298501986348195E-2</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15668,7 +15668,7 @@
         <v>5.21286007784256</v>
       </c>
       <c r="C266" s="1">
-        <v>0.10760496944564001</v>
+        <v>8.3749879844150901E-2</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15679,7 +15679,7 @@
         <v>5.2596778259212398</v>
       </c>
       <c r="C267" s="1">
-        <v>0.108210284447238</v>
+        <v>8.4288203419773597E-2</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15690,7 +15690,7 @@
         <v>5.2590212289624798</v>
       </c>
       <c r="C268" s="1">
-        <v>0.108391645730674</v>
+        <v>8.4433783424020706E-2</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15701,7 +15701,7 @@
         <v>5.2296998738747797</v>
       </c>
       <c r="C269" s="1">
-        <v>0.10781058117576001</v>
+        <v>8.3978129655986694E-2</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15712,7 +15712,7 @@
         <v>5.2667771366869696</v>
       </c>
       <c r="C270" s="1">
-        <v>0.108326143627196</v>
+        <v>8.4391376865179599E-2</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15723,7 +15723,7 @@
         <v>5.2271473404603404</v>
       </c>
       <c r="C271" s="1">
-        <v>0.107921570762375</v>
+        <v>8.3986778727553404E-2</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15734,7 +15734,7 @@
         <v>5.2172814151544804</v>
       </c>
       <c r="C272" s="1">
-        <v>0.107638855603815</v>
+        <v>8.3700704517771493E-2</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15745,7 +15745,7 @@
         <v>5.2026205255307998</v>
       </c>
       <c r="C273" s="1">
-        <v>0.10699058330880699</v>
+        <v>8.3337504828946599E-2</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15756,7 +15756,7 @@
         <v>5.2088502809019603</v>
       </c>
       <c r="C274" s="1">
-        <v>0.10798594921653699</v>
+        <v>8.4048471187493506E-2</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15767,7 +15767,7 @@
         <v>5.2306348705772896</v>
       </c>
       <c r="C275" s="1">
-        <v>0.107583539743761</v>
+        <v>8.3859299335631896E-2</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15778,7 +15778,7 @@
         <v>5.2252366536496302</v>
       </c>
       <c r="C276" s="1">
-        <v>0.108049349994359</v>
+        <v>8.4150599797561301E-2</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15789,7 +15789,7 @@
         <v>5.2416884024595696</v>
       </c>
       <c r="C277" s="1">
-        <v>0.107467389213943</v>
+        <v>8.3705403747337398E-2</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -15800,7 +15800,7 @@
         <v>5.2293252887733699</v>
       </c>
       <c r="C278" s="1">
-        <v>0.10771292800641501</v>
+        <v>8.38953398940607E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706F1DA-3F07-4242-8298-58FE87822F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349DF6D5-427F-4764-B84C-D9D7D84C1A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349DF6D5-427F-4764-B84C-D9D7D84C1A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED921676-03C1-4DA7-9596-6D7BBFF481BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED921676-03C1-4DA7-9596-6D7BBFF481BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA33A68-CF08-4AFA-88FA-2412C5355860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="349">
   <si>
     <t>May22,2026+11-50-22AM</t>
   </si>
@@ -909,6 +906,183 @@
   </si>
   <si>
     <t>Jul14,2026+6-16-24PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-04-00PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-13-10PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-22-33PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-30-33PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-38-38PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-46-37PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+3-54-53PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-02-52PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-11-03PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-19-02PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-29-19PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-38-38PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+4-50-06PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+5-14-19PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+5-22-17PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+5-34-47PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+5-42-51PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+6-20-54PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+6-35-34PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+6-43-28PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+6-52-08PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+7-09-53PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+7-17-49PM</t>
+  </si>
+  <si>
+    <t>Jul15,2026+7-27-51PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+8-55-13AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-04-11AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-15-02AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-23-01AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-33-02AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-41-08AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-49-15AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+9-57-53AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-05-58AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-14-09AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-22-13AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-30-40AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-39-15AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+10-47-37AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-01-11AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-09-27AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-17-25AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-25-19AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-36-19AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+11-44-18AM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+12-12-00PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+12-19-52PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+12-38-41PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+12-47-04PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+12-55-34PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-03-40PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-12-17PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-21-11PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-29-15PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-38-48PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-49-33PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+1-57-55PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+2-05-51PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+2-33-57PM</t>
+  </si>
+  <si>
+    <t>Jul16,2026+3-07-41PM</t>
   </si>
 </sst>
 </file>
@@ -3311,6 +3485,478 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-0A5E-41D6-B680-57131B471AE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:v>15-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$279:$B$302</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>5.2401573655099698</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2402095305102501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2325481598897898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2632048700287699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2341542225512701</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.2499074678307798</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.2609478156281302</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.2522638411999596</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.2381148673874796</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.2236574261532196</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2262449444555799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2457271314303799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.2597760818477397</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.2273625593786797</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2281725990355099</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.2464873820867899</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.2357499987829099</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.2426137496126399</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.25389374708476</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.2452132048918996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.2477036957110901</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.1912280334424699</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.2649162726060403</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.2682959002266401</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$279:$C$302</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>8.4020421663362793E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.3856539409502107E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.4441497497705006E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3922207540377103E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.3819979532311101E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4065913892834104E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.4094869806041694E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.3498425913598198E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.3501392552088799E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.3538886283743397E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.3653316711863296E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.36218907831483E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.3768728051409405E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3798815283381206E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.37952938220691E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.4084000178888202E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.4478909636109295E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.4376066440544406E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.42642456111901E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.3954508319290494E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.4241621326531999E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.39433811384213E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.4883882170655206E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.4153042797615304E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E04E-4239-AE72-E247FFFE8129}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:v>16-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$303:$B$337</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>4.0504847360743401</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0496768121653703</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0401570007949097</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0452933053436704</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0393053513377497</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0427869051265404</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0371132630075302</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0301105995964903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0520999190004696</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0532303423785203</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.0597656945719098</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0397313521665303</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0389446603470498</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.0491521884945199</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.0282207799584802</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.0373666399902799</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.0254616281370303</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.0346044905874798</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.0220126763814203</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.0377589881580498</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.0016969711271004</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.9850777599500198</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.0132441168710704</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.0107044449171996</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0042080560711302</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.0137738076926297</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.0189067438591497</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.0019418304313801</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.0058057955871602</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.0060301681826802</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.99829105994908</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.9906830558389799</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.99736506566357</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.98390122498571</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.9792620371784699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$303:$C$337</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>6.4664938143317294E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.48925563524336E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4717624366303003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5096945322289101E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4780635694392893E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.4828747039054904E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4845896931015903E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.4898532838035997E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4393394651674596E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.4836933722996301E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.4898123293677099E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.48141939607636E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.4945690313312696E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.4750632359324503E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.46466961945657E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.5070391277710998E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.5003508402351404E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.4702157939462199E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.4789520162763903E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.4698100702121605E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.39060983563466E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.4217223623450101E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.4146735969449406E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.4629796704458606E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.43943878164248E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.4478725052475205E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.4781321835991806E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.4392626905219894E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.4250407980306304E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.4167196154649705E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.4208136070914995E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6.4378306448205899E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.4317608614747404E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.3677492575877404E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.3641331008131394E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E04E-4239-AE72-E247FFFE8129}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3490,6 +4136,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3497,7 +4144,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5935,6 +6581,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5942,7 +6589,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6439,6 +7085,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6446,7 +7093,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8884,6 +9530,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8891,7 +9538,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9385,6 +10031,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9392,7 +10039,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12217,10 +12863,10 @@
       <xdr:rowOff>400050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>539750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12665,10 +13311,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
-  <dimension ref="A1:N278"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N337"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12694,7 +13340,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -12736,7 +13382,7 @@
         <v>2.4909699122220328E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -12778,7 +13424,7 @@
         <v>3.9061146219856075E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -12789,7 +13435,7 @@
         <v>0.13701539714226199</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -12800,7 +13446,7 @@
         <v>0.13611960900852699</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -12811,7 +13457,7 @@
         <v>0.13627945937632699</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -12822,7 +13468,7 @@
         <v>0.30390235043574698</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -12833,7 +13479,7 @@
         <v>0.30438419283964002</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -12844,7 +13490,7 @@
         <v>0.297161130585052</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -12855,7 +13501,7 @@
         <v>0.30092447877826201</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -12866,7 +13512,7 @@
         <v>0.30225556251139701</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -12877,7 +13523,7 @@
         <v>0.30453505035585898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -12888,7 +13534,7 @@
         <v>0.29441937543381203</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -12899,7 +13545,7 @@
         <v>0.29938049893952201</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -12910,7 +13556,7 @@
         <v>0.30198767465833298</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -12921,7 +13567,7 @@
         <v>0.29452133244947898</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -12932,7 +13578,7 @@
         <v>0.30226636207287</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -12943,7 +13589,7 @@
         <v>0.30276185184620003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -12954,7 +13600,7 @@
         <v>0.30565983998385898</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -12965,7 +13611,7 @@
         <v>0.30235700258888798</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -12976,7 +13622,7 @@
         <v>0.30470031507930101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -12987,7 +13633,7 @@
         <v>0.30681032275950298</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -12998,7 +13644,7 @@
         <v>0.31003085423784599</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -13009,7 +13655,7 @@
         <v>0.30130891367381502</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -13020,7 +13666,7 @@
         <v>0.141175020925183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -13031,7 +13677,7 @@
         <v>0.13910706901585701</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -13042,7 +13688,7 @@
         <v>0.14173595580689399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -13053,7 +13699,7 @@
         <v>0.141258173819516</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -13064,7 +13710,7 @@
         <v>0.142207734258748</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -13075,7 +13721,7 @@
         <v>0.13801119003128501</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
@@ -13086,7 +13732,7 @@
         <v>0.14302506923553299</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -13097,7 +13743,7 @@
         <v>0.171876620266287</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -13108,7 +13754,7 @@
         <v>0.17507983789020901</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -13119,7 +13765,7 @@
         <v>0.17353748848485201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -13130,7 +13776,7 @@
         <v>0.17399520336378199</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -13141,7 +13787,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -13152,7 +13798,7 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -13163,7 +13809,7 @@
         <v>0.17111359499762699</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -13174,7 +13820,7 @@
         <v>0.174442312499583</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -13185,7 +13831,7 @@
         <v>0.17165345419397299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -13196,7 +13842,7 @@
         <v>0.17188594050678699</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -13207,7 +13853,7 @@
         <v>0.17182639857690499</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -13218,7 +13864,7 @@
         <v>0.173011271970926</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -13229,7 +13875,7 @@
         <v>0.173393882992014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -13240,7 +13886,7 @@
         <v>0.17255170638235601</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -13251,7 +13897,7 @@
         <v>0.176156057962948</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -13262,7 +13908,7 @@
         <v>0.17277891898827699</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -13273,7 +13919,7 @@
         <v>0.173614948750792</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -13284,7 +13930,7 @@
         <v>0.17607067167010601</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -13295,7 +13941,7 @@
         <v>0.17040120856414201</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -13306,7 +13952,7 @@
         <v>0.17423160269966501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -13317,7 +13963,7 @@
         <v>0.174369956316375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -13328,7 +13974,7 @@
         <v>0.17111424613243301</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -13339,7 +13985,7 @@
         <v>0.174141819699693</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -13350,7 +13996,7 @@
         <v>0.17027613633024699</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -13361,7 +14007,7 @@
         <v>0.17305899861083601</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -13372,7 +14018,7 @@
         <v>0.169629744786672</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -13383,7 +14029,7 @@
         <v>0.17362236751906199</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
@@ -13394,7 +14040,7 @@
         <v>0.17378947989454699</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -13405,7 +14051,7 @@
         <v>0.17301730214639</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -13416,7 +14062,7 @@
         <v>0.17294290042990301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -13427,7 +14073,7 @@
         <v>0.17314296764265499</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -13438,7 +14084,7 @@
         <v>0.26702709086345899</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>67</v>
       </c>
@@ -13449,7 +14095,7 @@
         <v>0.26377604366503299</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>68</v>
       </c>
@@ -13460,7 +14106,7 @@
         <v>0.26272554597887199</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -13471,7 +14117,7 @@
         <v>0.26788317969509901</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
@@ -13482,7 +14128,7 @@
         <v>0.26503400399869398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
@@ -13493,7 +14139,7 @@
         <v>0.26673897966627602</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>72</v>
       </c>
@@ -13504,7 +14150,7 @@
         <v>0.26807575946030698</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>73</v>
       </c>
@@ -13515,7 +14161,7 @@
         <v>0.266570039729353</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -13526,7 +14172,7 @@
         <v>0.27166172606546901</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
@@ -13537,7 +14183,7 @@
         <v>0.26522605962651602</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -13548,7 +14194,7 @@
         <v>0.27094063293660098</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>77</v>
       </c>
@@ -13559,7 +14205,7 @@
         <v>0.26838563360762802</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>78</v>
       </c>
@@ -13570,7 +14216,7 @@
         <v>0.26226006746867903</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -13581,7 +14227,7 @@
         <v>0.26283415625491802</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>80</v>
       </c>
@@ -13592,7 +14238,7 @@
         <v>0.265891536409124</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>81</v>
       </c>
@@ -13603,7 +14249,7 @@
         <v>0.26086999753535101</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>82</v>
       </c>
@@ -13614,7 +14260,7 @@
         <v>0.264030412441006</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>83</v>
       </c>
@@ -13625,7 +14271,7 @@
         <v>0.26104421609513101</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
@@ -13636,7 +14282,7 @@
         <v>0.26790761730572898</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>85</v>
       </c>
@@ -13647,7 +14293,7 @@
         <v>0.26200964452208297</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>86</v>
       </c>
@@ -13658,7 +14304,7 @@
         <v>0.26657014430711701</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>87</v>
       </c>
@@ -13669,7 +14315,7 @@
         <v>0.264335730958146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>88</v>
       </c>
@@ -13680,7 +14326,7 @@
         <v>0.26876048744697101</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>89</v>
       </c>
@@ -13691,7 +14337,7 @@
         <v>0.26514897700620299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>90</v>
       </c>
@@ -13702,7 +14348,7 @@
         <v>0.26219390887345601</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>91</v>
       </c>
@@ -13713,7 +14359,7 @@
         <v>0.26184487099436499</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>92</v>
       </c>
@@ -13724,7 +14370,7 @@
         <v>0.26409583467590397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>93</v>
       </c>
@@ -13735,7 +14381,7 @@
         <v>0.26424448419416702</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>94</v>
       </c>
@@ -13746,7 +14392,7 @@
         <v>0.26363414452799</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>95</v>
       </c>
@@ -13757,7 +14403,7 @@
         <v>0.26464837628465498</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>96</v>
       </c>
@@ -13768,7 +14414,7 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>104</v>
       </c>
@@ -13779,7 +14425,7 @@
         <v>0.23820566920665201</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>105</v>
       </c>
@@ -13790,7 +14436,7 @@
         <v>0.23716854436609899</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>106</v>
       </c>
@@ -13801,7 +14447,7 @@
         <v>0.24334889035587701</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>107</v>
       </c>
@@ -13812,7 +14458,7 @@
         <v>0.24139693907330401</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>108</v>
       </c>
@@ -13823,7 +14469,7 @@
         <v>0.24177140642297701</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>109</v>
       </c>
@@ -13834,7 +14480,7 @@
         <v>0.24611015618375001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>110</v>
       </c>
@@ -13845,7 +14491,7 @@
         <v>0.24482638982888399</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>111</v>
       </c>
@@ -13856,7 +14502,7 @@
         <v>0.24047022478348701</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>112</v>
       </c>
@@ -13867,7 +14513,7 @@
         <v>0.24076714972723101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>113</v>
       </c>
@@ -13878,7 +14524,7 @@
         <v>0.244370206125226</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>114</v>
       </c>
@@ -13889,7 +14535,7 @@
         <v>0.24313993631303599</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>115</v>
       </c>
@@ -13900,7 +14546,7 @@
         <v>0.240076934656237</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>116</v>
       </c>
@@ -13911,7 +14557,7 @@
         <v>0.242245334794052</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>117</v>
       </c>
@@ -13922,7 +14568,7 @@
         <v>0.24081642222489599</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>118</v>
       </c>
@@ -13933,7 +14579,7 @@
         <v>0.23946128860629701</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>119</v>
       </c>
@@ -13944,7 +14590,7 @@
         <v>0.24067136591591201</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>120</v>
       </c>
@@ -13955,7 +14601,7 @@
         <v>0.241804540636641</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>121</v>
       </c>
@@ -13966,7 +14612,7 @@
         <v>0.237876942608618</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>122</v>
       </c>
@@ -13977,7 +14623,7 @@
         <v>0.241838145831969</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>123</v>
       </c>
@@ -13988,7 +14634,7 @@
         <v>0.24402502768845699</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>124</v>
       </c>
@@ -13999,7 +14645,7 @@
         <v>0.23989744417664499</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>125</v>
       </c>
@@ -14010,7 +14656,7 @@
         <v>0.240176182150968</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>126</v>
       </c>
@@ -14021,7 +14667,7 @@
         <v>0.238939795428251</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>127</v>
       </c>
@@ -14032,7 +14678,7 @@
         <v>0.23962573892411401</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>128</v>
       </c>
@@ -14043,7 +14689,7 @@
         <v>0.24176111907040099</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>129</v>
       </c>
@@ -14054,7 +14700,7 @@
         <v>0.24348653683848701</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>130</v>
       </c>
@@ -14065,7 +14711,7 @@
         <v>0.24073031648363399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>131</v>
       </c>
@@ -14076,7 +14722,7 @@
         <v>0.24558776594854301</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>132</v>
       </c>
@@ -14087,7 +14733,7 @@
         <v>0.239185337596831</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>133</v>
       </c>
@@ -14098,7 +14744,7 @@
         <v>0.241717931493385</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>134</v>
       </c>
@@ -14109,7 +14755,7 @@
         <v>0.24138266998260599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>135</v>
       </c>
@@ -14120,7 +14766,7 @@
         <v>0.24367652321245201</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>136</v>
       </c>
@@ -14131,7 +14777,7 @@
         <v>0.22233607124480101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>137</v>
       </c>
@@ -14142,7 +14788,7 @@
         <v>0.222916111013889</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>138</v>
       </c>
@@ -14153,7 +14799,7 @@
         <v>0.21978080516705001</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>139</v>
       </c>
@@ -14164,7 +14810,7 @@
         <v>0.21701744510815299</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>140</v>
       </c>
@@ -14175,7 +14821,7 @@
         <v>0.22292724198768199</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>141</v>
       </c>
@@ -14186,7 +14832,7 @@
         <v>0.222109442813166</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>142</v>
       </c>
@@ -14197,7 +14843,7 @@
         <v>0.221905259897859</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>143</v>
       </c>
@@ -14208,7 +14854,7 @@
         <v>0.21899661326540701</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -14219,7 +14865,7 @@
         <v>0.21885786728813</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>145</v>
       </c>
@@ -14230,7 +14876,7 @@
         <v>0.21579488523700499</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>146</v>
       </c>
@@ -14241,7 +14887,7 @@
         <v>0.220755926487161</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>147</v>
       </c>
@@ -14252,7 +14898,7 @@
         <v>0.22011228616490899</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>148</v>
       </c>
@@ -14263,7 +14909,7 @@
         <v>0.21961259407713499</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>149</v>
       </c>
@@ -14274,7 +14920,7 @@
         <v>0.22007796981835101</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>150</v>
       </c>
@@ -14285,7 +14931,7 @@
         <v>0.21807344865282799</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>151</v>
       </c>
@@ -14296,7 +14942,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>152</v>
       </c>
@@ -14307,7 +14953,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>153</v>
       </c>
@@ -14318,7 +14964,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>154</v>
       </c>
@@ -14329,7 +14975,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>155</v>
       </c>
@@ -14340,7 +14986,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>156</v>
       </c>
@@ -14351,7 +14997,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>157</v>
       </c>
@@ -14362,7 +15008,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>158</v>
       </c>
@@ -14373,7 +15019,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>159</v>
       </c>
@@ -14384,7 +15030,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>160</v>
       </c>
@@ -14395,7 +15041,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>161</v>
       </c>
@@ -14406,7 +15052,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>162</v>
       </c>
@@ -14417,7 +15063,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>163</v>
       </c>
@@ -14428,7 +15074,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>164</v>
       </c>
@@ -14439,7 +15085,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>165</v>
       </c>
@@ -14450,7 +15096,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>166</v>
       </c>
@@ -14461,7 +15107,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>167</v>
       </c>
@@ -14472,7 +15118,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>168</v>
       </c>
@@ -14483,7 +15129,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>169</v>
       </c>
@@ -14494,7 +15140,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>170</v>
       </c>
@@ -14505,7 +15151,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>172</v>
       </c>
@@ -14516,7 +15162,7 @@
         <v>3.30028948262861E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>173</v>
       </c>
@@ -14527,7 +15173,7 @@
         <v>3.3489889357849002E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>174</v>
       </c>
@@ -14538,7 +15184,7 @@
         <v>3.34050697248311E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>175</v>
       </c>
@@ -14549,7 +15195,7 @@
         <v>3.3663016244114899E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>176</v>
       </c>
@@ -14560,7 +15206,7 @@
         <v>3.3862208744561598E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>177</v>
       </c>
@@ -14571,7 +15217,7 @@
         <v>3.3371230140689601E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>178</v>
       </c>
@@ -14582,7 +15228,7 @@
         <v>3.3958687307630298E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>179</v>
       </c>
@@ -14593,7 +15239,7 @@
         <v>3.3717539743101703E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>180</v>
       </c>
@@ -14604,7 +15250,7 @@
         <v>3.4019624541611997E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>181</v>
       </c>
@@ -14615,7 +15261,7 @@
         <v>3.30325465399912E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>182</v>
       </c>
@@ -14626,7 +15272,7 @@
         <v>3.3342495220022902E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>183</v>
       </c>
@@ -14637,7 +15283,7 @@
         <v>3.3765726933882197E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>184</v>
       </c>
@@ -14648,7 +15294,7 @@
         <v>3.3827431022495302E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>185</v>
       </c>
@@ -14659,7 +15305,7 @@
         <v>3.2562436603975398E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>186</v>
       </c>
@@ -14670,7 +15316,7 @@
         <v>3.3936476228758998E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>187</v>
       </c>
@@ -14681,7 +15327,7 @@
         <v>3.3445511192293297E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>188</v>
       </c>
@@ -14692,7 +15338,7 @@
         <v>3.3061817051389601E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>189</v>
       </c>
@@ -14703,7 +15349,7 @@
         <v>3.35542069970673E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>190</v>
       </c>
@@ -14714,7 +15360,7 @@
         <v>3.4176849718869903E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>191</v>
       </c>
@@ -14725,7 +15371,7 @@
         <v>3.3607525034085699E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>192</v>
       </c>
@@ -14736,7 +15382,7 @@
         <v>3.3291217503168297E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>193</v>
       </c>
@@ -14747,7 +15393,7 @@
         <v>3.3587626783338299E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>194</v>
       </c>
@@ -14758,7 +15404,7 @@
         <v>3.3498059501305001E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>195</v>
       </c>
@@ -14769,7 +15415,7 @@
         <v>3.3612378265113999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>196</v>
       </c>
@@ -14780,7 +15426,7 @@
         <v>3.36767838831264E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>197</v>
       </c>
@@ -14791,7 +15437,7 @@
         <v>3.4205246508627503E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>198</v>
       </c>
@@ -14802,7 +15448,7 @@
         <v>3.33159042246957E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>199</v>
       </c>
@@ -14813,7 +15459,7 @@
         <v>3.4310317322257401E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>200</v>
       </c>
@@ -14824,7 +15470,7 @@
         <v>3.4082317162395397E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>201</v>
       </c>
@@ -14835,7 +15481,7 @@
         <v>3.3309537312556703E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>202</v>
       </c>
@@ -14846,7 +15492,7 @@
         <v>3.2808961198641698E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>203</v>
       </c>
@@ -14857,7 +15503,7 @@
         <v>3.3324024754485697E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>204</v>
       </c>
@@ -14868,7 +15514,7 @@
         <v>4.0620494830716898E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>205</v>
       </c>
@@ -14879,7 +15525,7 @@
         <v>4.0445250720025597E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>206</v>
       </c>
@@ -14890,7 +15536,7 @@
         <v>4.0191516108636097E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>207</v>
       </c>
@@ -14901,7 +15547,7 @@
         <v>4.0970033814296203E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>208</v>
       </c>
@@ -14912,7 +15558,7 @@
         <v>4.04373053253217E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>209</v>
       </c>
@@ -14923,7 +15569,7 @@
         <v>4.0649065132095999E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>210</v>
       </c>
@@ -14934,7 +15580,7 @@
         <v>3.9533611139950402E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>211</v>
       </c>
@@ -14945,7 +15591,7 @@
         <v>4.0155853483306803E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>212</v>
       </c>
@@ -14956,7 +15602,7 @@
         <v>4.0445594269577098E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>213</v>
       </c>
@@ -14967,7 +15613,7 @@
         <v>3.9604033537862203E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>214</v>
       </c>
@@ -14978,7 +15624,7 @@
         <v>4.0174033834531497E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>215</v>
       </c>
@@ -14989,7 +15635,7 @@
         <v>4.1231746357817303E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>216</v>
       </c>
@@ -15000,7 +15646,7 @@
         <v>4.0336571538600499E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>217</v>
       </c>
@@ -15011,7 +15657,7 @@
         <v>4.0359240284840503E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>218</v>
       </c>
@@ -15022,7 +15668,7 @@
         <v>4.0249713225980401E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>219</v>
       </c>
@@ -15033,7 +15679,7 @@
         <v>4.0520690948023297E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>220</v>
       </c>
@@ -15044,7 +15690,7 @@
         <v>4.02329856985481E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>221</v>
       </c>
@@ -15055,7 +15701,7 @@
         <v>4.0144847093634903E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>222</v>
       </c>
@@ -15066,7 +15712,7 @@
         <v>4.0409209035940002E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>223</v>
       </c>
@@ -15077,7 +15723,7 @@
         <v>4.10395989464786E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>224</v>
       </c>
@@ -15088,7 +15734,7 @@
         <v>3.98714030158333E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>225</v>
       </c>
@@ -15099,7 +15745,7 @@
         <v>3.98908146812504E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>226</v>
       </c>
@@ -15110,7 +15756,7 @@
         <v>4.0524916971605499E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>227</v>
       </c>
@@ -15121,7 +15767,7 @@
         <v>4.0390455654384101E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>228</v>
       </c>
@@ -15132,7 +15778,7 @@
         <v>4.1071400769317298E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>229</v>
       </c>
@@ -15143,7 +15789,7 @@
         <v>4.0178381373720602E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>230</v>
       </c>
@@ -15154,7 +15800,7 @@
         <v>4.0702941996408802E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>231</v>
       </c>
@@ -15165,7 +15811,7 @@
         <v>4.01385052767382E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>232</v>
       </c>
@@ -15176,7 +15822,7 @@
         <v>4.0018008651341898E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>233</v>
       </c>
@@ -15187,7 +15833,7 @@
         <v>3.9989666024372497E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>234</v>
       </c>
@@ -15198,7 +15844,7 @@
         <v>4.0322645046764097E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>235</v>
       </c>
@@ -15209,7 +15855,7 @@
         <v>4.0532664600090897E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>236</v>
       </c>
@@ -15220,7 +15866,7 @@
         <v>4.06963104125408E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>237</v>
       </c>
@@ -15231,7 +15877,7 @@
         <v>4.1172181601451197E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>238</v>
       </c>
@@ -15242,7 +15888,7 @@
         <v>3.9836921294789503E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>239</v>
       </c>
@@ -15253,7 +15899,7 @@
         <v>4.0347554180400501E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>240</v>
       </c>
@@ -15264,7 +15910,7 @@
         <v>6.4968524453632603E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>241</v>
       </c>
@@ -15275,7 +15921,7 @@
         <v>6.4822401873769905E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>242</v>
       </c>
@@ -15286,7 +15932,7 @@
         <v>6.4645386104361796E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>243</v>
       </c>
@@ -15297,7 +15943,7 @@
         <v>6.4722728337579E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>244</v>
       </c>
@@ -15308,7 +15954,7 @@
         <v>6.5198191332667299E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>245</v>
       </c>
@@ -15319,7 +15965,7 @@
         <v>6.5118995543562194E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>246</v>
       </c>
@@ -15330,7 +15976,7 @@
         <v>6.4744655225756606E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>247</v>
       </c>
@@ -15341,7 +15987,7 @@
         <v>6.5055203385797997E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>248</v>
       </c>
@@ -15352,7 +15998,7 @@
         <v>6.4948449195513402E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>249</v>
       </c>
@@ -15363,7 +16009,7 @@
         <v>6.4945497227791402E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>250</v>
       </c>
@@ -15374,7 +16020,7 @@
         <v>6.4863395330163096E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>251</v>
       </c>
@@ -15385,7 +16031,7 @@
         <v>6.4713449109524701E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>252</v>
       </c>
@@ -15396,7 +16042,7 @@
         <v>6.4896125092345797E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>253</v>
       </c>
@@ -15407,7 +16053,7 @@
         <v>6.5241502827778394E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>254</v>
       </c>
@@ -15418,7 +16064,7 @@
         <v>6.4980468998503793E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>255</v>
       </c>
@@ -15429,7 +16075,7 @@
         <v>6.5514217770456601E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>256</v>
       </c>
@@ -15440,7 +16086,7 @@
         <v>6.3922916299629498E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>257</v>
       </c>
@@ -15451,7 +16097,7 @@
         <v>6.4825237757855897E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>258</v>
       </c>
@@ -15462,7 +16108,7 @@
         <v>6.4470305505123601E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>259</v>
       </c>
@@ -15473,7 +16119,7 @@
         <v>6.5433699222487096E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>260</v>
       </c>
@@ -15484,7 +16130,7 @@
         <v>6.4237906062167796E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>261</v>
       </c>
@@ -15495,7 +16141,7 @@
         <v>6.51602437216873E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>262</v>
       </c>
@@ -15506,7 +16152,7 @@
         <v>6.4591400893665399E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>263</v>
       </c>
@@ -15517,7 +16163,7 @@
         <v>6.4621020370609905E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>264</v>
       </c>
@@ -15528,7 +16174,7 @@
         <v>6.4713175919996493E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>265</v>
       </c>
@@ -15539,7 +16185,7 @@
         <v>6.4608197537483703E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>266</v>
       </c>
@@ -15550,7 +16196,7 @@
         <v>6.4507451500493501E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>267</v>
       </c>
@@ -15561,7 +16207,7 @@
         <v>6.4884214968972106E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>268</v>
       </c>
@@ -15572,7 +16218,7 @@
         <v>8.4098670481367904E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>269</v>
       </c>
@@ -15583,7 +16229,7 @@
         <v>8.3770582022428597E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>270</v>
       </c>
@@ -15594,7 +16240,7 @@
         <v>8.3930571430078399E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>271</v>
       </c>
@@ -15605,7 +16251,7 @@
         <v>8.4386871474939104E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>272</v>
       </c>
@@ -15616,7 +16262,7 @@
         <v>8.3779094698236606E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>273</v>
       </c>
@@ -15627,7 +16273,7 @@
         <v>8.4368245251587398E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>274</v>
       </c>
@@ -15638,7 +16284,7 @@
         <v>8.4640740114124396E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>275</v>
       </c>
@@ -15649,7 +16295,7 @@
         <v>8.3819572528152295E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>276</v>
       </c>
@@ -15660,7 +16306,7 @@
         <v>8.4298501986348195E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>277</v>
       </c>
@@ -15671,7 +16317,7 @@
         <v>8.3749879844150901E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>278</v>
       </c>
@@ -15682,7 +16328,7 @@
         <v>8.4288203419773597E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>279</v>
       </c>
@@ -15693,7 +16339,7 @@
         <v>8.4433783424020706E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>280</v>
       </c>
@@ -15704,7 +16350,7 @@
         <v>8.3978129655986694E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>281</v>
       </c>
@@ -15715,7 +16361,7 @@
         <v>8.4391376865179599E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>282</v>
       </c>
@@ -15726,7 +16372,7 @@
         <v>8.3986778727553404E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>283</v>
       </c>
@@ -15737,7 +16383,7 @@
         <v>8.3700704517771493E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>284</v>
       </c>
@@ -15748,7 +16394,7 @@
         <v>8.3337504828946599E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>285</v>
       </c>
@@ -15759,7 +16405,7 @@
         <v>8.4048471187493506E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>286</v>
       </c>
@@ -15770,7 +16416,7 @@
         <v>8.3859299335631896E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>287</v>
       </c>
@@ -15781,7 +16427,7 @@
         <v>8.4150599797561301E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>288</v>
       </c>
@@ -15792,7 +16438,7 @@
         <v>8.3705403747337398E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>289</v>
       </c>
@@ -15801,6 +16447,655 @@
       </c>
       <c r="C278" s="1">
         <v>8.38953398940607E-2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A279" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B279" s="1">
+        <v>5.2401573655099698</v>
+      </c>
+      <c r="C279" s="1">
+        <v>8.4020421663362793E-2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A280" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B280" s="1">
+        <v>5.2402095305102501</v>
+      </c>
+      <c r="C280" s="1">
+        <v>8.3856539409502107E-2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A281" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B281" s="1">
+        <v>5.2325481598897898</v>
+      </c>
+      <c r="C281" s="1">
+        <v>8.4441497497705006E-2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A282" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B282" s="1">
+        <v>5.2632048700287699</v>
+      </c>
+      <c r="C282" s="1">
+        <v>8.3922207540377103E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A283" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B283" s="1">
+        <v>5.2341542225512701</v>
+      </c>
+      <c r="C283" s="1">
+        <v>8.3819979532311101E-2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A284" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B284" s="1">
+        <v>5.2499074678307798</v>
+      </c>
+      <c r="C284" s="1">
+        <v>8.4065913892834104E-2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A285" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B285" s="1">
+        <v>5.2609478156281302</v>
+      </c>
+      <c r="C285" s="1">
+        <v>8.4094869806041694E-2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A286" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B286" s="1">
+        <v>5.2522638411999596</v>
+      </c>
+      <c r="C286" s="1">
+        <v>8.3498425913598198E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A287" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B287" s="1">
+        <v>5.2381148673874796</v>
+      </c>
+      <c r="C287" s="1">
+        <v>8.3501392552088799E-2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A288" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B288" s="1">
+        <v>5.2236574261532196</v>
+      </c>
+      <c r="C288" s="1">
+        <v>8.3538886283743397E-2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A289" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B289" s="1">
+        <v>5.2262449444555799</v>
+      </c>
+      <c r="C289" s="1">
+        <v>8.3653316711863296E-2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A290" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B290" s="1">
+        <v>5.2457271314303799</v>
+      </c>
+      <c r="C290" s="1">
+        <v>8.36218907831483E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A291" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B291" s="1">
+        <v>5.2597760818477397</v>
+      </c>
+      <c r="C291" s="1">
+        <v>8.3768728051409405E-2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A292" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B292" s="1">
+        <v>5.2273625593786797</v>
+      </c>
+      <c r="C292" s="1">
+        <v>8.3798815283381206E-2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A293" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B293" s="1">
+        <v>5.2281725990355099</v>
+      </c>
+      <c r="C293" s="1">
+        <v>8.37952938220691E-2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A294" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B294" s="1">
+        <v>5.2464873820867899</v>
+      </c>
+      <c r="C294" s="1">
+        <v>8.4084000178888202E-2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A295" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B295" s="1">
+        <v>5.2357499987829099</v>
+      </c>
+      <c r="C295" s="1">
+        <v>8.4478909636109295E-2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A296" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B296" s="1">
+        <v>5.2426137496126399</v>
+      </c>
+      <c r="C296" s="1">
+        <v>8.4376066440544406E-2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A297" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B297" s="1">
+        <v>5.25389374708476</v>
+      </c>
+      <c r="C297" s="1">
+        <v>8.42642456111901E-2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A298" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B298" s="1">
+        <v>5.2452132048918996</v>
+      </c>
+      <c r="C298" s="1">
+        <v>8.3954508319290494E-2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A299" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B299" s="1">
+        <v>5.2477036957110901</v>
+      </c>
+      <c r="C299" s="1">
+        <v>8.4241621326531999E-2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A300" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B300" s="1">
+        <v>5.1912280334424699</v>
+      </c>
+      <c r="C300" s="1">
+        <v>8.39433811384213E-2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A301" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B301" s="1">
+        <v>5.2649162726060403</v>
+      </c>
+      <c r="C301" s="1">
+        <v>8.4883882170655206E-2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A302" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B302" s="1">
+        <v>5.2682959002266401</v>
+      </c>
+      <c r="C302" s="1">
+        <v>8.4153042797615304E-2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A303" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B303" s="1">
+        <v>4.0504847360743401</v>
+      </c>
+      <c r="C303" s="1">
+        <v>6.4664938143317294E-2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A304" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B304" s="1">
+        <v>4.0496768121653703</v>
+      </c>
+      <c r="C304" s="1">
+        <v>6.48925563524336E-2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A305" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B305" s="1">
+        <v>4.0401570007949097</v>
+      </c>
+      <c r="C305" s="1">
+        <v>6.4717624366303003E-2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A306" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B306" s="1">
+        <v>4.0452933053436704</v>
+      </c>
+      <c r="C306" s="1">
+        <v>6.5096945322289101E-2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A307" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B307" s="1">
+        <v>4.0393053513377497</v>
+      </c>
+      <c r="C307" s="1">
+        <v>6.4780635694392893E-2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A308" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B308" s="1">
+        <v>4.0427869051265404</v>
+      </c>
+      <c r="C308" s="1">
+        <v>6.4828747039054904E-2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A309" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B309" s="1">
+        <v>4.0371132630075302</v>
+      </c>
+      <c r="C309" s="1">
+        <v>6.4845896931015903E-2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A310" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B310" s="1">
+        <v>4.0301105995964903</v>
+      </c>
+      <c r="C310" s="1">
+        <v>6.4898532838035997E-2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A311" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B311" s="1">
+        <v>4.0520999190004696</v>
+      </c>
+      <c r="C311" s="1">
+        <v>6.4393394651674596E-2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A312" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B312" s="1">
+        <v>4.0532303423785203</v>
+      </c>
+      <c r="C312" s="1">
+        <v>6.4836933722996301E-2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A313" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B313" s="1">
+        <v>4.0597656945719098</v>
+      </c>
+      <c r="C313" s="1">
+        <v>6.4898123293677099E-2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A314" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B314" s="1">
+        <v>4.0397313521665303</v>
+      </c>
+      <c r="C314" s="1">
+        <v>6.48141939607636E-2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A315" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B315" s="1">
+        <v>4.0389446603470498</v>
+      </c>
+      <c r="C315" s="1">
+        <v>6.4945690313312696E-2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A316" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B316" s="1">
+        <v>4.0491521884945199</v>
+      </c>
+      <c r="C316" s="1">
+        <v>6.4750632359324503E-2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A317" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B317" s="1">
+        <v>4.0282207799584802</v>
+      </c>
+      <c r="C317" s="1">
+        <v>6.46466961945657E-2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A318" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B318" s="1">
+        <v>4.0373666399902799</v>
+      </c>
+      <c r="C318" s="1">
+        <v>6.5070391277710998E-2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A319" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B319" s="1">
+        <v>4.0254616281370303</v>
+      </c>
+      <c r="C319" s="1">
+        <v>6.5003508402351404E-2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A320" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B320" s="1">
+        <v>4.0346044905874798</v>
+      </c>
+      <c r="C320" s="1">
+        <v>6.4702157939462199E-2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A321" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B321" s="1">
+        <v>4.0220126763814203</v>
+      </c>
+      <c r="C321" s="1">
+        <v>6.4789520162763903E-2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A322" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B322" s="1">
+        <v>4.0377589881580498</v>
+      </c>
+      <c r="C322" s="1">
+        <v>6.4698100702121605E-2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A323" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B323" s="1">
+        <v>4.0016969711271004</v>
+      </c>
+      <c r="C323" s="1">
+        <v>6.39060983563466E-2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A324" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B324" s="1">
+        <v>3.9850777599500198</v>
+      </c>
+      <c r="C324" s="1">
+        <v>6.4217223623450101E-2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A325" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B325" s="1">
+        <v>4.0132441168710704</v>
+      </c>
+      <c r="C325" s="1">
+        <v>6.4146735969449406E-2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A326" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B326" s="1">
+        <v>4.0107044449171996</v>
+      </c>
+      <c r="C326" s="1">
+        <v>6.4629796704458606E-2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A327" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B327" s="1">
+        <v>4.0042080560711302</v>
+      </c>
+      <c r="C327" s="1">
+        <v>6.43943878164248E-2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A328" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B328" s="1">
+        <v>4.0137738076926297</v>
+      </c>
+      <c r="C328" s="1">
+        <v>6.4478725052475205E-2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A329" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B329" s="1">
+        <v>4.0189067438591497</v>
+      </c>
+      <c r="C329" s="1">
+        <v>6.4781321835991806E-2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A330" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B330" s="1">
+        <v>4.0019418304313801</v>
+      </c>
+      <c r="C330" s="1">
+        <v>6.4392626905219894E-2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A331" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B331" s="1">
+        <v>4.0058057955871602</v>
+      </c>
+      <c r="C331" s="1">
+        <v>6.4250407980306304E-2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A332" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B332" s="1">
+        <v>4.0060301681826802</v>
+      </c>
+      <c r="C332" s="1">
+        <v>6.4167196154649705E-2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A333" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B333" s="1">
+        <v>3.99829105994908</v>
+      </c>
+      <c r="C333" s="1">
+        <v>6.4208136070914995E-2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A334" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B334" s="1">
+        <v>3.9906830558389799</v>
+      </c>
+      <c r="C334" s="1">
+        <v>6.4378306448205899E-2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A335" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B335" s="1">
+        <v>3.99736506566357</v>
+      </c>
+      <c r="C335" s="1">
+        <v>6.4317608614747404E-2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A336" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B336" s="1">
+        <v>3.98390122498571</v>
+      </c>
+      <c r="C336" s="1">
+        <v>6.3677492575877404E-2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A337" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B337" s="1">
+        <v>3.9792620371784699</v>
+      </c>
+      <c r="C337" s="1">
+        <v>6.3641331008131394E-2</v>
       </c>
     </row>
   </sheetData>
@@ -15812,13 +17107,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -15855,7 +17150,7 @@
         <v>2.8613971962500952E-4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -15892,7 +17187,7 @@
         <v>0.12997532261023939</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -15923,7 +17218,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -15954,7 +17249,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -15985,7 +17280,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -16016,7 +17311,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -16047,7 +17342,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -16078,7 +17373,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -16105,7 +17400,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -16130,7 +17425,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -16153,7 +17448,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -16176,7 +17471,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -16199,7 +17494,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -16222,7 +17517,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -16245,7 +17540,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -16268,7 +17563,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -16291,7 +17586,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -16314,7 +17609,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -16336,7 +17631,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -16358,7 +17653,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -16380,7 +17675,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -16400,7 +17695,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -16420,7 +17715,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
@@ -16439,7 +17734,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -16458,7 +17753,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
@@ -16477,7 +17772,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
@@ -16496,7 +17791,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
@@ -16515,7 +17810,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
@@ -16531,7 +17826,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
@@ -16547,7 +17842,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
@@ -16563,7 +17858,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
@@ -16579,7 +17874,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
@@ -16595,7 +17890,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
@@ -16611,7 +17906,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>32</v>
       </c>
@@ -16624,7 +17919,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>33</v>
       </c>
@@ -16633,7 +17928,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>34</v>
       </c>
@@ -16642,7 +17937,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>35</v>
       </c>
@@ -16651,7 +17946,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>36</v>
       </c>
@@ -16667,12 +17962,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -16709,7 +18004,7 @@
         <v>1.4794192860515082E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -16746,7 +18041,7 @@
         <v>0.1090690310547095</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -16777,7 +18072,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -16808,7 +18103,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -16839,7 +18134,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -16870,7 +18165,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -16901,7 +18196,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -16932,7 +18227,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -16959,7 +18254,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -16984,7 +18279,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -17007,7 +18302,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -17030,7 +18325,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -17053,7 +18348,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -17076,7 +18371,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -17099,7 +18394,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -17122,7 +18417,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -17145,7 +18440,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -17168,7 +18463,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -17190,7 +18485,7 @@
         <v>13.5963637628518</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -17212,7 +18507,7 @@
         <v>13.6061621269385</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -17234,7 +18529,7 @@
         <v>13.564508484015001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -17254,7 +18549,7 @@
         <v>13.566012885219999</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -17274,7 +18569,7 @@
         <v>13.677050331463599</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
@@ -17293,7 +18588,7 @@
         <v>13.697864550150999</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -17312,7 +18607,7 @@
         <v>13.521765815989101</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
@@ -17331,7 +18626,7 @@
         <v>13.5769688965988</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
@@ -17350,7 +18645,7 @@
         <v>13.480301532390399</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
@@ -17369,7 +18664,7 @@
         <v>13.457843174234499</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
@@ -17385,7 +18680,7 @@
         <v>13.4601858284096</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
@@ -17401,7 +18696,7 @@
         <v>13.441398970797801</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
@@ -17417,7 +18712,7 @@
         <v>13.4597843604533</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
@@ -17433,7 +18728,7 @@
         <v>13.5606966844732</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
@@ -17449,7 +18744,7 @@
         <v>13.566424750775999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
@@ -17465,7 +18760,7 @@
         <v>13.677756444678201</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>32</v>
       </c>
@@ -17478,7 +18773,7 @@
         <v>13.7089668474497</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>33</v>
       </c>
@@ -17487,7 +18782,7 @@
         <v>13.5896342791272</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>34</v>
       </c>
@@ -17496,7 +18791,7 @@
         <v>13.672859971194899</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>35</v>
       </c>
@@ -17505,7 +18800,7 @@
         <v>13.4234538610926</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>36</v>
       </c>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA33A68-CF08-4AFA-88FA-2412C5355860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DBB335-98CE-4F06-9EE6-88837AFDAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4136,7 +4139,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4144,6 +4146,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6581,7 +6584,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6589,6 +6591,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7085,7 +7088,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7093,6 +7095,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9530,7 +9533,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9538,6 +9540,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10031,7 +10034,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10039,6 +10041,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13312,9 +13315,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
   <dimension ref="A1:N337"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13340,7 +13343,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -13382,7 +13385,7 @@
         <v>2.4909699122220328E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -13424,7 +13427,7 @@
         <v>3.9061146219856075E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -13435,7 +13438,7 @@
         <v>0.13701539714226199</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -13446,7 +13449,7 @@
         <v>0.13611960900852699</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -13457,7 +13460,7 @@
         <v>0.13627945937632699</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -13468,7 +13471,7 @@
         <v>0.30390235043574698</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -13479,7 +13482,7 @@
         <v>0.30438419283964002</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -13490,7 +13493,7 @@
         <v>0.297161130585052</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -13501,7 +13504,7 @@
         <v>0.30092447877826201</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -13512,7 +13515,7 @@
         <v>0.30225556251139701</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -13523,7 +13526,7 @@
         <v>0.30453505035585898</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -13534,7 +13537,7 @@
         <v>0.29441937543381203</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -13545,7 +13548,7 @@
         <v>0.29938049893952201</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -13556,7 +13559,7 @@
         <v>0.30198767465833298</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -13567,7 +13570,7 @@
         <v>0.29452133244947898</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -13578,7 +13581,7 @@
         <v>0.30226636207287</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -13589,7 +13592,7 @@
         <v>0.30276185184620003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -13600,7 +13603,7 @@
         <v>0.30565983998385898</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -13611,7 +13614,7 @@
         <v>0.30235700258888798</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>0.30470031507930101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -13633,7 +13636,7 @@
         <v>0.30681032275950298</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -13644,7 +13647,7 @@
         <v>0.31003085423784599</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -13655,7 +13658,7 @@
         <v>0.30130891367381502</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -13666,7 +13669,7 @@
         <v>0.141175020925183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -13677,7 +13680,7 @@
         <v>0.13910706901585701</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -13688,7 +13691,7 @@
         <v>0.14173595580689399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -13699,7 +13702,7 @@
         <v>0.141258173819516</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -13710,7 +13713,7 @@
         <v>0.142207734258748</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -13721,7 +13724,7 @@
         <v>0.13801119003128501</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
@@ -13732,7 +13735,7 @@
         <v>0.14302506923553299</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -13743,7 +13746,7 @@
         <v>0.171876620266287</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -13754,7 +13757,7 @@
         <v>0.17507983789020901</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -13765,7 +13768,7 @@
         <v>0.17353748848485201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -13776,7 +13779,7 @@
         <v>0.17399520336378199</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -13787,7 +13790,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -13798,7 +13801,7 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -13809,7 +13812,7 @@
         <v>0.17111359499762699</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -13820,7 +13823,7 @@
         <v>0.174442312499583</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -13831,7 +13834,7 @@
         <v>0.17165345419397299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -13842,7 +13845,7 @@
         <v>0.17188594050678699</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -13853,7 +13856,7 @@
         <v>0.17182639857690499</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -13864,7 +13867,7 @@
         <v>0.173011271970926</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -13875,7 +13878,7 @@
         <v>0.173393882992014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -13886,7 +13889,7 @@
         <v>0.17255170638235601</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -13897,7 +13900,7 @@
         <v>0.176156057962948</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -13908,7 +13911,7 @@
         <v>0.17277891898827699</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -13919,7 +13922,7 @@
         <v>0.173614948750792</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -13930,7 +13933,7 @@
         <v>0.17607067167010601</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -13941,7 +13944,7 @@
         <v>0.17040120856414201</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -13952,7 +13955,7 @@
         <v>0.17423160269966501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -13963,7 +13966,7 @@
         <v>0.174369956316375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -13974,7 +13977,7 @@
         <v>0.17111424613243301</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -13985,7 +13988,7 @@
         <v>0.174141819699693</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -13996,7 +13999,7 @@
         <v>0.17027613633024699</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -14007,7 +14010,7 @@
         <v>0.17305899861083601</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -14018,7 +14021,7 @@
         <v>0.169629744786672</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -14029,7 +14032,7 @@
         <v>0.17362236751906199</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
@@ -14040,7 +14043,7 @@
         <v>0.17378947989454699</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -14051,7 +14054,7 @@
         <v>0.17301730214639</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -14062,7 +14065,7 @@
         <v>0.17294290042990301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -14073,7 +14076,7 @@
         <v>0.17314296764265499</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -14084,7 +14087,7 @@
         <v>0.26702709086345899</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>67</v>
       </c>
@@ -14095,7 +14098,7 @@
         <v>0.26377604366503299</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>68</v>
       </c>
@@ -14106,7 +14109,7 @@
         <v>0.26272554597887199</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -14117,7 +14120,7 @@
         <v>0.26788317969509901</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
@@ -14128,7 +14131,7 @@
         <v>0.26503400399869398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
@@ -14139,7 +14142,7 @@
         <v>0.26673897966627602</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>72</v>
       </c>
@@ -14150,7 +14153,7 @@
         <v>0.26807575946030698</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>73</v>
       </c>
@@ -14161,7 +14164,7 @@
         <v>0.266570039729353</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -14172,7 +14175,7 @@
         <v>0.27166172606546901</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
@@ -14183,7 +14186,7 @@
         <v>0.26522605962651602</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -14194,7 +14197,7 @@
         <v>0.27094063293660098</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>77</v>
       </c>
@@ -14205,7 +14208,7 @@
         <v>0.26838563360762802</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>78</v>
       </c>
@@ -14216,7 +14219,7 @@
         <v>0.26226006746867903</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -14227,7 +14230,7 @@
         <v>0.26283415625491802</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>80</v>
       </c>
@@ -14238,7 +14241,7 @@
         <v>0.265891536409124</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>81</v>
       </c>
@@ -14249,7 +14252,7 @@
         <v>0.26086999753535101</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>82</v>
       </c>
@@ -14260,7 +14263,7 @@
         <v>0.264030412441006</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>83</v>
       </c>
@@ -14271,7 +14274,7 @@
         <v>0.26104421609513101</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
@@ -14282,7 +14285,7 @@
         <v>0.26790761730572898</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>85</v>
       </c>
@@ -14293,7 +14296,7 @@
         <v>0.26200964452208297</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>86</v>
       </c>
@@ -14304,7 +14307,7 @@
         <v>0.26657014430711701</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>87</v>
       </c>
@@ -14315,7 +14318,7 @@
         <v>0.264335730958146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>88</v>
       </c>
@@ -14326,7 +14329,7 @@
         <v>0.26876048744697101</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>89</v>
       </c>
@@ -14337,7 +14340,7 @@
         <v>0.26514897700620299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>90</v>
       </c>
@@ -14348,7 +14351,7 @@
         <v>0.26219390887345601</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>91</v>
       </c>
@@ -14359,7 +14362,7 @@
         <v>0.26184487099436499</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>92</v>
       </c>
@@ -14370,7 +14373,7 @@
         <v>0.26409583467590397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>93</v>
       </c>
@@ -14381,7 +14384,7 @@
         <v>0.26424448419416702</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>94</v>
       </c>
@@ -14392,7 +14395,7 @@
         <v>0.26363414452799</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>95</v>
       </c>
@@ -14403,7 +14406,7 @@
         <v>0.26464837628465498</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>96</v>
       </c>
@@ -14414,7 +14417,7 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>104</v>
       </c>
@@ -14425,7 +14428,7 @@
         <v>0.23820566920665201</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>105</v>
       </c>
@@ -14436,7 +14439,7 @@
         <v>0.23716854436609899</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>106</v>
       </c>
@@ -14447,7 +14450,7 @@
         <v>0.24334889035587701</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>107</v>
       </c>
@@ -14458,7 +14461,7 @@
         <v>0.24139693907330401</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>108</v>
       </c>
@@ -14469,7 +14472,7 @@
         <v>0.24177140642297701</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>109</v>
       </c>
@@ -14480,7 +14483,7 @@
         <v>0.24611015618375001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>110</v>
       </c>
@@ -14491,7 +14494,7 @@
         <v>0.24482638982888399</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>111</v>
       </c>
@@ -14502,7 +14505,7 @@
         <v>0.24047022478348701</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>112</v>
       </c>
@@ -14513,7 +14516,7 @@
         <v>0.24076714972723101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>113</v>
       </c>
@@ -14524,7 +14527,7 @@
         <v>0.244370206125226</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>114</v>
       </c>
@@ -14535,7 +14538,7 @@
         <v>0.24313993631303599</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>115</v>
       </c>
@@ -14546,7 +14549,7 @@
         <v>0.240076934656237</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>116</v>
       </c>
@@ -14557,7 +14560,7 @@
         <v>0.242245334794052</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>117</v>
       </c>
@@ -14568,7 +14571,7 @@
         <v>0.24081642222489599</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>118</v>
       </c>
@@ -14579,7 +14582,7 @@
         <v>0.23946128860629701</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>119</v>
       </c>
@@ -14590,7 +14593,7 @@
         <v>0.24067136591591201</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>120</v>
       </c>
@@ -14601,7 +14604,7 @@
         <v>0.241804540636641</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>121</v>
       </c>
@@ -14612,7 +14615,7 @@
         <v>0.237876942608618</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>122</v>
       </c>
@@ -14623,7 +14626,7 @@
         <v>0.241838145831969</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>123</v>
       </c>
@@ -14634,7 +14637,7 @@
         <v>0.24402502768845699</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>124</v>
       </c>
@@ -14645,7 +14648,7 @@
         <v>0.23989744417664499</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>125</v>
       </c>
@@ -14656,7 +14659,7 @@
         <v>0.240176182150968</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>126</v>
       </c>
@@ -14667,7 +14670,7 @@
         <v>0.238939795428251</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>127</v>
       </c>
@@ -14678,7 +14681,7 @@
         <v>0.23962573892411401</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>128</v>
       </c>
@@ -14689,7 +14692,7 @@
         <v>0.24176111907040099</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>129</v>
       </c>
@@ -14700,7 +14703,7 @@
         <v>0.24348653683848701</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>130</v>
       </c>
@@ -14711,7 +14714,7 @@
         <v>0.24073031648363399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>131</v>
       </c>
@@ -14722,7 +14725,7 @@
         <v>0.24558776594854301</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>132</v>
       </c>
@@ -14733,7 +14736,7 @@
         <v>0.239185337596831</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>133</v>
       </c>
@@ -14744,7 +14747,7 @@
         <v>0.241717931493385</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>134</v>
       </c>
@@ -14755,7 +14758,7 @@
         <v>0.24138266998260599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>135</v>
       </c>
@@ -14766,7 +14769,7 @@
         <v>0.24367652321245201</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>136</v>
       </c>
@@ -14777,7 +14780,7 @@
         <v>0.22233607124480101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>137</v>
       </c>
@@ -14788,7 +14791,7 @@
         <v>0.222916111013889</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>138</v>
       </c>
@@ -14799,7 +14802,7 @@
         <v>0.21978080516705001</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>139</v>
       </c>
@@ -14810,7 +14813,7 @@
         <v>0.21701744510815299</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>140</v>
       </c>
@@ -14821,7 +14824,7 @@
         <v>0.22292724198768199</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>141</v>
       </c>
@@ -14832,7 +14835,7 @@
         <v>0.222109442813166</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>142</v>
       </c>
@@ -14843,7 +14846,7 @@
         <v>0.221905259897859</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>143</v>
       </c>
@@ -14854,7 +14857,7 @@
         <v>0.21899661326540701</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -14865,7 +14868,7 @@
         <v>0.21885786728813</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>145</v>
       </c>
@@ -14876,7 +14879,7 @@
         <v>0.21579488523700499</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>146</v>
       </c>
@@ -14887,7 +14890,7 @@
         <v>0.220755926487161</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>147</v>
       </c>
@@ -14898,7 +14901,7 @@
         <v>0.22011228616490899</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>148</v>
       </c>
@@ -14909,7 +14912,7 @@
         <v>0.21961259407713499</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>149</v>
       </c>
@@ -14920,7 +14923,7 @@
         <v>0.22007796981835101</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>150</v>
       </c>
@@ -14931,7 +14934,7 @@
         <v>0.21807344865282799</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>151</v>
       </c>
@@ -14942,7 +14945,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>152</v>
       </c>
@@ -14953,7 +14956,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>153</v>
       </c>
@@ -14964,7 +14967,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>154</v>
       </c>
@@ -14975,7 +14978,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>155</v>
       </c>
@@ -14986,7 +14989,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>156</v>
       </c>
@@ -14997,7 +15000,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>157</v>
       </c>
@@ -15008,7 +15011,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>158</v>
       </c>
@@ -15019,7 +15022,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>159</v>
       </c>
@@ -15030,7 +15033,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>160</v>
       </c>
@@ -15041,7 +15044,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>161</v>
       </c>
@@ -15052,7 +15055,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>162</v>
       </c>
@@ -15063,7 +15066,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>163</v>
       </c>
@@ -15074,7 +15077,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>164</v>
       </c>
@@ -15085,7 +15088,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>165</v>
       </c>
@@ -15096,7 +15099,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>166</v>
       </c>
@@ -15107,7 +15110,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>167</v>
       </c>
@@ -15118,7 +15121,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>168</v>
       </c>
@@ -15129,7 +15132,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>169</v>
       </c>
@@ -15140,7 +15143,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>170</v>
       </c>
@@ -15151,7 +15154,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>172</v>
       </c>
@@ -15162,7 +15165,7 @@
         <v>3.30028948262861E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>173</v>
       </c>
@@ -15173,7 +15176,7 @@
         <v>3.3489889357849002E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>174</v>
       </c>
@@ -15184,7 +15187,7 @@
         <v>3.34050697248311E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>175</v>
       </c>
@@ -15195,7 +15198,7 @@
         <v>3.3663016244114899E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>176</v>
       </c>
@@ -15206,7 +15209,7 @@
         <v>3.3862208744561598E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>177</v>
       </c>
@@ -15217,7 +15220,7 @@
         <v>3.3371230140689601E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>178</v>
       </c>
@@ -15228,7 +15231,7 @@
         <v>3.3958687307630298E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>179</v>
       </c>
@@ -15239,7 +15242,7 @@
         <v>3.3717539743101703E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>180</v>
       </c>
@@ -15250,7 +15253,7 @@
         <v>3.4019624541611997E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>181</v>
       </c>
@@ -15261,7 +15264,7 @@
         <v>3.30325465399912E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>182</v>
       </c>
@@ -15272,7 +15275,7 @@
         <v>3.3342495220022902E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>183</v>
       </c>
@@ -15283,7 +15286,7 @@
         <v>3.3765726933882197E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>184</v>
       </c>
@@ -15294,7 +15297,7 @@
         <v>3.3827431022495302E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>185</v>
       </c>
@@ -15305,7 +15308,7 @@
         <v>3.2562436603975398E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>186</v>
       </c>
@@ -15316,7 +15319,7 @@
         <v>3.3936476228758998E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>187</v>
       </c>
@@ -15327,7 +15330,7 @@
         <v>3.3445511192293297E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>188</v>
       </c>
@@ -15338,7 +15341,7 @@
         <v>3.3061817051389601E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>189</v>
       </c>
@@ -15349,7 +15352,7 @@
         <v>3.35542069970673E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>190</v>
       </c>
@@ -15360,7 +15363,7 @@
         <v>3.4176849718869903E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>191</v>
       </c>
@@ -15371,7 +15374,7 @@
         <v>3.3607525034085699E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>192</v>
       </c>
@@ -15382,7 +15385,7 @@
         <v>3.3291217503168297E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>193</v>
       </c>
@@ -15393,7 +15396,7 @@
         <v>3.3587626783338299E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>194</v>
       </c>
@@ -15404,7 +15407,7 @@
         <v>3.3498059501305001E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>195</v>
       </c>
@@ -15415,7 +15418,7 @@
         <v>3.3612378265113999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>196</v>
       </c>
@@ -15426,7 +15429,7 @@
         <v>3.36767838831264E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>197</v>
       </c>
@@ -15437,7 +15440,7 @@
         <v>3.4205246508627503E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>198</v>
       </c>
@@ -15448,7 +15451,7 @@
         <v>3.33159042246957E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>199</v>
       </c>
@@ -15459,7 +15462,7 @@
         <v>3.4310317322257401E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>200</v>
       </c>
@@ -15470,7 +15473,7 @@
         <v>3.4082317162395397E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>201</v>
       </c>
@@ -15481,7 +15484,7 @@
         <v>3.3309537312556703E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>202</v>
       </c>
@@ -15492,7 +15495,7 @@
         <v>3.2808961198641698E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>203</v>
       </c>
@@ -15503,7 +15506,7 @@
         <v>3.3324024754485697E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>204</v>
       </c>
@@ -15514,7 +15517,7 @@
         <v>4.0620494830716898E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>205</v>
       </c>
@@ -15525,7 +15528,7 @@
         <v>4.0445250720025597E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>206</v>
       </c>
@@ -15536,7 +15539,7 @@
         <v>4.0191516108636097E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>207</v>
       </c>
@@ -15547,7 +15550,7 @@
         <v>4.0970033814296203E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>208</v>
       </c>
@@ -15558,7 +15561,7 @@
         <v>4.04373053253217E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>209</v>
       </c>
@@ -15569,7 +15572,7 @@
         <v>4.0649065132095999E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>210</v>
       </c>
@@ -15580,7 +15583,7 @@
         <v>3.9533611139950402E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>211</v>
       </c>
@@ -15591,7 +15594,7 @@
         <v>4.0155853483306803E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>212</v>
       </c>
@@ -15602,7 +15605,7 @@
         <v>4.0445594269577098E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>213</v>
       </c>
@@ -15613,7 +15616,7 @@
         <v>3.9604033537862203E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>214</v>
       </c>
@@ -15624,7 +15627,7 @@
         <v>4.0174033834531497E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>215</v>
       </c>
@@ -15635,7 +15638,7 @@
         <v>4.1231746357817303E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>216</v>
       </c>
@@ -15646,7 +15649,7 @@
         <v>4.0336571538600499E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>217</v>
       </c>
@@ -15657,7 +15660,7 @@
         <v>4.0359240284840503E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>218</v>
       </c>
@@ -15668,7 +15671,7 @@
         <v>4.0249713225980401E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>219</v>
       </c>
@@ -15679,7 +15682,7 @@
         <v>4.0520690948023297E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>220</v>
       </c>
@@ -15690,7 +15693,7 @@
         <v>4.02329856985481E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>221</v>
       </c>
@@ -15701,7 +15704,7 @@
         <v>4.0144847093634903E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>222</v>
       </c>
@@ -15712,7 +15715,7 @@
         <v>4.0409209035940002E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>223</v>
       </c>
@@ -15723,7 +15726,7 @@
         <v>4.10395989464786E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>224</v>
       </c>
@@ -15734,7 +15737,7 @@
         <v>3.98714030158333E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>225</v>
       </c>
@@ -15745,7 +15748,7 @@
         <v>3.98908146812504E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>226</v>
       </c>
@@ -15756,7 +15759,7 @@
         <v>4.0524916971605499E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>227</v>
       </c>
@@ -15767,7 +15770,7 @@
         <v>4.0390455654384101E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>228</v>
       </c>
@@ -15778,7 +15781,7 @@
         <v>4.1071400769317298E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>229</v>
       </c>
@@ -15789,7 +15792,7 @@
         <v>4.0178381373720602E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>230</v>
       </c>
@@ -15800,7 +15803,7 @@
         <v>4.0702941996408802E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>231</v>
       </c>
@@ -15811,7 +15814,7 @@
         <v>4.01385052767382E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>232</v>
       </c>
@@ -15822,7 +15825,7 @@
         <v>4.0018008651341898E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>233</v>
       </c>
@@ -15833,7 +15836,7 @@
         <v>3.9989666024372497E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>234</v>
       </c>
@@ -15844,7 +15847,7 @@
         <v>4.0322645046764097E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>235</v>
       </c>
@@ -15855,7 +15858,7 @@
         <v>4.0532664600090897E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>236</v>
       </c>
@@ -15866,7 +15869,7 @@
         <v>4.06963104125408E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>237</v>
       </c>
@@ -15877,7 +15880,7 @@
         <v>4.1172181601451197E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>238</v>
       </c>
@@ -15888,7 +15891,7 @@
         <v>3.9836921294789503E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>239</v>
       </c>
@@ -15899,7 +15902,7 @@
         <v>4.0347554180400501E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>240</v>
       </c>
@@ -15910,7 +15913,7 @@
         <v>6.4968524453632603E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>241</v>
       </c>
@@ -15921,7 +15924,7 @@
         <v>6.4822401873769905E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>242</v>
       </c>
@@ -15932,7 +15935,7 @@
         <v>6.4645386104361796E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>243</v>
       </c>
@@ -15943,7 +15946,7 @@
         <v>6.4722728337579E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>244</v>
       </c>
@@ -15954,7 +15957,7 @@
         <v>6.5198191332667299E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>245</v>
       </c>
@@ -15965,7 +15968,7 @@
         <v>6.5118995543562194E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>246</v>
       </c>
@@ -15976,7 +15979,7 @@
         <v>6.4744655225756606E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>247</v>
       </c>
@@ -15987,7 +15990,7 @@
         <v>6.5055203385797997E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>248</v>
       </c>
@@ -15998,7 +16001,7 @@
         <v>6.4948449195513402E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>249</v>
       </c>
@@ -16009,7 +16012,7 @@
         <v>6.4945497227791402E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>250</v>
       </c>
@@ -16020,7 +16023,7 @@
         <v>6.4863395330163096E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>251</v>
       </c>
@@ -16031,7 +16034,7 @@
         <v>6.4713449109524701E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>252</v>
       </c>
@@ -16042,7 +16045,7 @@
         <v>6.4896125092345797E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>253</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>6.5241502827778394E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>254</v>
       </c>
@@ -16064,7 +16067,7 @@
         <v>6.4980468998503793E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>255</v>
       </c>
@@ -16075,7 +16078,7 @@
         <v>6.5514217770456601E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>256</v>
       </c>
@@ -16086,7 +16089,7 @@
         <v>6.3922916299629498E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>257</v>
       </c>
@@ -16097,7 +16100,7 @@
         <v>6.4825237757855897E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>258</v>
       </c>
@@ -16108,7 +16111,7 @@
         <v>6.4470305505123601E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>259</v>
       </c>
@@ -16119,7 +16122,7 @@
         <v>6.5433699222487096E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>260</v>
       </c>
@@ -16130,7 +16133,7 @@
         <v>6.4237906062167796E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>261</v>
       </c>
@@ -16141,7 +16144,7 @@
         <v>6.51602437216873E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>262</v>
       </c>
@@ -16152,7 +16155,7 @@
         <v>6.4591400893665399E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>263</v>
       </c>
@@ -16163,7 +16166,7 @@
         <v>6.4621020370609905E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>264</v>
       </c>
@@ -16174,7 +16177,7 @@
         <v>6.4713175919996493E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>265</v>
       </c>
@@ -16185,7 +16188,7 @@
         <v>6.4608197537483703E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>266</v>
       </c>
@@ -16196,7 +16199,7 @@
         <v>6.4507451500493501E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>267</v>
       </c>
@@ -16207,7 +16210,7 @@
         <v>6.4884214968972106E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>268</v>
       </c>
@@ -16218,7 +16221,7 @@
         <v>8.4098670481367904E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>269</v>
       </c>
@@ -16229,7 +16232,7 @@
         <v>8.3770582022428597E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>270</v>
       </c>
@@ -16240,7 +16243,7 @@
         <v>8.3930571430078399E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>271</v>
       </c>
@@ -16251,7 +16254,7 @@
         <v>8.4386871474939104E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>272</v>
       </c>
@@ -16262,7 +16265,7 @@
         <v>8.3779094698236606E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>273</v>
       </c>
@@ -16273,7 +16276,7 @@
         <v>8.4368245251587398E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>274</v>
       </c>
@@ -16284,7 +16287,7 @@
         <v>8.4640740114124396E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>275</v>
       </c>
@@ -16295,7 +16298,7 @@
         <v>8.3819572528152295E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>276</v>
       </c>
@@ -16306,7 +16309,7 @@
         <v>8.4298501986348195E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>277</v>
       </c>
@@ -16317,7 +16320,7 @@
         <v>8.3749879844150901E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>278</v>
       </c>
@@ -16328,7 +16331,7 @@
         <v>8.4288203419773597E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>279</v>
       </c>
@@ -16339,7 +16342,7 @@
         <v>8.4433783424020706E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>280</v>
       </c>
@@ -16350,7 +16353,7 @@
         <v>8.3978129655986694E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>281</v>
       </c>
@@ -16361,7 +16364,7 @@
         <v>8.4391376865179599E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>282</v>
       </c>
@@ -16372,7 +16375,7 @@
         <v>8.3986778727553404E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>283</v>
       </c>
@@ -16383,7 +16386,7 @@
         <v>8.3700704517771493E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>284</v>
       </c>
@@ -16394,7 +16397,7 @@
         <v>8.3337504828946599E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>285</v>
       </c>
@@ -16405,7 +16408,7 @@
         <v>8.4048471187493506E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>286</v>
       </c>
@@ -16416,7 +16419,7 @@
         <v>8.3859299335631896E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>287</v>
       </c>
@@ -16427,7 +16430,7 @@
         <v>8.4150599797561301E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>288</v>
       </c>
@@ -16438,7 +16441,7 @@
         <v>8.3705403747337398E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>289</v>
       </c>
@@ -16449,7 +16452,7 @@
         <v>8.38953398940607E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>290</v>
       </c>
@@ -16460,7 +16463,7 @@
         <v>8.4020421663362793E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>291</v>
       </c>
@@ -16471,7 +16474,7 @@
         <v>8.3856539409502107E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>292</v>
       </c>
@@ -16482,7 +16485,7 @@
         <v>8.4441497497705006E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>293</v>
       </c>
@@ -16493,7 +16496,7 @@
         <v>8.3922207540377103E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>294</v>
       </c>
@@ -16504,7 +16507,7 @@
         <v>8.3819979532311101E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>295</v>
       </c>
@@ -16515,7 +16518,7 @@
         <v>8.4065913892834104E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>296</v>
       </c>
@@ -16526,7 +16529,7 @@
         <v>8.4094869806041694E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>297</v>
       </c>
@@ -16537,7 +16540,7 @@
         <v>8.3498425913598198E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>298</v>
       </c>
@@ -16548,7 +16551,7 @@
         <v>8.3501392552088799E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>299</v>
       </c>
@@ -16559,7 +16562,7 @@
         <v>8.3538886283743397E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>300</v>
       </c>
@@ -16570,7 +16573,7 @@
         <v>8.3653316711863296E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>301</v>
       </c>
@@ -16581,7 +16584,7 @@
         <v>8.36218907831483E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>302</v>
       </c>
@@ -16592,7 +16595,7 @@
         <v>8.3768728051409405E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>303</v>
       </c>
@@ -16603,7 +16606,7 @@
         <v>8.3798815283381206E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>304</v>
       </c>
@@ -16614,7 +16617,7 @@
         <v>8.37952938220691E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>305</v>
       </c>
@@ -16625,7 +16628,7 @@
         <v>8.4084000178888202E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>306</v>
       </c>
@@ -16636,7 +16639,7 @@
         <v>8.4478909636109295E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>307</v>
       </c>
@@ -16647,7 +16650,7 @@
         <v>8.4376066440544406E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>308</v>
       </c>
@@ -16658,7 +16661,7 @@
         <v>8.42642456111901E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>309</v>
       </c>
@@ -16669,7 +16672,7 @@
         <v>8.3954508319290494E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>310</v>
       </c>
@@ -16680,7 +16683,7 @@
         <v>8.4241621326531999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>311</v>
       </c>
@@ -16691,7 +16694,7 @@
         <v>8.39433811384213E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>312</v>
       </c>
@@ -16702,7 +16705,7 @@
         <v>8.4883882170655206E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>313</v>
       </c>
@@ -16713,7 +16716,7 @@
         <v>8.4153042797615304E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>314</v>
       </c>
@@ -16724,7 +16727,7 @@
         <v>6.4664938143317294E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>315</v>
       </c>
@@ -16735,7 +16738,7 @@
         <v>6.48925563524336E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>316</v>
       </c>
@@ -16746,7 +16749,7 @@
         <v>6.4717624366303003E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>317</v>
       </c>
@@ -16757,7 +16760,7 @@
         <v>6.5096945322289101E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>318</v>
       </c>
@@ -16768,7 +16771,7 @@
         <v>6.4780635694392893E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>319</v>
       </c>
@@ -16779,7 +16782,7 @@
         <v>6.4828747039054904E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>320</v>
       </c>
@@ -16790,7 +16793,7 @@
         <v>6.4845896931015903E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>321</v>
       </c>
@@ -16801,7 +16804,7 @@
         <v>6.4898532838035997E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>322</v>
       </c>
@@ -16812,7 +16815,7 @@
         <v>6.4393394651674596E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>323</v>
       </c>
@@ -16823,7 +16826,7 @@
         <v>6.4836933722996301E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>324</v>
       </c>
@@ -16834,7 +16837,7 @@
         <v>6.4898123293677099E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>325</v>
       </c>
@@ -16845,7 +16848,7 @@
         <v>6.48141939607636E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>326</v>
       </c>
@@ -16856,7 +16859,7 @@
         <v>6.4945690313312696E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>327</v>
       </c>
@@ -16867,7 +16870,7 @@
         <v>6.4750632359324503E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>328</v>
       </c>
@@ -16878,7 +16881,7 @@
         <v>6.46466961945657E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>329</v>
       </c>
@@ -16889,7 +16892,7 @@
         <v>6.5070391277710998E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>330</v>
       </c>
@@ -16900,7 +16903,7 @@
         <v>6.5003508402351404E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>331</v>
       </c>
@@ -16911,7 +16914,7 @@
         <v>6.4702157939462199E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>332</v>
       </c>
@@ -16922,7 +16925,7 @@
         <v>6.4789520162763903E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>333</v>
       </c>
@@ -16933,7 +16936,7 @@
         <v>6.4698100702121605E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>334</v>
       </c>
@@ -16944,7 +16947,7 @@
         <v>6.39060983563466E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>335</v>
       </c>
@@ -16955,7 +16958,7 @@
         <v>6.4217223623450101E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>336</v>
       </c>
@@ -16966,7 +16969,7 @@
         <v>6.4146735969449406E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>337</v>
       </c>
@@ -16977,7 +16980,7 @@
         <v>6.4629796704458606E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>338</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>6.43943878164248E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>339</v>
       </c>
@@ -16999,7 +17002,7 @@
         <v>6.4478725052475205E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>340</v>
       </c>
@@ -17010,7 +17013,7 @@
         <v>6.4781321835991806E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>341</v>
       </c>
@@ -17021,7 +17024,7 @@
         <v>6.4392626905219894E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>342</v>
       </c>
@@ -17032,7 +17035,7 @@
         <v>6.4250407980306304E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>343</v>
       </c>
@@ -17043,7 +17046,7 @@
         <v>6.4167196154649705E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>344</v>
       </c>
@@ -17054,7 +17057,7 @@
         <v>6.4208136070914995E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>345</v>
       </c>
@@ -17065,7 +17068,7 @@
         <v>6.4378306448205899E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>346</v>
       </c>
@@ -17076,7 +17079,7 @@
         <v>6.4317608614747404E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>347</v>
       </c>
@@ -17087,7 +17090,7 @@
         <v>6.3677492575877404E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>348</v>
       </c>
@@ -17107,13 +17110,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -17150,7 +17153,7 @@
         <v>2.8613971962500952E-4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -17187,7 +17190,7 @@
         <v>0.12997532261023939</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -17218,7 +17221,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -17249,7 +17252,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -17280,7 +17283,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -17311,7 +17314,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -17342,7 +17345,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -17373,7 +17376,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -17400,7 +17403,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -17425,7 +17428,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -17448,7 +17451,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -17471,7 +17474,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -17494,7 +17497,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -17517,7 +17520,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -17540,7 +17543,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -17563,7 +17566,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -17586,7 +17589,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -17609,7 +17612,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -17631,7 +17634,7 @@
         <v>0.22239501023331501</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -17653,7 +17656,7 @@
         <v>0.22148912103303101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -17675,7 +17678,7 @@
         <v>0.21932862474141701</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -17695,7 +17698,7 @@
         <v>0.221461481179243</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -17715,7 +17718,7 @@
         <v>0.22005818833098301</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -17734,7 +17737,7 @@
         <v>0.218777420016466</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -17753,7 +17756,7 @@
         <v>0.22017842865582701</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -17772,7 +17775,7 @@
         <v>0.21788210076678599</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -17791,7 +17794,7 @@
         <v>0.219800999056638</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -17810,7 +17813,7 @@
         <v>0.218443725860095</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -17826,7 +17829,7 @@
         <v>0.21984807108405599</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -17842,7 +17845,7 @@
         <v>0.21905089922811899</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -17858,7 +17861,7 @@
         <v>0.220804530471746</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -17874,7 +17877,7 @@
         <v>0.22042567690074599</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -17890,7 +17893,7 @@
         <v>0.22236680616370999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -17906,7 +17909,7 @@
         <v>0.219474041342478</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -17919,7 +17922,7 @@
         <v>0.22174008177054699</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -17928,7 +17931,7 @@
         <v>0.220246153111534</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -17937,7 +17940,7 @@
         <v>0.21859609431965099</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -17946,7 +17949,7 @@
         <v>0.22158291221496201</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -17962,12 +17965,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -18004,7 +18007,7 @@
         <v>1.4794192860515082E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -18041,7 +18044,7 @@
         <v>0.1090690310547095</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -18072,7 +18075,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -18103,7 +18106,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -18134,7 +18137,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -18165,7 +18168,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -18196,7 +18199,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -18227,7 +18230,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -18254,7 +18257,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -18279,7 +18282,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -18302,7 +18305,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -18325,7 +18328,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -18348,7 +18351,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -18371,7 +18374,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -18394,7 +18397,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -18417,7 +18420,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -18440,7 +18443,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -18463,7 +18466,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -18485,7 +18488,7 @@
         <v>13.5963637628518</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -18507,7 +18510,7 @@
         <v>13.6061621269385</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -18529,7 +18532,7 @@
         <v>13.564508484015001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -18549,7 +18552,7 @@
         <v>13.566012885219999</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -18569,7 +18572,7 @@
         <v>13.677050331463599</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -18588,7 +18591,7 @@
         <v>13.697864550150999</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -18607,7 +18610,7 @@
         <v>13.521765815989101</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -18626,7 +18629,7 @@
         <v>13.5769688965988</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -18645,7 +18648,7 @@
         <v>13.480301532390399</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -18664,7 +18667,7 @@
         <v>13.457843174234499</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -18680,7 +18683,7 @@
         <v>13.4601858284096</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -18696,7 +18699,7 @@
         <v>13.441398970797801</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -18712,7 +18715,7 @@
         <v>13.4597843604533</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -18728,7 +18731,7 @@
         <v>13.5606966844732</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -18744,7 +18747,7 @@
         <v>13.566424750775999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -18760,7 +18763,7 @@
         <v>13.677756444678201</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -18773,7 +18776,7 @@
         <v>13.7089668474497</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -18782,7 +18785,7 @@
         <v>13.5896342791272</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -18791,7 +18794,7 @@
         <v>13.672859971194899</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -18800,7 +18803,7 @@
         <v>13.4234538610926</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DBB335-98CE-4F06-9EE6-88837AFDAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C416F13-A814-4B7A-983F-57B391AB54A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="403">
   <si>
     <t>May22,2026+11-50-22AM</t>
   </si>
@@ -1086,6 +1086,168 @@
   </si>
   <si>
     <t>Jul16,2026+3-07-41PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+9-22-07AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+9-31-00AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+9-41-35AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+9-49-58AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+10-27-37AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+10-36-34AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+10-46-28AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+10-55-02AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+11-07-36AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+11-48-33AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+11-57-12AM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-05-38PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-13-37PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-23-46PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-32-11PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-40-09PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+12-55-22PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+1-03-13PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+1-11-44PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+1-20-36PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+1-29-25PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+1-58-46PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+2-36-50PM</t>
+  </si>
+  <si>
+    <t>Jul17,2026+2-55-06PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+8-55-20AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+9-11-06AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+9-22-21AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+9-31-37AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+9-39-29AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+9-47-32AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+10-12-30AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+10-41-07AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+10-50-14AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+11-07-43AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+11-22-46AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+11-34-16AM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-00-50PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-08-44PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-16-50PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-36-12PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-46-27PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+12-54-20PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+1-02-19PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+1-10-02PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+1-17-52PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+1-25-36PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+1-46-04PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+2-51-19PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+3-10-27PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+3-25-37PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+3-39-36PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+3-47-19PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+4-00-07PM</t>
+  </si>
+  <si>
+    <t>Jul20,2026+4-10-22PM</t>
   </si>
 </sst>
 </file>
@@ -3960,6 +4122,448 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-E04E-4239-AE72-E247FFFE8129}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:v>17-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$338:$B$361</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>6.5540355078319896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5827244241657299</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6067856280796899</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5726574723992401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.60849329589227</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.61449436632694</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.5773613187522404</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.6014893245484396</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.5572879597699503</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.6008191975600301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.6252507343515497</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5704906061544399</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.5936568893976704</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5983973262679001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.6115893763595901</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.5582265339750796</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.5712631537936099</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.6270719261065301</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.6192410240628501</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.57641937555222</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.6087667968385899</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.5350348620169401</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.5557760188699499</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.5032195210687904</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$338:$C$361</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.105551348978041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.105991123494967</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10533604175596301</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.105665444142923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.105198678205429</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.105495395727284</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.105314548416934</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10568145895007799</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10527614250211299</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.10576449952939899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.10568293315542</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.10581148690660699</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.105635832709833</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.105645315996043</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.105275447604903</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.105662668847811</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.105625257618033</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.106115800022815</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.106389444933465</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.105686237933491</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.106107125977925</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.10569305527527301</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.105721916432143</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.10501733793063001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8960-4FD8-864C-A05C95AA4FC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:v>20-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$362:$B$391</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>5.9622611291336396</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.0066466306228703</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.9421219928096498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.97435305885893</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9503505932316996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.9548297693894297</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.9553030366034303</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.9714415945772101</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9546595386126704</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9526717332290202</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.9925762983853099</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.9607737827043099</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.9798136479539004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.9855117155737396</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.0292733180363696</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.9440797542562098</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.9637069175640898</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.9851248839214604</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.9753311000708296</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.95595351810669</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.9436339167314696</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.9680724903054401</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.97890051441588</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.9641145262355701</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.9548137587277301</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.9412161279185698</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.9237749973025897</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.9321677454244002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.9655682681986404</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.9648566611082501</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$362:$C$391</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>9.4951214409789694E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.48427612752826E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5323780436117694E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.5239680372887395E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.4913957126963905E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5207811574283305E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5333549341072299E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.5272929905971096E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.5825730092529093E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5557760398135405E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.5707695616314301E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.5513472864986904E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.5307639125115001E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.6102530139334702E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.5842612321962603E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.5502184039375396E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.5885385701222001E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.6439591076729503E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.5315139971463694E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.5613752572800206E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.57329103303277E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9.4740461511437099E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.56068005906138E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.5241121615471297E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.5433597155929403E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.5987289369727502E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.5313166809118E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.5108590519696196E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.5279653817559096E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.5070431421425905E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8960-4FD8-864C-A05C95AA4FC9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12860,16 +13464,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>539750</xdr:rowOff>
+      <xdr:rowOff>273050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13314,7 +13918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
-  <dimension ref="A1:N337"/>
+  <dimension ref="A1:N391"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -17099,6 +17703,600 @@
       </c>
       <c r="C337" s="1">
         <v>6.3641331008131394E-2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B338" s="1">
+        <v>6.5540355078319896</v>
+      </c>
+      <c r="C338" s="1">
+        <v>0.105551348978041</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B339" s="1">
+        <v>6.5827244241657299</v>
+      </c>
+      <c r="C339" s="1">
+        <v>0.105991123494967</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B340" s="1">
+        <v>6.6067856280796899</v>
+      </c>
+      <c r="C340" s="1">
+        <v>0.10533604175596301</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B341" s="1">
+        <v>6.5726574723992401</v>
+      </c>
+      <c r="C341" s="1">
+        <v>0.105665444142923</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B342" s="1">
+        <v>6.60849329589227</v>
+      </c>
+      <c r="C342" s="1">
+        <v>0.105198678205429</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B343" s="1">
+        <v>6.61449436632694</v>
+      </c>
+      <c r="C343" s="1">
+        <v>0.105495395727284</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B344" s="1">
+        <v>6.5773613187522404</v>
+      </c>
+      <c r="C344" s="1">
+        <v>0.105314548416934</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B345" s="1">
+        <v>6.6014893245484396</v>
+      </c>
+      <c r="C345" s="1">
+        <v>0.10568145895007799</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B346" s="1">
+        <v>6.5572879597699503</v>
+      </c>
+      <c r="C346" s="1">
+        <v>0.10527614250211299</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B347" s="1">
+        <v>6.6008191975600301</v>
+      </c>
+      <c r="C347" s="1">
+        <v>0.10576449952939899</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B348" s="1">
+        <v>6.6252507343515497</v>
+      </c>
+      <c r="C348" s="1">
+        <v>0.10568293315542</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B349" s="1">
+        <v>6.5704906061544399</v>
+      </c>
+      <c r="C349" s="1">
+        <v>0.10581148690660699</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B350" s="1">
+        <v>6.5936568893976704</v>
+      </c>
+      <c r="C350" s="1">
+        <v>0.105635832709833</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B351" s="1">
+        <v>6.5983973262679001</v>
+      </c>
+      <c r="C351" s="1">
+        <v>0.105645315996043</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B352" s="1">
+        <v>6.6115893763595901</v>
+      </c>
+      <c r="C352" s="1">
+        <v>0.105275447604903</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B353" s="1">
+        <v>6.5582265339750796</v>
+      </c>
+      <c r="C353" s="1">
+        <v>0.105662668847811</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B354" s="1">
+        <v>6.5712631537936099</v>
+      </c>
+      <c r="C354" s="1">
+        <v>0.105625257618033</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B355" s="1">
+        <v>6.6270719261065301</v>
+      </c>
+      <c r="C355" s="1">
+        <v>0.106115800022815</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B356" s="1">
+        <v>6.6192410240628501</v>
+      </c>
+      <c r="C356" s="1">
+        <v>0.106389444933465</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B357" s="1">
+        <v>6.57641937555222</v>
+      </c>
+      <c r="C357" s="1">
+        <v>0.105686237933491</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B358" s="1">
+        <v>6.6087667968385899</v>
+      </c>
+      <c r="C358" s="1">
+        <v>0.106107125977925</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B359" s="1">
+        <v>6.5350348620169401</v>
+      </c>
+      <c r="C359" s="1">
+        <v>0.10569305527527301</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B360" s="1">
+        <v>6.5557760188699499</v>
+      </c>
+      <c r="C360" s="1">
+        <v>0.105721916432143</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B361" s="1">
+        <v>6.5032195210687904</v>
+      </c>
+      <c r="C361" s="1">
+        <v>0.10501733793063001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B362" s="1">
+        <v>5.9622611291336396</v>
+      </c>
+      <c r="C362" s="1">
+        <v>9.4951214409789694E-2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B363" s="1">
+        <v>6.0066466306228703</v>
+      </c>
+      <c r="C363" s="1">
+        <v>9.48427612752826E-2</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B364" s="1">
+        <v>5.9421219928096498</v>
+      </c>
+      <c r="C364" s="1">
+        <v>9.5323780436117694E-2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B365" s="1">
+        <v>5.97435305885893</v>
+      </c>
+      <c r="C365" s="1">
+        <v>9.5239680372887395E-2</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B366" s="1">
+        <v>5.9503505932316996</v>
+      </c>
+      <c r="C366" s="1">
+        <v>9.4913957126963905E-2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B367" s="1">
+        <v>5.9548297693894297</v>
+      </c>
+      <c r="C367" s="1">
+        <v>9.5207811574283305E-2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B368" s="1">
+        <v>5.9553030366034303</v>
+      </c>
+      <c r="C368" s="1">
+        <v>9.5333549341072299E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B369" s="1">
+        <v>5.9714415945772101</v>
+      </c>
+      <c r="C369" s="1">
+        <v>9.5272929905971096E-2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B370" s="1">
+        <v>5.9546595386126704</v>
+      </c>
+      <c r="C370" s="1">
+        <v>9.5825730092529093E-2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B371" s="1">
+        <v>5.9526717332290202</v>
+      </c>
+      <c r="C371" s="1">
+        <v>9.5557760398135405E-2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B372" s="1">
+        <v>5.9925762983853099</v>
+      </c>
+      <c r="C372" s="1">
+        <v>9.5707695616314301E-2</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B373" s="1">
+        <v>5.9607737827043099</v>
+      </c>
+      <c r="C373" s="1">
+        <v>9.5513472864986904E-2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B374" s="1">
+        <v>5.9798136479539004</v>
+      </c>
+      <c r="C374" s="1">
+        <v>9.5307639125115001E-2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B375" s="1">
+        <v>5.9855117155737396</v>
+      </c>
+      <c r="C375" s="1">
+        <v>9.6102530139334702E-2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B376" s="1">
+        <v>6.0292733180363696</v>
+      </c>
+      <c r="C376" s="1">
+        <v>9.5842612321962603E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B377" s="1">
+        <v>5.9440797542562098</v>
+      </c>
+      <c r="C377" s="1">
+        <v>9.5502184039375396E-2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B378" s="1">
+        <v>5.9637069175640898</v>
+      </c>
+      <c r="C378" s="1">
+        <v>9.5885385701222001E-2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B379" s="1">
+        <v>5.9851248839214604</v>
+      </c>
+      <c r="C379" s="1">
+        <v>9.6439591076729503E-2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B380" s="1">
+        <v>5.9753311000708296</v>
+      </c>
+      <c r="C380" s="1">
+        <v>9.5315139971463694E-2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B381" s="1">
+        <v>5.95595351810669</v>
+      </c>
+      <c r="C381" s="1">
+        <v>9.5613752572800206E-2</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B382" s="1">
+        <v>5.9436339167314696</v>
+      </c>
+      <c r="C382" s="1">
+        <v>9.57329103303277E-2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B383" s="1">
+        <v>5.9680724903054401</v>
+      </c>
+      <c r="C383" s="1">
+        <v>9.4740461511437099E-2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B384" s="1">
+        <v>5.97890051441588</v>
+      </c>
+      <c r="C384" s="1">
+        <v>9.56068005906138E-2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B385" s="1">
+        <v>5.9641145262355701</v>
+      </c>
+      <c r="C385" s="1">
+        <v>9.5241121615471297E-2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B386" s="1">
+        <v>5.9548137587277301</v>
+      </c>
+      <c r="C386" s="1">
+        <v>9.5433597155929403E-2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B387" s="1">
+        <v>5.9412161279185698</v>
+      </c>
+      <c r="C387" s="1">
+        <v>9.5987289369727502E-2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B388" s="1">
+        <v>5.9237749973025897</v>
+      </c>
+      <c r="C388" s="1">
+        <v>9.5313166809118E-2</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B389" s="1">
+        <v>5.9321677454244002</v>
+      </c>
+      <c r="C389" s="1">
+        <v>9.5108590519696196E-2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B390" s="1">
+        <v>5.9655682681986404</v>
+      </c>
+      <c r="C390" s="1">
+        <v>9.5279653817559096E-2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B391" s="1">
+        <v>5.9648566611082501</v>
+      </c>
+      <c r="C391" s="1">
+        <v>9.5070431421425905E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C416F13-A814-4B7A-983F-57B391AB54A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09B28F3-B141-4BFA-846C-FBC4A3F9103D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="433">
   <si>
     <t>May22,2026+11-50-22AM</t>
   </si>
@@ -848,9 +848,6 @@
     <t>Jul14,2026+12-14-44PM</t>
   </si>
   <si>
-    <t>Jul14,2026+12-26-20PM</t>
-  </si>
-  <si>
     <t>Jul14,2026+12-34-37PM</t>
   </si>
   <si>
@@ -1157,9 +1154,6 @@
     <t>Jul17,2026+2-36-50PM</t>
   </si>
   <si>
-    <t>Jul17,2026+2-55-06PM</t>
-  </si>
-  <si>
     <t>Jul20,2026+8-55-20AM</t>
   </si>
   <si>
@@ -1248,6 +1242,102 @@
   </si>
   <si>
     <t>Jul20,2026+4-10-22PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-09-03AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-17-16AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-25-02AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-32-41AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-40-56AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+9-52-24AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+10-04-37AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+10-41-13AM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+12-09-01PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+12-43-22PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+12-53-22PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+1-01-31PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+1-09-11PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+1-30-31PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+1-40-05PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+1-58-35PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+2-08-08PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+2-15-55PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+2-23-55PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+2-32-03PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-10-36PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-18-15PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-26-50PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-34-26PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-42-02PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-49-49PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+3-57-30PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+4-05-10PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+4-20-56PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+4-31-22PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+4-38-59PM</t>
+  </si>
+  <si>
+    <t>Jul21,2026+4-46-38PM</t>
   </si>
 </sst>
 </file>
@@ -3498,74 +3588,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>All!$B$257:$B$278</c:f>
+              <c:f>All!$B$257:$B$277</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>5.2258479562069899</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.1321123174082999</c:v>
+                  <c:v>5.2437157298636796</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.2437157298636796</c:v>
+                  <c:v>5.2504871284328898</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.2504871284328898</c:v>
+                  <c:v>5.2503356968257</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.2503356968257</c:v>
+                  <c:v>5.2336543988027202</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.2336543988027202</c:v>
+                  <c:v>5.2591832551717097</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2591832551717097</c:v>
+                  <c:v>5.2469052817766597</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.2469052817766597</c:v>
+                  <c:v>5.25892843081182</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.25892843081182</c:v>
+                  <c:v>5.21286007784256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.21286007784256</c:v>
+                  <c:v>5.2596778259212398</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.2596778259212398</c:v>
+                  <c:v>5.2590212289624798</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.2590212289624798</c:v>
+                  <c:v>5.2296998738747797</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.2296998738747797</c:v>
+                  <c:v>5.2667771366869696</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.2667771366869696</c:v>
+                  <c:v>5.2271473404603404</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.2271473404603404</c:v>
+                  <c:v>5.2172814151544804</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.2172814151544804</c:v>
+                  <c:v>5.2026205255307998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.2026205255307998</c:v>
+                  <c:v>5.2088502809019603</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.2088502809019603</c:v>
+                  <c:v>5.2306348705772896</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.2306348705772896</c:v>
+                  <c:v>5.2252366536496302</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.2252366536496302</c:v>
+                  <c:v>5.2416884024595696</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.2416884024595696</c:v>
-                </c:pt>
-                <c:pt idx="21">
                   <c:v>5.2293252887733699</c:v>
                 </c:pt>
               </c:numCache>
@@ -3573,74 +3660,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>All!$C$257:$C$278</c:f>
+              <c:f>All!$C$257:$C$277</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>8.4098670481367904E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.3770582022428597E-2</c:v>
+                  <c:v>8.3930571430078399E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.3930571430078399E-2</c:v>
+                  <c:v>8.4386871474939104E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.4386871474939104E-2</c:v>
+                  <c:v>8.3779094698236606E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.3779094698236606E-2</c:v>
+                  <c:v>8.4368245251587398E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.4368245251587398E-2</c:v>
+                  <c:v>8.4640740114124396E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.4640740114124396E-2</c:v>
+                  <c:v>8.3819572528152295E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.3819572528152295E-2</c:v>
+                  <c:v>8.4298501986348195E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.4298501986348195E-2</c:v>
+                  <c:v>8.3749879844150901E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3749879844150901E-2</c:v>
+                  <c:v>8.4288203419773597E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.4288203419773597E-2</c:v>
+                  <c:v>8.4433783424020706E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.4433783424020706E-2</c:v>
+                  <c:v>8.3978129655986694E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.3978129655986694E-2</c:v>
+                  <c:v>8.4391376865179599E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.4391376865179599E-2</c:v>
+                  <c:v>8.3986778727553404E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.3986778727553404E-2</c:v>
+                  <c:v>8.3700704517771493E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.3700704517771493E-2</c:v>
+                  <c:v>8.3337504828946599E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.3337504828946599E-2</c:v>
+                  <c:v>8.4048471187493506E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.4048471187493506E-2</c:v>
+                  <c:v>8.3859299335631896E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.3859299335631896E-2</c:v>
+                  <c:v>8.4150599797561301E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.4150599797561301E-2</c:v>
+                  <c:v>8.3705403747337398E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.3705403747337398E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
                   <c:v>8.38953398940607E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -3689,7 +3773,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>All!$B$279:$B$302</c:f>
+              <c:f>All!$B$278:$B$301</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -3770,7 +3854,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>All!$C$279:$C$302</c:f>
+              <c:f>All!$C$278:$C$301</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -3892,7 +3976,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>All!$B$303:$B$337</c:f>
+              <c:f>All!$B$302:$B$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -4006,7 +4090,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>All!$C$303:$C$337</c:f>
+              <c:f>All!$C$302:$C$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -4161,10 +4245,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>All!$B$338:$B$361</c:f>
+              <c:f>All!$B$337:$B$359</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>6.5540355078319896</c:v>
                 </c:pt>
@@ -4233,19 +4317,16 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>6.5557760188699499</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.5032195210687904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>All!$C$338:$C$361</c:f>
+              <c:f>All!$C$337:$C$359</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.105551348978041</c:v>
                 </c:pt>
@@ -4314,9 +4395,6 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.105721916432143</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.10501733793063001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4364,7 +4442,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>All!$B$362:$B$391</c:f>
+              <c:f>All!$B$360:$B$389</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
@@ -4463,7 +4541,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>All!$C$362:$C$391</c:f>
+              <c:f>All!$C$360:$C$389</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
@@ -4564,6 +4642,257 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-8960-4FD8-864C-A05C95AA4FC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="16"/>
+          <c:order val="16"/>
+          <c:tx>
+            <c:v>21-Jul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All!$B$390:$B$421</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>3.0672817324059798</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.06498328697809</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.06753441554193</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0756019900176499</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0649036050172098</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.06529341587372</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0726606549971298</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.0831176610414701</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0668965665752701</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0577539539137901</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.0461287705788598</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.0420177016521102</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0577648925430601</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.07207699092403</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.0603120961688499</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.0495273783215602</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.0483213432966099</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.0507028081060601</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0503873160495498</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.0616213771126799</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.0441812745358798</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.0545733491419398</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.0565111313221198</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.0569612836170998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.0531280697850698</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.0495276887412501</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.0451824247254602</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.0636069285517098</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.0573709331599099</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.0482345249944598</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.0486121479316401</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.0547580292283598</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All!$C$390:$C$421</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>4.9220544832568401E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.8826525513616603E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9256122272570202E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.97179954883646E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9725118840505199E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9381962862556E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.8979944321647401E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.9045485231240298E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.8965298287210399E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.8957627310304702E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.9000057015244597E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.8651617087087401E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.8810930819998197E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.8901071369119802E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.9126205451321202E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.95058693259324E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.8651769164606402E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.8908241247632697E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.8699146330509702E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.91555175312548E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.9268660787059597E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.8826826414769098E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.8764627198113697E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.9029160899217702E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.8854122518207498E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.9133881801381701E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.9071806924917999E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.9142870700877098E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.9249210174874901E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.8951873888496603E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.8933368456572202E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.87619094275357E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E732-4D6D-A1BB-56358B21E154}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13918,7 +14247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAAD8A8-384F-4377-BC44-2ABC2E3B55D8}">
-  <dimension ref="A1:N391"/>
+  <dimension ref="A1:N421"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -16830,10 +17159,10 @@
         <v>269</v>
       </c>
       <c r="B258" s="1">
-        <v>5.1321123174082999</v>
+        <v>5.2437157298636796</v>
       </c>
       <c r="C258" s="1">
-        <v>8.3770582022428597E-2</v>
+        <v>8.3930571430078399E-2</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16841,10 +17170,10 @@
         <v>270</v>
       </c>
       <c r="B259" s="1">
-        <v>5.2437157298636796</v>
+        <v>5.2504871284328898</v>
       </c>
       <c r="C259" s="1">
-        <v>8.3930571430078399E-2</v>
+        <v>8.4386871474939104E-2</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16852,10 +17181,10 @@
         <v>271</v>
       </c>
       <c r="B260" s="1">
-        <v>5.2504871284328898</v>
+        <v>5.2503356968257</v>
       </c>
       <c r="C260" s="1">
-        <v>8.4386871474939104E-2</v>
+        <v>8.3779094698236606E-2</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16863,10 +17192,10 @@
         <v>272</v>
       </c>
       <c r="B261" s="1">
-        <v>5.2503356968257</v>
+        <v>5.2336543988027202</v>
       </c>
       <c r="C261" s="1">
-        <v>8.3779094698236606E-2</v>
+        <v>8.4368245251587398E-2</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16874,10 +17203,10 @@
         <v>273</v>
       </c>
       <c r="B262" s="1">
-        <v>5.2336543988027202</v>
+        <v>5.2591832551717097</v>
       </c>
       <c r="C262" s="1">
-        <v>8.4368245251587398E-2</v>
+        <v>8.4640740114124396E-2</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16885,10 +17214,10 @@
         <v>274</v>
       </c>
       <c r="B263" s="1">
-        <v>5.2591832551717097</v>
+        <v>5.2469052817766597</v>
       </c>
       <c r="C263" s="1">
-        <v>8.4640740114124396E-2</v>
+        <v>8.3819572528152295E-2</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16896,10 +17225,10 @@
         <v>275</v>
       </c>
       <c r="B264" s="1">
-        <v>5.2469052817766597</v>
+        <v>5.25892843081182</v>
       </c>
       <c r="C264" s="1">
-        <v>8.3819572528152295E-2</v>
+        <v>8.4298501986348195E-2</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16907,10 +17236,10 @@
         <v>276</v>
       </c>
       <c r="B265" s="1">
-        <v>5.25892843081182</v>
+        <v>5.21286007784256</v>
       </c>
       <c r="C265" s="1">
-        <v>8.4298501986348195E-2</v>
+        <v>8.3749879844150901E-2</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16918,10 +17247,10 @@
         <v>277</v>
       </c>
       <c r="B266" s="1">
-        <v>5.21286007784256</v>
+        <v>5.2596778259212398</v>
       </c>
       <c r="C266" s="1">
-        <v>8.3749879844150901E-2</v>
+        <v>8.4288203419773597E-2</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16929,10 +17258,10 @@
         <v>278</v>
       </c>
       <c r="B267" s="1">
-        <v>5.2596778259212398</v>
+        <v>5.2590212289624798</v>
       </c>
       <c r="C267" s="1">
-        <v>8.4288203419773597E-2</v>
+        <v>8.4433783424020706E-2</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16940,10 +17269,10 @@
         <v>279</v>
       </c>
       <c r="B268" s="1">
-        <v>5.2590212289624798</v>
+        <v>5.2296998738747797</v>
       </c>
       <c r="C268" s="1">
-        <v>8.4433783424020706E-2</v>
+        <v>8.3978129655986694E-2</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16951,10 +17280,10 @@
         <v>280</v>
       </c>
       <c r="B269" s="1">
-        <v>5.2296998738747797</v>
+        <v>5.2667771366869696</v>
       </c>
       <c r="C269" s="1">
-        <v>8.3978129655986694E-2</v>
+        <v>8.4391376865179599E-2</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16962,10 +17291,10 @@
         <v>281</v>
       </c>
       <c r="B270" s="1">
-        <v>5.2667771366869696</v>
+        <v>5.2271473404603404</v>
       </c>
       <c r="C270" s="1">
-        <v>8.4391376865179599E-2</v>
+        <v>8.3986778727553404E-2</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16973,10 +17302,10 @@
         <v>282</v>
       </c>
       <c r="B271" s="1">
-        <v>5.2271473404603404</v>
+        <v>5.2172814151544804</v>
       </c>
       <c r="C271" s="1">
-        <v>8.3986778727553404E-2</v>
+        <v>8.3700704517771493E-2</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16984,10 +17313,10 @@
         <v>283</v>
       </c>
       <c r="B272" s="1">
-        <v>5.2172814151544804</v>
+        <v>5.2026205255307998</v>
       </c>
       <c r="C272" s="1">
-        <v>8.3700704517771493E-2</v>
+        <v>8.3337504828946599E-2</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -16995,10 +17324,10 @@
         <v>284</v>
       </c>
       <c r="B273" s="1">
-        <v>5.2026205255307998</v>
+        <v>5.2088502809019603</v>
       </c>
       <c r="C273" s="1">
-        <v>8.3337504828946599E-2</v>
+        <v>8.4048471187493506E-2</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17006,10 +17335,10 @@
         <v>285</v>
       </c>
       <c r="B274" s="1">
-        <v>5.2088502809019603</v>
+        <v>5.2306348705772896</v>
       </c>
       <c r="C274" s="1">
-        <v>8.4048471187493506E-2</v>
+        <v>8.3859299335631896E-2</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17017,10 +17346,10 @@
         <v>286</v>
       </c>
       <c r="B275" s="1">
-        <v>5.2306348705772896</v>
+        <v>5.2252366536496302</v>
       </c>
       <c r="C275" s="1">
-        <v>8.3859299335631896E-2</v>
+        <v>8.4150599797561301E-2</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17028,10 +17357,10 @@
         <v>287</v>
       </c>
       <c r="B276" s="1">
-        <v>5.2252366536496302</v>
+        <v>5.2416884024595696</v>
       </c>
       <c r="C276" s="1">
-        <v>8.4150599797561301E-2</v>
+        <v>8.3705403747337398E-2</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17039,10 +17368,10 @@
         <v>288</v>
       </c>
       <c r="B277" s="1">
-        <v>5.2416884024595696</v>
+        <v>5.2293252887733699</v>
       </c>
       <c r="C277" s="1">
-        <v>8.3705403747337398E-2</v>
+        <v>8.38953398940607E-2</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17050,10 +17379,10 @@
         <v>289</v>
       </c>
       <c r="B278" s="1">
-        <v>5.2293252887733699</v>
+        <v>5.2401573655099698</v>
       </c>
       <c r="C278" s="1">
-        <v>8.38953398940607E-2</v>
+        <v>8.4020421663362793E-2</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17061,10 +17390,10 @@
         <v>290</v>
       </c>
       <c r="B279" s="1">
-        <v>5.2401573655099698</v>
+        <v>5.2402095305102501</v>
       </c>
       <c r="C279" s="1">
-        <v>8.4020421663362793E-2</v>
+        <v>8.3856539409502107E-2</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17072,10 +17401,10 @@
         <v>291</v>
       </c>
       <c r="B280" s="1">
-        <v>5.2402095305102501</v>
+        <v>5.2325481598897898</v>
       </c>
       <c r="C280" s="1">
-        <v>8.3856539409502107E-2</v>
+        <v>8.4441497497705006E-2</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17083,10 +17412,10 @@
         <v>292</v>
       </c>
       <c r="B281" s="1">
-        <v>5.2325481598897898</v>
+        <v>5.2632048700287699</v>
       </c>
       <c r="C281" s="1">
-        <v>8.4441497497705006E-2</v>
+        <v>8.3922207540377103E-2</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17094,10 +17423,10 @@
         <v>293</v>
       </c>
       <c r="B282" s="1">
-        <v>5.2632048700287699</v>
+        <v>5.2341542225512701</v>
       </c>
       <c r="C282" s="1">
-        <v>8.3922207540377103E-2</v>
+        <v>8.3819979532311101E-2</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17105,10 +17434,10 @@
         <v>294</v>
       </c>
       <c r="B283" s="1">
-        <v>5.2341542225512701</v>
+        <v>5.2499074678307798</v>
       </c>
       <c r="C283" s="1">
-        <v>8.3819979532311101E-2</v>
+        <v>8.4065913892834104E-2</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17116,10 +17445,10 @@
         <v>295</v>
       </c>
       <c r="B284" s="1">
-        <v>5.2499074678307798</v>
+        <v>5.2609478156281302</v>
       </c>
       <c r="C284" s="1">
-        <v>8.4065913892834104E-2</v>
+        <v>8.4094869806041694E-2</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17127,10 +17456,10 @@
         <v>296</v>
       </c>
       <c r="B285" s="1">
-        <v>5.2609478156281302</v>
+        <v>5.2522638411999596</v>
       </c>
       <c r="C285" s="1">
-        <v>8.4094869806041694E-2</v>
+        <v>8.3498425913598198E-2</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17138,10 +17467,10 @@
         <v>297</v>
       </c>
       <c r="B286" s="1">
-        <v>5.2522638411999596</v>
+        <v>5.2381148673874796</v>
       </c>
       <c r="C286" s="1">
-        <v>8.3498425913598198E-2</v>
+        <v>8.3501392552088799E-2</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17149,10 +17478,10 @@
         <v>298</v>
       </c>
       <c r="B287" s="1">
-        <v>5.2381148673874796</v>
+        <v>5.2236574261532196</v>
       </c>
       <c r="C287" s="1">
-        <v>8.3501392552088799E-2</v>
+        <v>8.3538886283743397E-2</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17160,10 +17489,10 @@
         <v>299</v>
       </c>
       <c r="B288" s="1">
-        <v>5.2236574261532196</v>
+        <v>5.2262449444555799</v>
       </c>
       <c r="C288" s="1">
-        <v>8.3538886283743397E-2</v>
+        <v>8.3653316711863296E-2</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17171,10 +17500,10 @@
         <v>300</v>
       </c>
       <c r="B289" s="1">
-        <v>5.2262449444555799</v>
+        <v>5.2457271314303799</v>
       </c>
       <c r="C289" s="1">
-        <v>8.3653316711863296E-2</v>
+        <v>8.36218907831483E-2</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17182,10 +17511,10 @@
         <v>301</v>
       </c>
       <c r="B290" s="1">
-        <v>5.2457271314303799</v>
+        <v>5.2597760818477397</v>
       </c>
       <c r="C290" s="1">
-        <v>8.36218907831483E-2</v>
+        <v>8.3768728051409405E-2</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17193,10 +17522,10 @@
         <v>302</v>
       </c>
       <c r="B291" s="1">
-        <v>5.2597760818477397</v>
+        <v>5.2273625593786797</v>
       </c>
       <c r="C291" s="1">
-        <v>8.3768728051409405E-2</v>
+        <v>8.3798815283381206E-2</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17204,10 +17533,10 @@
         <v>303</v>
       </c>
       <c r="B292" s="1">
-        <v>5.2273625593786797</v>
+        <v>5.2281725990355099</v>
       </c>
       <c r="C292" s="1">
-        <v>8.3798815283381206E-2</v>
+        <v>8.37952938220691E-2</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17215,10 +17544,10 @@
         <v>304</v>
       </c>
       <c r="B293" s="1">
-        <v>5.2281725990355099</v>
+        <v>5.2464873820867899</v>
       </c>
       <c r="C293" s="1">
-        <v>8.37952938220691E-2</v>
+        <v>8.4084000178888202E-2</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17226,10 +17555,10 @@
         <v>305</v>
       </c>
       <c r="B294" s="1">
-        <v>5.2464873820867899</v>
+        <v>5.2357499987829099</v>
       </c>
       <c r="C294" s="1">
-        <v>8.4084000178888202E-2</v>
+        <v>8.4478909636109295E-2</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17237,10 +17566,10 @@
         <v>306</v>
       </c>
       <c r="B295" s="1">
-        <v>5.2357499987829099</v>
+        <v>5.2426137496126399</v>
       </c>
       <c r="C295" s="1">
-        <v>8.4478909636109295E-2</v>
+        <v>8.4376066440544406E-2</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17248,10 +17577,10 @@
         <v>307</v>
       </c>
       <c r="B296" s="1">
-        <v>5.2426137496126399</v>
+        <v>5.25389374708476</v>
       </c>
       <c r="C296" s="1">
-        <v>8.4376066440544406E-2</v>
+        <v>8.42642456111901E-2</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17259,10 +17588,10 @@
         <v>308</v>
       </c>
       <c r="B297" s="1">
-        <v>5.25389374708476</v>
+        <v>5.2452132048918996</v>
       </c>
       <c r="C297" s="1">
-        <v>8.42642456111901E-2</v>
+        <v>8.3954508319290494E-2</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17270,10 +17599,10 @@
         <v>309</v>
       </c>
       <c r="B298" s="1">
-        <v>5.2452132048918996</v>
+        <v>5.2477036957110901</v>
       </c>
       <c r="C298" s="1">
-        <v>8.3954508319290494E-2</v>
+        <v>8.4241621326531999E-2</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17281,10 +17610,10 @@
         <v>310</v>
       </c>
       <c r="B299" s="1">
-        <v>5.2477036957110901</v>
+        <v>5.1912280334424699</v>
       </c>
       <c r="C299" s="1">
-        <v>8.4241621326531999E-2</v>
+        <v>8.39433811384213E-2</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17292,10 +17621,10 @@
         <v>311</v>
       </c>
       <c r="B300" s="1">
-        <v>5.1912280334424699</v>
+        <v>5.2649162726060403</v>
       </c>
       <c r="C300" s="1">
-        <v>8.39433811384213E-2</v>
+        <v>8.4883882170655206E-2</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17303,10 +17632,10 @@
         <v>312</v>
       </c>
       <c r="B301" s="1">
-        <v>5.2649162726060403</v>
+        <v>5.2682959002266401</v>
       </c>
       <c r="C301" s="1">
-        <v>8.4883882170655206E-2</v>
+        <v>8.4153042797615304E-2</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17314,10 +17643,10 @@
         <v>313</v>
       </c>
       <c r="B302" s="1">
-        <v>5.2682959002266401</v>
+        <v>4.0504847360743401</v>
       </c>
       <c r="C302" s="1">
-        <v>8.4153042797615304E-2</v>
+        <v>6.4664938143317294E-2</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17325,10 +17654,10 @@
         <v>314</v>
       </c>
       <c r="B303" s="1">
-        <v>4.0504847360743401</v>
+        <v>4.0496768121653703</v>
       </c>
       <c r="C303" s="1">
-        <v>6.4664938143317294E-2</v>
+        <v>6.48925563524336E-2</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17336,10 +17665,10 @@
         <v>315</v>
       </c>
       <c r="B304" s="1">
-        <v>4.0496768121653703</v>
+        <v>4.0401570007949097</v>
       </c>
       <c r="C304" s="1">
-        <v>6.48925563524336E-2</v>
+        <v>6.4717624366303003E-2</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17347,10 +17676,10 @@
         <v>316</v>
       </c>
       <c r="B305" s="1">
-        <v>4.0401570007949097</v>
+        <v>4.0452933053436704</v>
       </c>
       <c r="C305" s="1">
-        <v>6.4717624366303003E-2</v>
+        <v>6.5096945322289101E-2</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17358,10 +17687,10 @@
         <v>317</v>
       </c>
       <c r="B306" s="1">
-        <v>4.0452933053436704</v>
+        <v>4.0393053513377497</v>
       </c>
       <c r="C306" s="1">
-        <v>6.5096945322289101E-2</v>
+        <v>6.4780635694392893E-2</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17369,10 +17698,10 @@
         <v>318</v>
       </c>
       <c r="B307" s="1">
-        <v>4.0393053513377497</v>
+        <v>4.0427869051265404</v>
       </c>
       <c r="C307" s="1">
-        <v>6.4780635694392893E-2</v>
+        <v>6.4828747039054904E-2</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17380,10 +17709,10 @@
         <v>319</v>
       </c>
       <c r="B308" s="1">
-        <v>4.0427869051265404</v>
+        <v>4.0371132630075302</v>
       </c>
       <c r="C308" s="1">
-        <v>6.4828747039054904E-2</v>
+        <v>6.4845896931015903E-2</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17391,10 +17720,10 @@
         <v>320</v>
       </c>
       <c r="B309" s="1">
-        <v>4.0371132630075302</v>
+        <v>4.0301105995964903</v>
       </c>
       <c r="C309" s="1">
-        <v>6.4845896931015903E-2</v>
+        <v>6.4898532838035997E-2</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17402,10 +17731,10 @@
         <v>321</v>
       </c>
       <c r="B310" s="1">
-        <v>4.0301105995964903</v>
+        <v>4.0520999190004696</v>
       </c>
       <c r="C310" s="1">
-        <v>6.4898532838035997E-2</v>
+        <v>6.4393394651674596E-2</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17413,10 +17742,10 @@
         <v>322</v>
       </c>
       <c r="B311" s="1">
-        <v>4.0520999190004696</v>
+        <v>4.0532303423785203</v>
       </c>
       <c r="C311" s="1">
-        <v>6.4393394651674596E-2</v>
+        <v>6.4836933722996301E-2</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17424,10 +17753,10 @@
         <v>323</v>
       </c>
       <c r="B312" s="1">
-        <v>4.0532303423785203</v>
+        <v>4.0597656945719098</v>
       </c>
       <c r="C312" s="1">
-        <v>6.4836933722996301E-2</v>
+        <v>6.4898123293677099E-2</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17435,10 +17764,10 @@
         <v>324</v>
       </c>
       <c r="B313" s="1">
-        <v>4.0597656945719098</v>
+        <v>4.0397313521665303</v>
       </c>
       <c r="C313" s="1">
-        <v>6.4898123293677099E-2</v>
+        <v>6.48141939607636E-2</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17446,10 +17775,10 @@
         <v>325</v>
       </c>
       <c r="B314" s="1">
-        <v>4.0397313521665303</v>
+        <v>4.0389446603470498</v>
       </c>
       <c r="C314" s="1">
-        <v>6.48141939607636E-2</v>
+        <v>6.4945690313312696E-2</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17457,10 +17786,10 @@
         <v>326</v>
       </c>
       <c r="B315" s="1">
-        <v>4.0389446603470498</v>
+        <v>4.0491521884945199</v>
       </c>
       <c r="C315" s="1">
-        <v>6.4945690313312696E-2</v>
+        <v>6.4750632359324503E-2</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17468,10 +17797,10 @@
         <v>327</v>
       </c>
       <c r="B316" s="1">
-        <v>4.0491521884945199</v>
+        <v>4.0282207799584802</v>
       </c>
       <c r="C316" s="1">
-        <v>6.4750632359324503E-2</v>
+        <v>6.46466961945657E-2</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17479,10 +17808,10 @@
         <v>328</v>
       </c>
       <c r="B317" s="1">
-        <v>4.0282207799584802</v>
+        <v>4.0373666399902799</v>
       </c>
       <c r="C317" s="1">
-        <v>6.46466961945657E-2</v>
+        <v>6.5070391277710998E-2</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17490,10 +17819,10 @@
         <v>329</v>
       </c>
       <c r="B318" s="1">
-        <v>4.0373666399902799</v>
+        <v>4.0254616281370303</v>
       </c>
       <c r="C318" s="1">
-        <v>6.5070391277710998E-2</v>
+        <v>6.5003508402351404E-2</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17501,10 +17830,10 @@
         <v>330</v>
       </c>
       <c r="B319" s="1">
-        <v>4.0254616281370303</v>
+        <v>4.0346044905874798</v>
       </c>
       <c r="C319" s="1">
-        <v>6.5003508402351404E-2</v>
+        <v>6.4702157939462199E-2</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17512,10 +17841,10 @@
         <v>331</v>
       </c>
       <c r="B320" s="1">
-        <v>4.0346044905874798</v>
+        <v>4.0220126763814203</v>
       </c>
       <c r="C320" s="1">
-        <v>6.4702157939462199E-2</v>
+        <v>6.4789520162763903E-2</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17523,10 +17852,10 @@
         <v>332</v>
       </c>
       <c r="B321" s="1">
-        <v>4.0220126763814203</v>
+        <v>4.0377589881580498</v>
       </c>
       <c r="C321" s="1">
-        <v>6.4789520162763903E-2</v>
+        <v>6.4698100702121605E-2</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17534,10 +17863,10 @@
         <v>333</v>
       </c>
       <c r="B322" s="1">
-        <v>4.0377589881580498</v>
+        <v>4.0016969711271004</v>
       </c>
       <c r="C322" s="1">
-        <v>6.4698100702121605E-2</v>
+        <v>6.39060983563466E-2</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17545,10 +17874,10 @@
         <v>334</v>
       </c>
       <c r="B323" s="1">
-        <v>4.0016969711271004</v>
+        <v>3.9850777599500198</v>
       </c>
       <c r="C323" s="1">
-        <v>6.39060983563466E-2</v>
+        <v>6.4217223623450101E-2</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17556,10 +17885,10 @@
         <v>335</v>
       </c>
       <c r="B324" s="1">
-        <v>3.9850777599500198</v>
+        <v>4.0132441168710704</v>
       </c>
       <c r="C324" s="1">
-        <v>6.4217223623450101E-2</v>
+        <v>6.4146735969449406E-2</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17567,10 +17896,10 @@
         <v>336</v>
       </c>
       <c r="B325" s="1">
-        <v>4.0132441168710704</v>
+        <v>4.0107044449171996</v>
       </c>
       <c r="C325" s="1">
-        <v>6.4146735969449406E-2</v>
+        <v>6.4629796704458606E-2</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17578,10 +17907,10 @@
         <v>337</v>
       </c>
       <c r="B326" s="1">
-        <v>4.0107044449171996</v>
+        <v>4.0042080560711302</v>
       </c>
       <c r="C326" s="1">
-        <v>6.4629796704458606E-2</v>
+        <v>6.43943878164248E-2</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17589,10 +17918,10 @@
         <v>338</v>
       </c>
       <c r="B327" s="1">
-        <v>4.0042080560711302</v>
+        <v>4.0137738076926297</v>
       </c>
       <c r="C327" s="1">
-        <v>6.43943878164248E-2</v>
+        <v>6.4478725052475205E-2</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17600,10 +17929,10 @@
         <v>339</v>
       </c>
       <c r="B328" s="1">
-        <v>4.0137738076926297</v>
+        <v>4.0189067438591497</v>
       </c>
       <c r="C328" s="1">
-        <v>6.4478725052475205E-2</v>
+        <v>6.4781321835991806E-2</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17611,10 +17940,10 @@
         <v>340</v>
       </c>
       <c r="B329" s="1">
-        <v>4.0189067438591497</v>
+        <v>4.0019418304313801</v>
       </c>
       <c r="C329" s="1">
-        <v>6.4781321835991806E-2</v>
+        <v>6.4392626905219894E-2</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17622,10 +17951,10 @@
         <v>341</v>
       </c>
       <c r="B330" s="1">
-        <v>4.0019418304313801</v>
+        <v>4.0058057955871602</v>
       </c>
       <c r="C330" s="1">
-        <v>6.4392626905219894E-2</v>
+        <v>6.4250407980306304E-2</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17633,10 +17962,10 @@
         <v>342</v>
       </c>
       <c r="B331" s="1">
-        <v>4.0058057955871602</v>
+        <v>4.0060301681826802</v>
       </c>
       <c r="C331" s="1">
-        <v>6.4250407980306304E-2</v>
+        <v>6.4167196154649705E-2</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17644,10 +17973,10 @@
         <v>343</v>
       </c>
       <c r="B332" s="1">
-        <v>4.0060301681826802</v>
+        <v>3.99829105994908</v>
       </c>
       <c r="C332" s="1">
-        <v>6.4167196154649705E-2</v>
+        <v>6.4208136070914995E-2</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17655,10 +17984,10 @@
         <v>344</v>
       </c>
       <c r="B333" s="1">
-        <v>3.99829105994908</v>
+        <v>3.9906830558389799</v>
       </c>
       <c r="C333" s="1">
-        <v>6.4208136070914995E-2</v>
+        <v>6.4378306448205899E-2</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17666,10 +17995,10 @@
         <v>345</v>
       </c>
       <c r="B334" s="1">
-        <v>3.9906830558389799</v>
+        <v>3.99736506566357</v>
       </c>
       <c r="C334" s="1">
-        <v>6.4378306448205899E-2</v>
+        <v>6.4317608614747404E-2</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17677,10 +18006,10 @@
         <v>346</v>
       </c>
       <c r="B335" s="1">
-        <v>3.99736506566357</v>
+        <v>3.98390122498571</v>
       </c>
       <c r="C335" s="1">
-        <v>6.4317608614747404E-2</v>
+        <v>6.3677492575877404E-2</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17688,10 +18017,10 @@
         <v>347</v>
       </c>
       <c r="B336" s="1">
-        <v>3.98390122498571</v>
+        <v>3.9792620371784699</v>
       </c>
       <c r="C336" s="1">
-        <v>6.3677492575877404E-2</v>
+        <v>6.3641331008131394E-2</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17699,10 +18028,10 @@
         <v>348</v>
       </c>
       <c r="B337" s="1">
-        <v>3.9792620371784699</v>
+        <v>6.5540355078319896</v>
       </c>
       <c r="C337" s="1">
-        <v>6.3641331008131394E-2</v>
+        <v>0.105551348978041</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17710,10 +18039,10 @@
         <v>349</v>
       </c>
       <c r="B338" s="1">
-        <v>6.5540355078319896</v>
+        <v>6.5827244241657299</v>
       </c>
       <c r="C338" s="1">
-        <v>0.105551348978041</v>
+        <v>0.105991123494967</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17721,10 +18050,10 @@
         <v>350</v>
       </c>
       <c r="B339" s="1">
-        <v>6.5827244241657299</v>
+        <v>6.6067856280796899</v>
       </c>
       <c r="C339" s="1">
-        <v>0.105991123494967</v>
+        <v>0.10533604175596301</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17732,10 +18061,10 @@
         <v>351</v>
       </c>
       <c r="B340" s="1">
-        <v>6.6067856280796899</v>
+        <v>6.5726574723992401</v>
       </c>
       <c r="C340" s="1">
-        <v>0.10533604175596301</v>
+        <v>0.105665444142923</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17743,10 +18072,10 @@
         <v>352</v>
       </c>
       <c r="B341" s="1">
-        <v>6.5726574723992401</v>
+        <v>6.60849329589227</v>
       </c>
       <c r="C341" s="1">
-        <v>0.105665444142923</v>
+        <v>0.105198678205429</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17754,10 +18083,10 @@
         <v>353</v>
       </c>
       <c r="B342" s="1">
-        <v>6.60849329589227</v>
+        <v>6.61449436632694</v>
       </c>
       <c r="C342" s="1">
-        <v>0.105198678205429</v>
+        <v>0.105495395727284</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17765,10 +18094,10 @@
         <v>354</v>
       </c>
       <c r="B343" s="1">
-        <v>6.61449436632694</v>
+        <v>6.5773613187522404</v>
       </c>
       <c r="C343" s="1">
-        <v>0.105495395727284</v>
+        <v>0.105314548416934</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17776,10 +18105,10 @@
         <v>355</v>
       </c>
       <c r="B344" s="1">
-        <v>6.5773613187522404</v>
+        <v>6.6014893245484396</v>
       </c>
       <c r="C344" s="1">
-        <v>0.105314548416934</v>
+        <v>0.10568145895007799</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17787,10 +18116,10 @@
         <v>356</v>
       </c>
       <c r="B345" s="1">
-        <v>6.6014893245484396</v>
+        <v>6.5572879597699503</v>
       </c>
       <c r="C345" s="1">
-        <v>0.10568145895007799</v>
+        <v>0.10527614250211299</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17798,10 +18127,10 @@
         <v>357</v>
       </c>
       <c r="B346" s="1">
-        <v>6.5572879597699503</v>
+        <v>6.6008191975600301</v>
       </c>
       <c r="C346" s="1">
-        <v>0.10527614250211299</v>
+        <v>0.10576449952939899</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17809,10 +18138,10 @@
         <v>358</v>
       </c>
       <c r="B347" s="1">
-        <v>6.6008191975600301</v>
+        <v>6.6252507343515497</v>
       </c>
       <c r="C347" s="1">
-        <v>0.10576449952939899</v>
+        <v>0.10568293315542</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17820,10 +18149,10 @@
         <v>359</v>
       </c>
       <c r="B348" s="1">
-        <v>6.6252507343515497</v>
+        <v>6.5704906061544399</v>
       </c>
       <c r="C348" s="1">
-        <v>0.10568293315542</v>
+        <v>0.10581148690660699</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17831,10 +18160,10 @@
         <v>360</v>
       </c>
       <c r="B349" s="1">
-        <v>6.5704906061544399</v>
+        <v>6.5936568893976704</v>
       </c>
       <c r="C349" s="1">
-        <v>0.10581148690660699</v>
+        <v>0.105635832709833</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17842,10 +18171,10 @@
         <v>361</v>
       </c>
       <c r="B350" s="1">
-        <v>6.5936568893976704</v>
+        <v>6.5983973262679001</v>
       </c>
       <c r="C350" s="1">
-        <v>0.105635832709833</v>
+        <v>0.105645315996043</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17853,10 +18182,10 @@
         <v>362</v>
       </c>
       <c r="B351" s="1">
-        <v>6.5983973262679001</v>
+        <v>6.6115893763595901</v>
       </c>
       <c r="C351" s="1">
-        <v>0.105645315996043</v>
+        <v>0.105275447604903</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17864,10 +18193,10 @@
         <v>363</v>
       </c>
       <c r="B352" s="1">
-        <v>6.6115893763595901</v>
+        <v>6.5582265339750796</v>
       </c>
       <c r="C352" s="1">
-        <v>0.105275447604903</v>
+        <v>0.105662668847811</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17875,10 +18204,10 @@
         <v>364</v>
       </c>
       <c r="B353" s="1">
-        <v>6.5582265339750796</v>
+        <v>6.5712631537936099</v>
       </c>
       <c r="C353" s="1">
-        <v>0.105662668847811</v>
+        <v>0.105625257618033</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17886,10 +18215,10 @@
         <v>365</v>
       </c>
       <c r="B354" s="1">
-        <v>6.5712631537936099</v>
+        <v>6.6270719261065301</v>
       </c>
       <c r="C354" s="1">
-        <v>0.105625257618033</v>
+        <v>0.106115800022815</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17897,10 +18226,10 @@
         <v>366</v>
       </c>
       <c r="B355" s="1">
-        <v>6.6270719261065301</v>
+        <v>6.6192410240628501</v>
       </c>
       <c r="C355" s="1">
-        <v>0.106115800022815</v>
+        <v>0.106389444933465</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17908,10 +18237,10 @@
         <v>367</v>
       </c>
       <c r="B356" s="1">
-        <v>6.6192410240628501</v>
+        <v>6.57641937555222</v>
       </c>
       <c r="C356" s="1">
-        <v>0.106389444933465</v>
+        <v>0.105686237933491</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17919,10 +18248,10 @@
         <v>368</v>
       </c>
       <c r="B357" s="1">
-        <v>6.57641937555222</v>
+        <v>6.6087667968385899</v>
       </c>
       <c r="C357" s="1">
-        <v>0.105686237933491</v>
+        <v>0.106107125977925</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17930,10 +18259,10 @@
         <v>369</v>
       </c>
       <c r="B358" s="1">
-        <v>6.6087667968385899</v>
+        <v>6.5350348620169401</v>
       </c>
       <c r="C358" s="1">
-        <v>0.106107125977925</v>
+        <v>0.10569305527527301</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17941,10 +18270,10 @@
         <v>370</v>
       </c>
       <c r="B359" s="1">
-        <v>6.5350348620169401</v>
+        <v>6.5557760188699499</v>
       </c>
       <c r="C359" s="1">
-        <v>0.10569305527527301</v>
+        <v>0.105721916432143</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17952,10 +18281,10 @@
         <v>371</v>
       </c>
       <c r="B360" s="1">
-        <v>6.5557760188699499</v>
+        <v>5.9622611291336396</v>
       </c>
       <c r="C360" s="1">
-        <v>0.105721916432143</v>
+        <v>9.4951214409789694E-2</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17963,10 +18292,10 @@
         <v>372</v>
       </c>
       <c r="B361" s="1">
-        <v>6.5032195210687904</v>
+        <v>6.0066466306228703</v>
       </c>
       <c r="C361" s="1">
-        <v>0.10501733793063001</v>
+        <v>9.48427612752826E-2</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17974,10 +18303,10 @@
         <v>373</v>
       </c>
       <c r="B362" s="1">
-        <v>5.9622611291336396</v>
+        <v>5.9421219928096498</v>
       </c>
       <c r="C362" s="1">
-        <v>9.4951214409789694E-2</v>
+        <v>9.5323780436117694E-2</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17985,10 +18314,10 @@
         <v>374</v>
       </c>
       <c r="B363" s="1">
-        <v>6.0066466306228703</v>
+        <v>5.97435305885893</v>
       </c>
       <c r="C363" s="1">
-        <v>9.48427612752826E-2</v>
+        <v>9.5239680372887395E-2</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -17996,10 +18325,10 @@
         <v>375</v>
       </c>
       <c r="B364" s="1">
-        <v>5.9421219928096498</v>
+        <v>5.9503505932316996</v>
       </c>
       <c r="C364" s="1">
-        <v>9.5323780436117694E-2</v>
+        <v>9.4913957126963905E-2</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18007,10 +18336,10 @@
         <v>376</v>
       </c>
       <c r="B365" s="1">
-        <v>5.97435305885893</v>
+        <v>5.9548297693894297</v>
       </c>
       <c r="C365" s="1">
-        <v>9.5239680372887395E-2</v>
+        <v>9.5207811574283305E-2</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18018,10 +18347,10 @@
         <v>377</v>
       </c>
       <c r="B366" s="1">
-        <v>5.9503505932316996</v>
+        <v>5.9553030366034303</v>
       </c>
       <c r="C366" s="1">
-        <v>9.4913957126963905E-2</v>
+        <v>9.5333549341072299E-2</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18029,10 +18358,10 @@
         <v>378</v>
       </c>
       <c r="B367" s="1">
-        <v>5.9548297693894297</v>
+        <v>5.9714415945772101</v>
       </c>
       <c r="C367" s="1">
-        <v>9.5207811574283305E-2</v>
+        <v>9.5272929905971096E-2</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18040,10 +18369,10 @@
         <v>379</v>
       </c>
       <c r="B368" s="1">
-        <v>5.9553030366034303</v>
+        <v>5.9546595386126704</v>
       </c>
       <c r="C368" s="1">
-        <v>9.5333549341072299E-2</v>
+        <v>9.5825730092529093E-2</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18051,10 +18380,10 @@
         <v>380</v>
       </c>
       <c r="B369" s="1">
-        <v>5.9714415945772101</v>
+        <v>5.9526717332290202</v>
       </c>
       <c r="C369" s="1">
-        <v>9.5272929905971096E-2</v>
+        <v>9.5557760398135405E-2</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18062,10 +18391,10 @@
         <v>381</v>
       </c>
       <c r="B370" s="1">
-        <v>5.9546595386126704</v>
+        <v>5.9925762983853099</v>
       </c>
       <c r="C370" s="1">
-        <v>9.5825730092529093E-2</v>
+        <v>9.5707695616314301E-2</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18073,10 +18402,10 @@
         <v>382</v>
       </c>
       <c r="B371" s="1">
-        <v>5.9526717332290202</v>
+        <v>5.9607737827043099</v>
       </c>
       <c r="C371" s="1">
-        <v>9.5557760398135405E-2</v>
+        <v>9.5513472864986904E-2</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18084,10 +18413,10 @@
         <v>383</v>
       </c>
       <c r="B372" s="1">
-        <v>5.9925762983853099</v>
+        <v>5.9798136479539004</v>
       </c>
       <c r="C372" s="1">
-        <v>9.5707695616314301E-2</v>
+        <v>9.5307639125115001E-2</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18095,10 +18424,10 @@
         <v>384</v>
       </c>
       <c r="B373" s="1">
-        <v>5.9607737827043099</v>
+        <v>5.9855117155737396</v>
       </c>
       <c r="C373" s="1">
-        <v>9.5513472864986904E-2</v>
+        <v>9.6102530139334702E-2</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18106,10 +18435,10 @@
         <v>385</v>
       </c>
       <c r="B374" s="1">
-        <v>5.9798136479539004</v>
+        <v>6.0292733180363696</v>
       </c>
       <c r="C374" s="1">
-        <v>9.5307639125115001E-2</v>
+        <v>9.5842612321962603E-2</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18117,10 +18446,10 @@
         <v>386</v>
       </c>
       <c r="B375" s="1">
-        <v>5.9855117155737396</v>
+        <v>5.9440797542562098</v>
       </c>
       <c r="C375" s="1">
-        <v>9.6102530139334702E-2</v>
+        <v>9.5502184039375396E-2</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18128,10 +18457,10 @@
         <v>387</v>
       </c>
       <c r="B376" s="1">
-        <v>6.0292733180363696</v>
+        <v>5.9637069175640898</v>
       </c>
       <c r="C376" s="1">
-        <v>9.5842612321962603E-2</v>
+        <v>9.5885385701222001E-2</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18139,10 +18468,10 @@
         <v>388</v>
       </c>
       <c r="B377" s="1">
-        <v>5.9440797542562098</v>
+        <v>5.9851248839214604</v>
       </c>
       <c r="C377" s="1">
-        <v>9.5502184039375396E-2</v>
+        <v>9.6439591076729503E-2</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18150,10 +18479,10 @@
         <v>389</v>
       </c>
       <c r="B378" s="1">
-        <v>5.9637069175640898</v>
+        <v>5.9753311000708296</v>
       </c>
       <c r="C378" s="1">
-        <v>9.5885385701222001E-2</v>
+        <v>9.5315139971463694E-2</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18161,10 +18490,10 @@
         <v>390</v>
       </c>
       <c r="B379" s="1">
-        <v>5.9851248839214604</v>
+        <v>5.95595351810669</v>
       </c>
       <c r="C379" s="1">
-        <v>9.6439591076729503E-2</v>
+        <v>9.5613752572800206E-2</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18172,10 +18501,10 @@
         <v>391</v>
       </c>
       <c r="B380" s="1">
-        <v>5.9753311000708296</v>
+        <v>5.9436339167314696</v>
       </c>
       <c r="C380" s="1">
-        <v>9.5315139971463694E-2</v>
+        <v>9.57329103303277E-2</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18183,10 +18512,10 @@
         <v>392</v>
       </c>
       <c r="B381" s="1">
-        <v>5.95595351810669</v>
+        <v>5.9680724903054401</v>
       </c>
       <c r="C381" s="1">
-        <v>9.5613752572800206E-2</v>
+        <v>9.4740461511437099E-2</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18194,10 +18523,10 @@
         <v>393</v>
       </c>
       <c r="B382" s="1">
-        <v>5.9436339167314696</v>
+        <v>5.97890051441588</v>
       </c>
       <c r="C382" s="1">
-        <v>9.57329103303277E-2</v>
+        <v>9.56068005906138E-2</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18205,10 +18534,10 @@
         <v>394</v>
       </c>
       <c r="B383" s="1">
-        <v>5.9680724903054401</v>
+        <v>5.9641145262355701</v>
       </c>
       <c r="C383" s="1">
-        <v>9.4740461511437099E-2</v>
+        <v>9.5241121615471297E-2</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18216,10 +18545,10 @@
         <v>395</v>
       </c>
       <c r="B384" s="1">
-        <v>5.97890051441588</v>
+        <v>5.9548137587277301</v>
       </c>
       <c r="C384" s="1">
-        <v>9.56068005906138E-2</v>
+        <v>9.5433597155929403E-2</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18227,10 +18556,10 @@
         <v>396</v>
       </c>
       <c r="B385" s="1">
-        <v>5.9641145262355701</v>
+        <v>5.9412161279185698</v>
       </c>
       <c r="C385" s="1">
-        <v>9.5241121615471297E-2</v>
+        <v>9.5987289369727502E-2</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18238,10 +18567,10 @@
         <v>397</v>
       </c>
       <c r="B386" s="1">
-        <v>5.9548137587277301</v>
+        <v>5.9237749973025897</v>
       </c>
       <c r="C386" s="1">
-        <v>9.5433597155929403E-2</v>
+        <v>9.5313166809118E-2</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18249,10 +18578,10 @@
         <v>398</v>
       </c>
       <c r="B387" s="1">
-        <v>5.9412161279185698</v>
+        <v>5.9321677454244002</v>
       </c>
       <c r="C387" s="1">
-        <v>9.5987289369727502E-2</v>
+        <v>9.5108590519696196E-2</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18260,10 +18589,10 @@
         <v>399</v>
       </c>
       <c r="B388" s="1">
-        <v>5.9237749973025897</v>
+        <v>5.9655682681986404</v>
       </c>
       <c r="C388" s="1">
-        <v>9.5313166809118E-2</v>
+        <v>9.5279653817559096E-2</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18271,10 +18600,10 @@
         <v>400</v>
       </c>
       <c r="B389" s="1">
-        <v>5.9321677454244002</v>
+        <v>5.9648566611082501</v>
       </c>
       <c r="C389" s="1">
-        <v>9.5108590519696196E-2</v>
+        <v>9.5070431421425905E-2</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18282,10 +18611,10 @@
         <v>401</v>
       </c>
       <c r="B390" s="1">
-        <v>5.9655682681986404</v>
+        <v>3.0672817324059798</v>
       </c>
       <c r="C390" s="1">
-        <v>9.5279653817559096E-2</v>
+        <v>4.9220544832568401E-2</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -18293,10 +18622,340 @@
         <v>402</v>
       </c>
       <c r="B391" s="1">
-        <v>5.9648566611082501</v>
+        <v>3.06498328697809</v>
       </c>
       <c r="C391" s="1">
-        <v>9.5070431421425905E-2</v>
+        <v>4.8826525513616603E-2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B392" s="1">
+        <v>3.06753441554193</v>
+      </c>
+      <c r="C392" s="1">
+        <v>4.9256122272570202E-2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B393" s="1">
+        <v>3.0756019900176499</v>
+      </c>
+      <c r="C393" s="1">
+        <v>4.97179954883646E-2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B394" s="1">
+        <v>3.0649036050172098</v>
+      </c>
+      <c r="C394" s="1">
+        <v>4.9725118840505199E-2</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B395" s="1">
+        <v>3.06529341587372</v>
+      </c>
+      <c r="C395" s="1">
+        <v>4.9381962862556E-2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B396" s="1">
+        <v>3.0726606549971298</v>
+      </c>
+      <c r="C396" s="1">
+        <v>4.8979944321647401E-2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B397" s="1">
+        <v>3.0831176610414701</v>
+      </c>
+      <c r="C397" s="1">
+        <v>4.9045485231240298E-2</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B398" s="1">
+        <v>3.0668965665752701</v>
+      </c>
+      <c r="C398" s="1">
+        <v>4.8965298287210399E-2</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B399" s="1">
+        <v>3.0577539539137901</v>
+      </c>
+      <c r="C399" s="1">
+        <v>4.8957627310304702E-2</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B400" s="1">
+        <v>3.0461287705788598</v>
+      </c>
+      <c r="C400" s="1">
+        <v>4.9000057015244597E-2</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B401" s="1">
+        <v>3.0420177016521102</v>
+      </c>
+      <c r="C401" s="1">
+        <v>4.8651617087087401E-2</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B402" s="1">
+        <v>3.0577648925430601</v>
+      </c>
+      <c r="C402" s="1">
+        <v>4.8810930819998197E-2</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B403" s="1">
+        <v>3.07207699092403</v>
+      </c>
+      <c r="C403" s="1">
+        <v>4.8901071369119802E-2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B404" s="1">
+        <v>3.0603120961688499</v>
+      </c>
+      <c r="C404" s="1">
+        <v>4.9126205451321202E-2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B405" s="1">
+        <v>3.0495273783215602</v>
+      </c>
+      <c r="C405" s="1">
+        <v>4.95058693259324E-2</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B406" s="1">
+        <v>3.0483213432966099</v>
+      </c>
+      <c r="C406" s="1">
+        <v>4.8651769164606402E-2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B407" s="1">
+        <v>3.0507028081060601</v>
+      </c>
+      <c r="C407" s="1">
+        <v>4.8908241247632697E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B408" s="1">
+        <v>3.0503873160495498</v>
+      </c>
+      <c r="C408" s="1">
+        <v>4.8699146330509702E-2</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B409" s="1">
+        <v>3.0616213771126799</v>
+      </c>
+      <c r="C409" s="1">
+        <v>4.91555175312548E-2</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B410" s="1">
+        <v>3.0441812745358798</v>
+      </c>
+      <c r="C410" s="1">
+        <v>4.9268660787059597E-2</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B411" s="1">
+        <v>3.0545733491419398</v>
+      </c>
+      <c r="C411" s="1">
+        <v>4.8826826414769098E-2</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B412" s="1">
+        <v>3.0565111313221198</v>
+      </c>
+      <c r="C412" s="1">
+        <v>4.8764627198113697E-2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B413" s="1">
+        <v>3.0569612836170998</v>
+      </c>
+      <c r="C413" s="1">
+        <v>4.9029160899217702E-2</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B414" s="1">
+        <v>3.0531280697850698</v>
+      </c>
+      <c r="C414" s="1">
+        <v>4.8854122518207498E-2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B415" s="1">
+        <v>3.0495276887412501</v>
+      </c>
+      <c r="C415" s="1">
+        <v>4.9133881801381701E-2</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B416" s="1">
+        <v>3.0451824247254602</v>
+      </c>
+      <c r="C416" s="1">
+        <v>4.9071806924917999E-2</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B417" s="1">
+        <v>3.0636069285517098</v>
+      </c>
+      <c r="C417" s="1">
+        <v>4.9142870700877098E-2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B418" s="1">
+        <v>3.0573709331599099</v>
+      </c>
+      <c r="C418" s="1">
+        <v>4.9249210174874901E-2</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B419" s="1">
+        <v>3.0482345249944598</v>
+      </c>
+      <c r="C419" s="1">
+        <v>4.8951873888496603E-2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B420" s="1">
+        <v>3.0486121479316401</v>
+      </c>
+      <c r="C420" s="1">
+        <v>4.8933368456572202E-2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B421" s="1">
+        <v>3.0547580292283598</v>
+      </c>
+      <c r="C421" s="1">
+        <v>4.87619094275357E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Fit Results/AllFitsF1=4.xlsx
+++ b/Fit Results/AllFitsF1=4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09B28F3-B141-4BFA-846C-FBC4A3F9103D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26496A1B-C625-4E3E-814C-938B4007988D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4125" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="5" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="894" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19006,7 +19007,7 @@
         <v>3.9061146219856075E-4</v>
       </c>
       <c r="I1">
-        <f t="shared" ref="I1" si="1">_xlfn.STDEV.S(I4:I39)/SQRT(COUNT(I4:I39))</f>
+        <f>_xlfn.STDEV.S(I4:I39)/SQRT(COUNT(I4:I39))</f>
         <v>2.8613971962500952E-4</v>
       </c>
     </row>
@@ -19019,31 +19020,31 @@
         <v>0.77222061447474444</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="2">100*C1/AVERAGE(C4:C39)</f>
+        <f t="shared" ref="C2:H2" si="1">100*C1/AVERAGE(C4:C39)</f>
         <v>0.31059913870542799</v>
       </c>
       <c r="D2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.47323404082039927</v>
       </c>
       <c r="E2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.51299689196796872</v>
       </c>
       <c r="F2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.19002663504224529</v>
       </c>
       <c r="G2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.19588898416061237</v>
       </c>
       <c r="H2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.16177404443417376</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2" si="3">100*I1/AVERAGE(I4:I39)</f>
+        <f>100*I1/AVERAGE(I4:I39)</f>
         <v>0.12997532261023939</v>
       </c>
     </row>
@@ -19860,7 +19861,7 @@
         <v>2.4909699122220328E-2</v>
       </c>
       <c r="I1">
-        <f t="shared" ref="I1" si="1">_xlfn.STDEV.S(I4:I39)/SQRT(COUNT(I4:I39))</f>
+        <f>_xlfn.STDEV.S(I4:I39)/SQRT(COUNT(I4:I39))</f>
         <v>1.4794192860515082E-2</v>
       </c>
     </row>
@@ -19873,19 +19874,19 @@
         <v>0.31448069643187493</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="2">100*C1/AVERAGE(C4:C39)</f>
+        <f t="shared" ref="C2:H2" si="1">100*C1/AVERAGE(C4:C39)</f>
         <v>0.116432955776871</v>
       </c>
       <c r="D2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.29686053435370169</v>
       </c>
       <c r="E2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.21644587691990655</v>
       </c>
       <c r="F2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.14582319975211133</v>
       </c>
       <c r="G2">
@@ -19893,11 +19894,11 @@
         <v>0.10085341371304617</v>
       </c>
       <c r="H2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.16869744421197019</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2" si="3">100*I1/AVERAGE(I4:I39)</f>
+        <f>100*I1/AVERAGE(I4:I39)</f>
         <v>0.1090690310547095</v>
       </c>
     </row>
